--- a/results/job_matches_2026-04-16.xlsx
+++ b/results/job_matches_2026-04-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -958,25 +958,25 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Live Nation</t>
+          <t>Ignite Insurance Systems</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Scala, Kafka, MySQL, MongoDB, NoSQL, Splunk, CI/CD</t>
+          <t>Redshift, RDS, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,19 +986,19 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31ca2baaf21560e8</t>
+          <t>https://www.indeed.com/viewjob?jk=560d14506d8aa36b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior ML Engineer</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Momentive Software</t>
+          <t>BLOC Resources, LLC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Azure, GCP</t>
+          <t>Azure, Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f99034f0e149e6e6</t>
+          <t>https://www.indeed.com/viewjob?jk=d9e13379e16ee4b4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Ad Ops Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ignite Insurance Systems</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=560d14506d8aa36b</t>
+          <t>https://www.indeed.com/viewjob?jk=f14f238cb8b8c5f1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Verisk</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema, dbt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e99b4467c3c6aa55</t>
+          <t>https://www.indeed.com/viewjob?jk=7c4955f2e41966ef</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BLOC Resources, LLC</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Azure, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9e13379e16ee4b4</t>
+          <t>https://www.indeed.com/viewjob?jk=fcd17ae9e035b9a9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Ad Ops Engineer</t>
+          <t>Associate IT Officer, Data and Information Management (Associate Data Engineer)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>World Bank Group</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,19 +1161,19 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f14f238cb8b8c5f1</t>
+          <t>https://www.indeed.com/viewjob?jk=7a40cff6b5df03cd</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer- OrderlyMeds</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>OrderlyMeds</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1182,46 +1182,46 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema, dbt</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c4955f2e41966ef</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb2a73a0846955d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Azure, GCP, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Databricks, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcd17ae9e035b9a9</t>
+          <t>https://www.indeed.com/viewjob?jk=aa4d88005315e7ba</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer- OrderlyMeds</t>
+          <t>Senior Analytics Engineer - Power BI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>OrderlyMeds</t>
+          <t>Broadview Federal Credit Union</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Databricks Lakehouse, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb2a73a0846955d</t>
+          <t>https://www.indeed.com/viewjob?jk=ddee7a1fd9164fde</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data &amp; AI Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Olson Kundig</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Databricks, Scala, DynamoDB</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, GCP, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa4d88005315e7ba</t>
+          <t>https://www.indeed.com/viewjob?jk=d831e0d8e2c5553f</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Solution Architect, Enterprise - Eastern Time Zone</t>
+          <t>Data Architecture Intern</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Smart Data Solutions</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
+          <t>AWS, S3, IAM, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f33106731db1775</t>
+          <t>https://www.indeed.com/viewjob?jk=d67805e12d384da2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Solution Architect, Enterprise - Eastern Time Zone</t>
+          <t>Senior, Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Cassandra</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,172 +1371,172 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90d356ab99a57489</t>
+          <t>https://www.indeed.com/viewjob?jk=3fcd1c4e67959eea</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Solution Architect, Enterprise - Eastern Time Zone</t>
+          <t>AI Intern</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, dbt, MLflow</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15664632526fabdb</t>
+          <t>https://www.indeed.com/viewjob?jk=7bea47ac5f13bd1f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Solution Architect, Enterprise - Eastern Time Zone</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=507830f63a6d47c9</t>
+          <t>https://www.indeed.com/viewjob?jk=93144249a4967543</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Solution Architect, Enterprise - Eastern Time Zone</t>
+          <t>Research Engineer II</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Texas A&amp;M University</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bryan, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98d7971656e73b43</t>
+          <t>https://www.indeed.com/viewjob?jk=09b3207da19db4ee</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Olson Kundig</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Atlanta, KS, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, GCP, Snowflake, Data Modeling, ETL</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Azure Cosmos DB, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d831e0d8e2c5553f</t>
+          <t>https://www.indeed.com/viewjob?jk=e9a02726d78410b5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Architecture Intern</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Smart Data Solutions</t>
+          <t>Energy Services Group</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d67805e12d384da2</t>
+          <t>https://www.indeed.com/viewjob?jk=6918de34da34b82a</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior, Software Engineer</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Cassandra</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fcd1c4e67959eea</t>
+          <t>https://www.indeed.com/viewjob?jk=b2a1afc987319b9a</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AI Intern</t>
+          <t>Site Reliability Engineer (Cloud Enablement)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Flexera</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, dbt, MLflow</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bea47ac5f13bd1f</t>
+          <t>https://www.indeed.com/viewjob?jk=72d1842ef3999b1d</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Enterprise Application Developer (Full Stack)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>Exponent</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, ECS, RDS, Azure, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93144249a4967543</t>
+          <t>https://www.indeed.com/viewjob?jk=57406ee750d6ac9c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Research Engineer II</t>
+          <t>Data Engineer - Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bryan, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, ETL, Power BI, Tableau</t>
+          <t>RDS, Databricks, GCP, Spark, Scala, Kafka, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09b3207da19db4ee</t>
+          <t>https://www.indeed.com/viewjob?jk=48617c6692425cb2</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atlanta, KS, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Azure Cosmos DB, Data Modeling, ELT</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9a02726d78410b5</t>
+          <t>https://www.indeed.com/viewjob?jk=a5acecf0e4305790</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>AI/ML Engineering Intern (Summer 2026)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Energy Services Group</t>
+          <t>Poshmark</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>Redshift, Databricks, Spark, Scala, Kafka, MongoDB, MLflow, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,67 +1756,67 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6918de34da34b82a</t>
+          <t>https://www.indeed.com/viewjob?jk=7fd3431b51acd4b5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Cloudera Public Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Plano, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2a1afc987319b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=ce7428fbc9c89fa9</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (Cloud Enablement)</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Flexera</t>
+          <t>Panasonic Automotive</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Vertex AI, Spark, Scala, Spark Streaming, Kafka, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,67 +1826,67 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72d1842ef3999b1d</t>
+          <t>https://www.indeed.com/viewjob?jk=11ce688bd126a002</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Enterprise Application Developer (Full Stack)</t>
+          <t>Software Engineer - Backend Java</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Exponent</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, ECS, RDS, Azure, Scala, SQL Server</t>
+          <t>AWS, Lambda, RDS, Scala, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57406ee750d6ac9c</t>
+          <t>https://www.indeed.com/viewjob?jk=a18ff10136ae42f8</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Warehouse Architect</t>
+          <t>DevOps &amp; AI Automation Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Databricks, GCP, Spark, Scala, Kafka, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48617c6692425cb2</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6b296a0ce2f382</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Sr. Software Engineer - Data Infrastructure</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>AWS, S3, RDS, GCP, HDFS, Hive, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5acecf0e4305790</t>
+          <t>https://www.indeed.com/viewjob?jk=df9f48d9232b00bf</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AI/ML Engineering Intern (Summer 2026)</t>
+          <t>Senior Data Engineer - IICS</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Poshmark</t>
+          <t>SYSTECH USA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, Scala, Kafka, MongoDB, MLflow, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Redshift, Cloud Storage, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,159 +1966,159 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fd3431b51acd4b5</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf36b7e279da791</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Cloudera Public Cloud Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Banner Health</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Plano, CA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce7428fbc9c89fa9</t>
+          <t>https://www.indeed.com/viewjob?jk=c8d9928392bc7529</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Senior Software Engineer Data Platform</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Panasonic Automotive</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, Spark, Scala, Spark Streaming, Kafka, MLOps, MLflow</t>
+          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11ce688bd126a002</t>
+          <t>https://www.indeed.com/viewjob?jk=e64308de1c862cb5</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend Java</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Kharon</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Databricks, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a18ff10136ae42f8</t>
+          <t>https://www.indeed.com/viewjob?jk=1834ddbeb8ec8bb3</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DevOps &amp; AI Automation Engineer</t>
+          <t>Full Stack Developer (JS/TS, AWS)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Low Associates</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>South Bend, IN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Lambda, API Gateway, IAM, Azure, GCP, Cloud Storage, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6b296a0ce2f382</t>
+          <t>https://www.indeed.com/viewjob?jk=45727b1c951a0e5a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Data Infrastructure</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Sunbit, Inc</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, GCP, HDFS, Hive, Spark, Scala, Kafka, CI/CD</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df9f48d9232b00bf</t>
+          <t>https://www.indeed.com/viewjob?jk=1444a89356fbe315</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - IICS</t>
+          <t>Senior Developer - Level III - 26-04057</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SYSTECH USA</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Cloud Storage, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD</t>
+          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf36b7e279da791</t>
+          <t>https://www.indeed.com/viewjob?jk=43063b055188ce3c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Developer - Level III - 26-04057</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Banner Health</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, ELT</t>
+          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8d9928392bc7529</t>
+          <t>https://www.indeed.com/viewjob?jk=6cc0ba82c4bd25dc</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Data Platform</t>
+          <t>Senior Developer - Level III - 26-04057</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake</t>
+          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e64308de1c862cb5</t>
+          <t>https://www.indeed.com/viewjob?jk=9eeb6502ebf78cc0</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Developer - Level III - 26-04057</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Kharon</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Santa Clarita, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1834ddbeb8ec8bb3</t>
+          <t>https://www.indeed.com/viewjob?jk=473b7754552ef179</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Backend Engineer II</t>
+          <t>Senior Developer - Level III - 26-04057</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>HackerRank Careers</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Lancaster, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae2342b890625b11</t>
+          <t>https://www.indeed.com/viewjob?jk=5e872365f29ac108</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Full Stack Developer (JS/TS, AWS)</t>
+          <t>Sr Business Intelligence Developer - Onsite</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Low Associates</t>
+          <t>Bass Pro Shops</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>South Bend, IN, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,29 +2341,29 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, Azure, GCP, Cloud Storage, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45727b1c951a0e5a</t>
+          <t>https://www.indeed.com/viewjob?jk=ba1611f04cfe11a7</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Machine Learning Engineer (171680)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Sunbit, Inc</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2376,42 +2376,42 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1444a89356fbe315</t>
+          <t>https://www.indeed.com/viewjob?jk=a860d07867e70be2</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Developer - Level III - 26-04057</t>
+          <t>Senior SRE</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, GCP, Scala, DynamoDB, Cassandra, NoSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43063b055188ce3c</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc41b902449ace0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Developer - Level III - 26-04057</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cc0ba82c4bd25dc</t>
+          <t>https://www.indeed.com/viewjob?jk=3088b1f92a7a6242</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Developer - Level III - 26-04057</t>
+          <t>AI Cloud Security and Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Troutman Pepper Locke</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eeb6502ebf78cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=04325b074eb62665</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Developer - Level III - 26-04057</t>
+          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Santa Clarita, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=473b7754552ef179</t>
+          <t>https://www.indeed.com/viewjob?jk=c20056a5b9ffca80</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Developer - Level III - 26-04057</t>
+          <t>Data Engineer (SQL / Spark / Python)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>cloudteam</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Lancaster, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, Oozie, YARN</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e872365f29ac108</t>
+          <t>https://www.indeed.com/viewjob?jk=6ae648cd8fe57362</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr Business Intelligence Developer - Onsite</t>
+          <t>Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Bass Pro Shops</t>
+          <t>Holland &amp; Knight</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Brandon, FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, Airflow, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,59 +2596,59 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba1611f04cfe11a7</t>
+          <t>https://www.indeed.com/viewjob?jk=3abb3ed211255b11</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer (171680)</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a860d07867e70be2</t>
+          <t>https://www.indeed.com/viewjob?jk=766f2f5e9a7201f1</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Cloud Software Engineer 3 - III</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>InterImage</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3088b1f92a7a6242</t>
+          <t>https://www.indeed.com/viewjob?jk=16ddbf61e3ea0b92</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AI Cloud Security and Infrastructure Engineer</t>
+          <t>Cloud Software Engineer 3 - II</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Troutman Pepper Locke</t>
+          <t>InterImage</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04325b074eb62665</t>
+          <t>https://www.indeed.com/viewjob?jk=43bfe7ca1f6eddb7</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
+          <t>Cloud Software Engineer 3 - I</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>InterImage</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
+          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c20056a5b9ffca80</t>
+          <t>https://www.indeed.com/viewjob?jk=2124d09922154cc4</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer (SQL / Spark / Python)</t>
+          <t>GIS Support Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>cloudteam</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, Oozie, YARN</t>
+          <t>AWS, API Gateway, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ae648cd8fe57362</t>
+          <t>https://www.indeed.com/viewjob?jk=e24b40c19089ff90</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>Data Engineer - Dallas, TX</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Holland &amp; Knight</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Brandon, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, Airflow, Git</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3abb3ed211255b11</t>
+          <t>https://www.indeed.com/viewjob?jk=865a46cfbc7cc3f4</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Software Developer Architect (Cloud Services)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
+          <t>AWS, Lambda, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766f2f5e9a7201f1</t>
+          <t>https://www.indeed.com/viewjob?jk=ec8ec9187f270065</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer 3 - III</t>
+          <t>Sr. Software QA Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>InterImage</t>
+          <t>Carlsmed</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16ddbf61e3ea0b92</t>
+          <t>https://www.indeed.com/viewjob?jk=f92907b243e51105</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer 3 - II</t>
+          <t>Data Engineer, Cat Digital Data &amp; AI</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>InterImage</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43bfe7ca1f6eddb7</t>
+          <t>https://www.indeed.com/viewjob?jk=699bf154d150027f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer 3 - I</t>
+          <t>Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>InterImage</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
+          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2124d09922154cc4</t>
+          <t>https://www.indeed.com/viewjob?jk=39b5eeee4ff704ee</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>GIS Support Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Splunk, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e24b40c19089ff90</t>
+          <t>https://www.indeed.com/viewjob?jk=10b635a4480602f9</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer - Dallas, TX</t>
+          <t>SRE Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=865a46cfbc7cc3f4</t>
+          <t>https://www.indeed.com/viewjob?jk=907826ed55a037a8</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer, Cat Digital Data &amp; AI</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Oracle, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,67 +3051,67 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=699bf154d150027f</t>
+          <t>https://www.indeed.com/viewjob?jk=bca63339137d0189</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BillGO, Inc.</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Fort Collins, CO, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, DynamoDB, Star Schema, ELT, Tableau, GitHub Actions</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69713d6be44a4b67</t>
+          <t>https://www.indeed.com/viewjob?jk=deb135bf06a2110e</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer (Full Stack)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39b5eeee4ff704ee</t>
+          <t>https://www.indeed.com/viewjob?jk=2be9ee403cf20f67</t>
         </is>
       </c>
     </row>
@@ -3133,20 +3133,20 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Splunk, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b635a4480602f9</t>
+          <t>https://www.indeed.com/viewjob?jk=156e5a4def2a4a5d</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SRE Architect</t>
+          <t>Senior Analytic Data Engineer (Python/Power BI)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Highmark Health</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Splunk, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, ETL, Power BI</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=907826ed55a037a8</t>
+          <t>https://www.indeed.com/viewjob?jk=100c60fa90e63408</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Sr. Software Engineer II</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Oracle, ETL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Splunk, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bca63339137d0189</t>
+          <t>https://www.indeed.com/viewjob?jk=04a1d1c06680e371</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Core &amp; Main</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deb135bf06a2110e</t>
+          <t>https://www.indeed.com/viewjob?jk=b5e2495e00e0060d</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Devops Engineer - MN</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>RAZR Marketing, Inc.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, PostgreSQL, Docker, Kubernetes, CloudWatch</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2be9ee403cf20f67</t>
+          <t>https://www.indeed.com/viewjob?jk=3375eb3b3d50ba05</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Core &amp; Main</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=156e5a4def2a4a5d</t>
+          <t>https://www.indeed.com/viewjob?jk=b2cdf5f4ac6a6c1a</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Analytic Data Engineer (Python/Power BI)</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Highmark Health</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, ETL, Power BI</t>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=100c60fa90e63408</t>
+          <t>https://www.indeed.com/viewjob?jk=1a31dfca06d884ad</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Splunk, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04a1d1c06680e371</t>
+          <t>https://www.indeed.com/viewjob?jk=f6b1cb632eed3bcb</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer - MN</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>RAZR Marketing, Inc.</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, PostgreSQL, Docker, Kubernetes, CloudWatch</t>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3375eb3b3d50ba05</t>
+          <t>https://www.indeed.com/viewjob?jk=ec090a150db0c5f8</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Core &amp; Main</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2cdf5f4ac6a6c1a</t>
+          <t>https://www.indeed.com/viewjob?jk=3fe79bacd5e58f55</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a31dfca06d884ad</t>
+          <t>https://www.indeed.com/viewjob?jk=f09282ebd98b3570</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6b1cb632eed3bcb</t>
+          <t>https://www.indeed.com/viewjob?jk=fa1d73f24fc01af9</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec090a150db0c5f8</t>
+          <t>https://www.indeed.com/viewjob?jk=7e4150c94fe908c8</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>WILLDAN GROUP</t>
+          <t>Metropolitan Companies</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Wyomissing, PA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, SQL Server, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fe79bacd5e58f55</t>
+          <t>https://www.indeed.com/viewjob?jk=12c03c3bb6ce8c38</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Senior Software Engineer, Experimentation Platform (Backend Services)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>WILLDAN GROUP</t>
+          <t>Paramount Streaming</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, Redshift, RDS, GCP, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,19 +3646,19 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f09282ebd98b3570</t>
+          <t>https://www.indeed.com/viewjob?jk=1f33593f93ffe80a</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Senior Software Engineer, Data Migration &amp; Code Generation</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>WILLDAN GROUP</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, Kafka, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1d73f24fc01af9</t>
+          <t>https://www.indeed.com/viewjob?jk=f20bc83aea1de83b</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Supervisor, Software Engineering</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>WILLDAN GROUP</t>
+          <t>Energy Systems Group</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Newburgh, IN, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e4150c94fe908c8</t>
+          <t>https://www.indeed.com/viewjob?jk=9c197f77bdf171e6</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst/Associate - New York</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Metropolitan Companies</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Wyomissing, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, SQL Server, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12c03c3bb6ce8c38</t>
+          <t>https://www.indeed.com/viewjob?jk=1dd43ffc6d7fda89</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Experimentation Platform (Backend Services)</t>
+          <t>IS Technical Specialist</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Paramount Streaming</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, GCP, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f33593f93ffe80a</t>
+          <t>https://www.indeed.com/viewjob?jk=757269b719268379</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Migration &amp; Code Generation</t>
+          <t>IS Technical Specialist</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD, Kubernetes</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f20bc83aea1de83b</t>
+          <t>https://www.indeed.com/viewjob?jk=609b33430f9df835</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Supervisor, Software Engineering</t>
+          <t>IS Technical Specialist</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Energy Systems Group</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Newburgh, IN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c197f77bdf171e6</t>
+          <t>https://www.indeed.com/viewjob?jk=ef377da6b1a8bbfd</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst/Associate - New York</t>
+          <t>IS Technical Specialist</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dd43ffc6d7fda89</t>
+          <t>https://www.indeed.com/viewjob?jk=6aea6ee79779b03b</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Fairlawn, OH, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=757269b719268379</t>
+          <t>https://www.indeed.com/viewjob?jk=da070db6e9060b88</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=609b33430f9df835</t>
+          <t>https://www.indeed.com/viewjob?jk=63d188ef103369c5</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>IS Technical Specialist</t>
+          <t>Database Automation Developer (contract)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, MongoDB, CI/CD, Terraform, AKS, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef377da6b1a8bbfd</t>
+          <t>https://www.indeed.com/viewjob?jk=78a015d8ecbb3c7f</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>IS Technical Specialist</t>
+          <t>C++ Software Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>First Orion</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>North Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
+          <t>AWS, Scala, Oracle, MySQL, NoSQL, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4030,146 +4030,6 @@
         </is>
       </c>
       <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6aea6ee79779b03b</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>IS Technical Specialist</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Huntington Bank</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Fairlawn, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=da070db6e9060b88</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>IS Technical Specialist</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Huntington Bank</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=63d188ef103369c5</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Database Automation Developer (contract)</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>BNY</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, MongoDB, CI/CD, Terraform, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=78a015d8ecbb3c7f</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>C++ Software Engineer</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>First Orion</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>North Little Rock, AR, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, Scala, Oracle, MySQL, NoSQL, CI/CD, Docker, Kubernetes, Git, Python</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=8393d3f10d4fb672</t>
         </is>

--- a/results/job_matches_2026-04-16.xlsx
+++ b/results/job_matches_2026-04-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Analytics Architect</t>
+          <t>Data Architect/Modeler</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Infoverity</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dublin, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca5a94e3ea76c9da</t>
+          <t>https://www.indeed.com/viewjob?jk=e10ec33698957c81</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Architect, Senior</t>
+          <t>Analytics Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Intermountain Health</t>
+          <t>Infoverity</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Murray, UT, US USA</t>
+          <t>Dublin, OH, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, S3, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8184ec5fc529fc27</t>
+          <t>https://www.indeed.com/viewjob?jk=ca5a94e3ea76c9da</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS Glue</t>
+          <t>Data Architect, Senior</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Intermountain Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Murray, UT, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, SQS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f1496d3a0b45451</t>
+          <t>https://www.indeed.com/viewjob?jk=8184ec5fc529fc27</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Kafka Engineer</t>
+          <t>Software Engineer III - AWS Glue</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TECHNOLOGENT</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, Oracle</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SQS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51b24f7efaba6116</t>
+          <t>https://www.indeed.com/viewjob?jk=5f1496d3a0b45451</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Application Developer, Portland Oregon</t>
+          <t>Senior Infrastructure Kafka Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Portland General Electric</t>
+          <t>TECHNOLOGENT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, Oracle</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9f186e739ef98be</t>
+          <t>https://www.indeed.com/viewjob?jk=51b24f7efaba6116</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Application Developer, Portland Oregon</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HelioCampus</t>
+          <t>Portland General Electric</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=333fbc294a529a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=f9f186e739ef98be</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer/Data Scientist</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>HelioCampus</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a711c2fcb36b6cf</t>
+          <t>https://www.indeed.com/viewjob?jk=333fbc294a529a0f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (ON-SITE)</t>
+          <t>Data Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Equinox</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, Snowflake, DynamoDB</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=038b96d69cecd888</t>
+          <t>https://www.indeed.com/viewjob?jk=8a711c2fcb36b6cf</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Databricks Data Analyst</t>
+          <t>Sr. Data Engineer (ON-SITE)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>Equinox</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, Snowflake, DynamoDB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce89a36f70a3941b</t>
+          <t>https://www.indeed.com/viewjob?jk=038b96d69cecd888</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I</t>
+          <t>Databricks Data Analyst</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LTK</t>
+          <t>Lincoln Financial Group</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,69 +871,69 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Scala, PostgreSQL, MySQL, DynamoDB, Cassandra, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77a9388986ca4483</t>
+          <t>https://www.indeed.com/viewjob?jk=ce89a36f70a3941b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Software Engineer I</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>LTK</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, ECS, RDS, Scala, PostgreSQL, MySQL, DynamoDB, Cassandra, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb699a2e3bdbb440</t>
+          <t>https://www.indeed.com/viewjob?jk=77a9388986ca4483</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Warehouse Analyst Seniors: Cloud Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, ETL, CI/CD</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d87aa04a7733264b</t>
+          <t>https://www.indeed.com/viewjob?jk=cb699a2e3bdbb440</t>
         </is>
       </c>
     </row>
@@ -1063,60 +1063,60 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Associate IT Officer, Data and Information Management (Associate Data Engineer)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>World Bank Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c4955f2e41966ef</t>
+          <t>https://www.indeed.com/viewjob?jk=7a40cff6b5df03cd</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Data Engineer- OrderlyMeds</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>OrderlyMeds</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Azure, GCP, Scala, Kafka</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcd17ae9e035b9a9</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb2a73a0846955d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Associate IT Officer, Data and Information Management (Associate Data Engineer)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>World Bank Group</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Databricks, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a40cff6b5df03cd</t>
+          <t>https://www.indeed.com/viewjob?jk=aa4d88005315e7ba</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer- OrderlyMeds</t>
+          <t>Senior Analytics Engineer - Power BI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>OrderlyMeds</t>
+          <t>Broadview Federal Credit Union</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Databricks Lakehouse, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb2a73a0846955d</t>
+          <t>https://www.indeed.com/viewjob?jk=ddee7a1fd9164fde</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Architecture Intern</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Smart Data Solutions</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Databricks, Scala, DynamoDB</t>
+          <t>AWS, S3, IAM, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa4d88005315e7ba</t>
+          <t>https://www.indeed.com/viewjob?jk=d67805e12d384da2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer - Power BI</t>
+          <t>Senior, Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Broadview Federal Credit Union</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Databricks Lakehouse, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Cassandra</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddee7a1fd9164fde</t>
+          <t>https://www.indeed.com/viewjob?jk=3fcd1c4e67959eea</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Developer</t>
+          <t>AI Intern</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Olson Kundig</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, GCP, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, dbt, MLflow</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,59 +1301,59 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d831e0d8e2c5553f</t>
+          <t>https://www.indeed.com/viewjob?jk=7bea47ac5f13bd1f</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Architecture Intern</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Smart Data Solutions</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d67805e12d384da2</t>
+          <t>https://www.indeed.com/viewjob?jk=93144249a4967543</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior, Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Atlanta, KS, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Cassandra</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Azure Cosmos DB, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fcd1c4e67959eea</t>
+          <t>https://www.indeed.com/viewjob?jk=e9a02726d78410b5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AI Intern</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Energy Services Group</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, dbt, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bea47ac5f13bd1f</t>
+          <t>https://www.indeed.com/viewjob?jk=6918de34da34b82a</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93144249a4967543</t>
+          <t>https://www.indeed.com/viewjob?jk=b2a1afc987319b9a</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Research Engineer II</t>
+          <t>Site Reliability Engineer (Cloud Enablement)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University</t>
+          <t>Flexera</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bryan, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, ETL, Power BI, Tableau</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09b3207da19db4ee</t>
+          <t>https://www.indeed.com/viewjob?jk=72d1842ef3999b1d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Development Engineer - Cloud Dev</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>Transmedics</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Atlanta, KS, US USA</t>
+          <t>Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Azure Cosmos DB, Data Modeling, ELT</t>
+          <t>AWS, Lambda, Kinesis, Redshift, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9a02726d78410b5</t>
+          <t>https://www.indeed.com/viewjob?jk=2f2220b49620882d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Senior Enterprise Application Developer (Full Stack)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Energy Services Group</t>
+          <t>Exponent</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, ECS, RDS, Azure, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6918de34da34b82a</t>
+          <t>https://www.indeed.com/viewjob?jk=57406ee750d6ac9c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Data Engineer - Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, Databricks, GCP, Spark, Scala, Kafka, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2a1afc987319b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=48617c6692425cb2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (Cloud Enablement)</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Flexera</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72d1842ef3999b1d</t>
+          <t>https://www.indeed.com/viewjob?jk=a5acecf0e4305790</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Enterprise Application Developer (Full Stack)</t>
+          <t>AI/ML Engineering Intern (Summer 2026)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Exponent</t>
+          <t>Poshmark</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, ECS, RDS, Azure, Scala, SQL Server</t>
+          <t>Redshift, Databricks, Spark, Scala, Kafka, MongoDB, MLflow, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,67 +1651,67 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57406ee750d6ac9c</t>
+          <t>https://www.indeed.com/viewjob?jk=7fd3431b51acd4b5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Warehouse Architect</t>
+          <t>Cloudera Public Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Plano, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Databricks, GCP, Spark, Scala, Kafka, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48617c6692425cb2</t>
+          <t>https://www.indeed.com/viewjob?jk=ce7428fbc9c89fa9</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Panasonic Automotive</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Vertex AI, Spark, Scala, Spark Streaming, Kafka, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5acecf0e4305790</t>
+          <t>https://www.indeed.com/viewjob?jk=11ce688bd126a002</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AI/ML Engineering Intern (Summer 2026)</t>
+          <t>DevOps &amp; AI Automation Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Poshmark</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, Scala, Kafka, MongoDB, MLflow, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,84 +1756,84 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fd3431b51acd4b5</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6b296a0ce2f382</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Cloudera Public Cloud Platform Engineer</t>
+          <t>Senior Data Engineer - IICS</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>SYSTECH USA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Plano, CA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
+          <t>AWS, Redshift, Cloud Storage, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce7428fbc9c89fa9</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf36b7e279da791</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Panasonic Automotive</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, Spark, Scala, Spark Streaming, Kafka, MLOps, MLflow</t>
+          <t>AWS, Glue, S3, RDS, Scala, Kafka, Snowflake, SQL Server, ETL, Tableau</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11ce688bd126a002</t>
+          <t>https://www.indeed.com/viewjob?jk=782f670b324716aa</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend Java</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1843,50 +1843,50 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, S3, RDS, Scala, Kafka, Snowflake, SQL Server, ETL, Tableau</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a18ff10136ae42f8</t>
+          <t>https://www.indeed.com/viewjob?jk=65a4b202ac924d0b</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DevOps &amp; AI Automation Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Kharon</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Databricks, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6b296a0ce2f382</t>
+          <t>https://www.indeed.com/viewjob?jk=757ea9686f738a0e</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Data Infrastructure</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Kharon</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, GCP, HDFS, Hive, Spark, Scala, Kafka, CI/CD</t>
+          <t>AWS, S3, RDS, Databricks, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df9f48d9232b00bf</t>
+          <t>https://www.indeed.com/viewjob?jk=1834ddbeb8ec8bb3</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - IICS</t>
+          <t>Senior Full Stack Developer, Smart Factory Solutions</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SYSTECH USA</t>
+          <t>Magna International</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Cloud Storage, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, ECS, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf36b7e279da791</t>
+          <t>https://www.indeed.com/viewjob?jk=a7d8d9f6032e5b6f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Developer (JS/TS, AWS)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Banner Health</t>
+          <t>Low Associates</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>South Bend, IN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Lambda, API Gateway, IAM, Azure, GCP, Cloud Storage, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8d9928392bc7529</t>
+          <t>https://www.indeed.com/viewjob?jk=45727b1c951a0e5a</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Data Platform</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sunbit, Inc</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e64308de1c862cb5</t>
+          <t>https://www.indeed.com/viewjob?jk=1444a89356fbe315</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Developer - Level III - 26-04057</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Kharon</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1834ddbeb8ec8bb3</t>
+          <t>https://www.indeed.com/viewjob?jk=43063b055188ce3c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Full Stack Developer (JS/TS, AWS)</t>
+          <t>Senior Developer - Level III - 26-04057</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Low Associates</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>South Bend, IN, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, Azure, GCP, Cloud Storage, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45727b1c951a0e5a</t>
+          <t>https://www.indeed.com/viewjob?jk=6cc0ba82c4bd25dc</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Developer - Level III - 26-04057</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Sunbit, Inc</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
+          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1444a89356fbe315</t>
+          <t>https://www.indeed.com/viewjob?jk=9eeb6502ebf78cc0</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Santa Clarita, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43063b055188ce3c</t>
+          <t>https://www.indeed.com/viewjob?jk=473b7754552ef179</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Lancaster, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cc0ba82c4bd25dc</t>
+          <t>https://www.indeed.com/viewjob?jk=5e872365f29ac108</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Developer - Level III - 26-04057</t>
+          <t>Sr Business Intelligence Developer - Onsite</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Bass Pro Shops</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eeb6502ebf78cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=ba1611f04cfe11a7</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Developer - Level III - 26-04057</t>
+          <t>Machine Learning Engineer (171680)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Santa Clarita, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,42 +2271,42 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=473b7754552ef179</t>
+          <t>https://www.indeed.com/viewjob?jk=a860d07867e70be2</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Developer - Level III - 26-04057</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Lancaster, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e872365f29ac108</t>
+          <t>https://www.indeed.com/viewjob?jk=523330c74b38a27b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr Business Intelligence Developer - Onsite</t>
+          <t>Senior SRE</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Bass Pro Shops</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, GCP, Scala, DynamoDB, Cassandra, NoSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,59 +2351,59 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba1611f04cfe11a7</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc41b902449ace0</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer (171680)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a860d07867e70be2</t>
+          <t>https://www.indeed.com/viewjob?jk=7beef8ad4f571f7a</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior SRE</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, DynamoDB, Cassandra, NoSQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc41b902449ace0</t>
+          <t>https://www.indeed.com/viewjob?jk=3088b1f92a7a6242</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>AI Cloud Security and Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Troutman Pepper Locke</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3088b1f92a7a6242</t>
+          <t>https://www.indeed.com/viewjob?jk=04325b074eb62665</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AI Cloud Security and Infrastructure Engineer</t>
+          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Troutman Pepper Locke</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04325b074eb62665</t>
+          <t>https://www.indeed.com/viewjob?jk=c20056a5b9ffca80</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
+          <t>Data Engineer (SQL / Spark / Python)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>cloudteam</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, Oozie, YARN</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c20056a5b9ffca80</t>
+          <t>https://www.indeed.com/viewjob?jk=6ae648cd8fe57362</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer (SQL / Spark / Python)</t>
+          <t>Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>cloudteam</t>
+          <t>Holland &amp; Knight</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Brandon, FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, Oozie, YARN</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, Airflow, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ae648cd8fe57362</t>
+          <t>https://www.indeed.com/viewjob?jk=3abb3ed211255b11</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Holland &amp; Knight</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Brandon, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3abb3ed211255b11</t>
+          <t>https://www.indeed.com/viewjob?jk=766f2f5e9a7201f1</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Cloud Software Engineer 3 - III</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>InterImage</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,14 +2631,14 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766f2f5e9a7201f1</t>
+          <t>https://www.indeed.com/viewjob?jk=16ddbf61e3ea0b92</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer 3 - III</t>
+          <t>Cloud Software Engineer 3 - II</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2666,14 +2666,14 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16ddbf61e3ea0b92</t>
+          <t>https://www.indeed.com/viewjob?jk=43bfe7ca1f6eddb7</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer 3 - II</t>
+          <t>Cloud Software Engineer 3 - I</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43bfe7ca1f6eddb7</t>
+          <t>https://www.indeed.com/viewjob?jk=2124d09922154cc4</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer 3 - I</t>
+          <t>GIS Support Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>InterImage</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
+          <t>AWS, API Gateway, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2124d09922154cc4</t>
+          <t>https://www.indeed.com/viewjob?jk=e24b40c19089ff90</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>GIS Support Engineer</t>
+          <t>Senior Performance Test Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>TIAG</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, IAM, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e24b40c19089ff90</t>
+          <t>https://www.indeed.com/viewjob?jk=82eb3dabcdfd111c</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer - Dallas, TX</t>
+          <t>Software Developer Architect (Cloud Services)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=865a46cfbc7cc3f4</t>
+          <t>https://www.indeed.com/viewjob?jk=ec8ec9187f270065</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Developer Architect (Cloud Services)</t>
+          <t>Sr. Software QA Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Carlsmed</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec8ec9187f270065</t>
+          <t>https://www.indeed.com/viewjob?jk=f92907b243e51105</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr. Software QA Engineer</t>
+          <t>Data Engineer, Cat Digital Data &amp; AI</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Carlsmed</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,14 +2876,14 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f92907b243e51105</t>
+          <t>https://www.indeed.com/viewjob?jk=699bf154d150027f</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer, Cat Digital Data &amp; AI</t>
+          <t>Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=699bf154d150027f</t>
+          <t>https://www.indeed.com/viewjob?jk=39b5eeee4ff704ee</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer (Full Stack)</t>
+          <t>SRE Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39b5eeee4ff704ee</t>
+          <t>https://www.indeed.com/viewjob?jk=907826ed55a037a8</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Splunk, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Oracle, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b635a4480602f9</t>
+          <t>https://www.indeed.com/viewjob?jk=bca63339137d0189</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SRE Architect</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Splunk, CI/CD, Terraform</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=907826ed55a037a8</t>
+          <t>https://www.indeed.com/viewjob?jk=deb135bf06a2110e</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Oracle, ETL, CI/CD, Git</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bca63339137d0189</t>
+          <t>https://www.indeed.com/viewjob?jk=2be9ee403cf20f67</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deb135bf06a2110e</t>
+          <t>https://www.indeed.com/viewjob?jk=156e5a4def2a4a5d</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Analytic Data Engineer (Python/Power BI)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Highmark Health</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, ETL, Power BI</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2be9ee403cf20f67</t>
+          <t>https://www.indeed.com/viewjob?jk=100c60fa90e63408</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Software Engineer II</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Splunk, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=156e5a4def2a4a5d</t>
+          <t>https://www.indeed.com/viewjob?jk=04a1d1c06680e371</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Analytic Data Engineer (Python/Power BI)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Highmark Health</t>
+          <t>Core &amp; Main</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, ETL, Power BI</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=100c60fa90e63408</t>
+          <t>https://www.indeed.com/viewjob?jk=b5e2495e00e0060d</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II</t>
+          <t>Senior Devops Engineer - MN</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>RAZR Marketing, Inc.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Splunk, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, PostgreSQL, Docker, Kubernetes, CloudWatch</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04a1d1c06680e371</t>
+          <t>https://www.indeed.com/viewjob?jk=3375eb3b3d50ba05</t>
         </is>
       </c>
     </row>
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5e2495e00e0060d</t>
+          <t>https://www.indeed.com/viewjob?jk=b2cdf5f4ac6a6c1a</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer - MN</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>RAZR Marketing, Inc.</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, PostgreSQL, Docker, Kubernetes, CloudWatch</t>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3375eb3b3d50ba05</t>
+          <t>https://www.indeed.com/viewjob?jk=1a31dfca06d884ad</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Core &amp; Main</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2cdf5f4ac6a6c1a</t>
+          <t>https://www.indeed.com/viewjob?jk=f6b1cb632eed3bcb</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a31dfca06d884ad</t>
+          <t>https://www.indeed.com/viewjob?jk=ec090a150db0c5f8</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6b1cb632eed3bcb</t>
+          <t>https://www.indeed.com/viewjob?jk=3fe79bacd5e58f55</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec090a150db0c5f8</t>
+          <t>https://www.indeed.com/viewjob?jk=f09282ebd98b3570</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fe79bacd5e58f55</t>
+          <t>https://www.indeed.com/viewjob?jk=fa1d73f24fc01af9</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f09282ebd98b3570</t>
+          <t>https://www.indeed.com/viewjob?jk=7e4150c94fe908c8</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>WILLDAN GROUP</t>
+          <t>Metropolitan Companies</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wyomissing, PA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, SQL Server, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1d73f24fc01af9</t>
+          <t>https://www.indeed.com/viewjob?jk=12c03c3bb6ce8c38</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Senior Software Engineer, Experimentation Platform (Backend Services)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>WILLDAN GROUP</t>
+          <t>Paramount Streaming</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, Redshift, RDS, GCP, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e4150c94fe908c8</t>
+          <t>https://www.indeed.com/viewjob?jk=1f33593f93ffe80a</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Metropolitan Companies</t>
+          <t>CardioOne</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Wyomissing, PA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, SQL Server, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12c03c3bb6ce8c38</t>
+          <t>https://www.indeed.com/viewjob?jk=7b44f024bbd36d11</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Experimentation Platform (Backend Services)</t>
+          <t>Supervisor, Software Engineering</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Paramount Streaming</t>
+          <t>Energy Systems Group</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Newburgh, IN, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, GCP, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f33593f93ffe80a</t>
+          <t>https://www.indeed.com/viewjob?jk=9c197f77bdf171e6</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Migration &amp; Code Generation</t>
+          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst/Associate - New York</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD, Kubernetes</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f20bc83aea1de83b</t>
+          <t>https://www.indeed.com/viewjob?jk=1dd43ffc6d7fda89</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Supervisor, Software Engineering</t>
+          <t>IS Technical Specialist</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Energy Systems Group</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Newburgh, IN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c197f77bdf171e6</t>
+          <t>https://www.indeed.com/viewjob?jk=757269b719268379</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst/Associate - New York</t>
+          <t>IS Technical Specialist</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dd43ffc6d7fda89</t>
+          <t>https://www.indeed.com/viewjob?jk=609b33430f9df835</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=757269b719268379</t>
+          <t>https://www.indeed.com/viewjob?jk=ef377da6b1a8bbfd</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=609b33430f9df835</t>
+          <t>https://www.indeed.com/viewjob?jk=6aea6ee79779b03b</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Fairlawn, OH, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef377da6b1a8bbfd</t>
+          <t>https://www.indeed.com/viewjob?jk=da070db6e9060b88</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aea6ee79779b03b</t>
+          <t>https://www.indeed.com/viewjob?jk=63d188ef103369c5</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>IS Technical Specialist</t>
+          <t>Database Automation Developer (contract)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Fairlawn, OH, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, MongoDB, CI/CD, Terraform, AKS, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,112 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da070db6e9060b88</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>IS Technical Specialist</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Huntington Bank</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=63d188ef103369c5</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Database Automation Developer (contract)</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>BNY</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, MongoDB, CI/CD, Terraform, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=78a015d8ecbb3c7f</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>C++ Software Engineer</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>First Orion</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>North Little Rock, AR, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, Scala, Oracle, MySQL, NoSQL, CI/CD, Docker, Kubernetes, Git, Python</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8393d3f10d4fb672</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-16.xlsx
+++ b/results/job_matches_2026-04-16.xlsx
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS Glue</t>
+          <t>Senior Infrastructure Kafka Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>TECHNOLOGENT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, SQS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, Oracle</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f1496d3a0b45451</t>
+          <t>https://www.indeed.com/viewjob?jk=51b24f7efaba6116</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Kafka Engineer</t>
+          <t>Application Developer, Portland Oregon</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TECHNOLOGENT</t>
+          <t>Portland General Electric</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, Oracle</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51b24f7efaba6116</t>
+          <t>https://www.indeed.com/viewjob?jk=f9f186e739ef98be</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Application Developer, Portland Oregon</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Portland General Electric</t>
+          <t>HelioCampus</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9f186e739ef98be</t>
+          <t>https://www.indeed.com/viewjob?jk=333fbc294a529a0f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HelioCampus</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=333fbc294a529a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=8a711c2fcb36b6cf</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer/Data Scientist</t>
+          <t>Sr. Data Engineer (ON-SITE)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Equinox</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, Snowflake, DynamoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a711c2fcb36b6cf</t>
+          <t>https://www.indeed.com/viewjob?jk=038b96d69cecd888</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (ON-SITE)</t>
+          <t>Databricks Data Analyst</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Equinox</t>
+          <t>Lincoln Financial Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, Snowflake, DynamoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=038b96d69cecd888</t>
+          <t>https://www.indeed.com/viewjob?jk=ce89a36f70a3941b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Databricks Data Analyst</t>
+          <t>Sr Software Engineer I</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>LTK</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,104 +871,104 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, Lambda, ECS, RDS, Scala, PostgreSQL, MySQL, DynamoDB, Cassandra, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce89a36f70a3941b</t>
+          <t>https://www.indeed.com/viewjob?jk=77a9388986ca4483</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LTK</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Scala, PostgreSQL, MySQL, DynamoDB, Cassandra, CI/CD</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77a9388986ca4483</t>
+          <t>https://www.indeed.com/viewjob?jk=cb699a2e3bdbb440</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>BLOC Resources, LLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>Azure, Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb699a2e3bdbb440</t>
+          <t>https://www.indeed.com/viewjob?jk=d9e13379e16ee4b4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Ad Ops Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ignite Insurance Systems</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=560d14506d8aa36b</t>
+          <t>https://www.indeed.com/viewjob?jk=f14f238cb8b8c5f1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Associate IT Officer, Data and Information Management (Associate Data Engineer)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BLOC Resources, LLC</t>
+          <t>World Bank Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,19 +1021,19 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9e13379e16ee4b4</t>
+          <t>https://www.indeed.com/viewjob?jk=7a40cff6b5df03cd</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Ad Ops Engineer</t>
+          <t>Data Engineer- OrderlyMeds</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>OrderlyMeds</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1042,11 +1042,11 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f14f238cb8b8c5f1</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb2a73a0846955d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Associate IT Officer, Data and Information Management (Associate Data Engineer)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>World Bank Group</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Databricks, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a40cff6b5df03cd</t>
+          <t>https://www.indeed.com/viewjob?jk=aa4d88005315e7ba</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer- OrderlyMeds</t>
+          <t>Java Software Developer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>OrderlyMeds</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb2a73a0846955d</t>
+          <t>https://www.indeed.com/viewjob?jk=4c2cee659fe1d0db</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Analytics Engineer - Power BI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Broadview Federal Credit Union</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Databricks, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Databricks Lakehouse, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa4d88005315e7ba</t>
+          <t>https://www.indeed.com/viewjob?jk=ddee7a1fd9164fde</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer - Power BI</t>
+          <t>Data Architecture Intern</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Broadview Federal Credit Union</t>
+          <t>Smart Data Solutions</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Databricks Lakehouse, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, S3, IAM, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddee7a1fd9164fde</t>
+          <t>https://www.indeed.com/viewjob?jk=d67805e12d384da2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Architecture Intern</t>
+          <t>Senior, Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Smart Data Solutions</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Cassandra</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d67805e12d384da2</t>
+          <t>https://www.indeed.com/viewjob?jk=3fcd1c4e67959eea</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior, Software Engineer</t>
+          <t>AI Intern</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Cassandra</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, dbt, MLflow</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fcd1c4e67959eea</t>
+          <t>https://www.indeed.com/viewjob?jk=7bea47ac5f13bd1f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI Intern</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, dbt, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bea47ac5f13bd1f</t>
+          <t>https://www.indeed.com/viewjob?jk=93144249a4967543</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Atlanta, KS, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Azure Cosmos DB, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93144249a4967543</t>
+          <t>https://www.indeed.com/viewjob?jk=e9a02726d78410b5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>Energy Services Group</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, KS, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Azure Cosmos DB, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9a02726d78410b5</t>
+          <t>https://www.indeed.com/viewjob?jk=6918de34da34b82a</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Energy Services Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6918de34da34b82a</t>
+          <t>https://www.indeed.com/viewjob?jk=b2a1afc987319b9a</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Site Reliability Engineer (Cloud Enablement)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Flexera</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2a1afc987319b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=72d1842ef3999b1d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (Cloud Enablement)</t>
+          <t>Senior Software Development Engineer - Cloud Dev</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Flexera</t>
+          <t>Transmedics</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Lambda, Kinesis, Redshift, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72d1842ef3999b1d</t>
+          <t>https://www.indeed.com/viewjob?jk=2f2220b49620882d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - Cloud Dev</t>
+          <t>Senior Enterprise Application Developer (Full Stack)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Transmedics</t>
+          <t>Exponent</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Andover, MA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, ECS, RDS, Azure, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2220b49620882d</t>
+          <t>https://www.indeed.com/viewjob?jk=57406ee750d6ac9c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Enterprise Application Developer (Full Stack)</t>
+          <t>Data Engineer - Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Exponent</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, ECS, RDS, Azure, Scala, SQL Server</t>
+          <t>RDS, Databricks, GCP, Spark, Scala, Kafka, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57406ee750d6ac9c</t>
+          <t>https://www.indeed.com/viewjob?jk=48617c6692425cb2</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Warehouse Architect</t>
+          <t>Senior Enterprise Application Developer (Full Stack)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>Exponent</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Databricks, GCP, Spark, Scala, Kafka, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, ECS, RDS, Azure, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48617c6692425cb2</t>
+          <t>https://www.indeed.com/viewjob?jk=acf79124967bf4c3</t>
         </is>
       </c>
     </row>
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=757ea9686f738a0e</t>
+          <t>https://www.indeed.com/viewjob?jk=1834ddbeb8ec8bb3</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Full Stack Developer, Smart Factory Solutions</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Kharon</t>
+          <t>Magna International</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, S3, ECS, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1834ddbeb8ec8bb3</t>
+          <t>https://www.indeed.com/viewjob?jk=a7d8d9f6032e5b6f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer, Smart Factory Solutions</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Magna International</t>
+          <t>Sunbit, Inc</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7d8d9f6032e5b6f</t>
+          <t>https://www.indeed.com/viewjob?jk=1444a89356fbe315</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Full Stack Developer (JS/TS, AWS)</t>
+          <t>Web Application Architect 3</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Low Associates</t>
+          <t>Bloomberg Industry Group</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>South Bend, IN, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, Azure, GCP, Cloud Storage, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45727b1c951a0e5a</t>
+          <t>https://www.indeed.com/viewjob?jk=7846d03774f71aa5</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Full Stack Developer (JS/TS, AWS)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Sunbit, Inc</t>
+          <t>Low Associates</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>South Bend, IN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,17 +2026,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
+          <t>AWS, Lambda, API Gateway, IAM, Azure, GCP, Cloud Storage, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1444a89356fbe315</t>
+          <t>https://www.indeed.com/viewjob?jk=45727b1c951a0e5a</t>
         </is>
       </c>
     </row>
@@ -2813,17 +2813,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Software QA Engineer</t>
+          <t>SRE Architect</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Carlsmed</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f92907b243e51105</t>
+          <t>https://www.indeed.com/viewjob?jk=907826ed55a037a8</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer, Cat Digital Data &amp; AI</t>
+          <t>Sr. Software QA Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Carlsmed</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,14 +2876,14 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=699bf154d150027f</t>
+          <t>https://www.indeed.com/viewjob?jk=f92907b243e51105</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer (Full Stack)</t>
+          <t>Data Engineer, Cat Digital Data &amp; AI</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39b5eeee4ff704ee</t>
+          <t>https://www.indeed.com/viewjob?jk=699bf154d150027f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SRE Architect</t>
+          <t>Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Splunk, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=907826ed55a037a8</t>
+          <t>https://www.indeed.com/viewjob?jk=39b5eeee4ff704ee</t>
         </is>
       </c>
     </row>
@@ -3583,17 +3583,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst/Associate - New York</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CardioOne</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,17 +3601,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b44f024bbd36d11</t>
+          <t>https://www.indeed.com/viewjob?jk=1dd43ffc6d7fda89</t>
         </is>
       </c>
     </row>
@@ -3653,17 +3653,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst/Associate - New York</t>
+          <t>IS Technical Specialist</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dd43ffc6d7fda89</t>
+          <t>https://www.indeed.com/viewjob?jk=757269b719268379</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=757269b719268379</t>
+          <t>https://www.indeed.com/viewjob?jk=609b33430f9df835</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=609b33430f9df835</t>
+          <t>https://www.indeed.com/viewjob?jk=ef377da6b1a8bbfd</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef377da6b1a8bbfd</t>
+          <t>https://www.indeed.com/viewjob?jk=6aea6ee79779b03b</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Fairlawn, OH, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aea6ee79779b03b</t>
+          <t>https://www.indeed.com/viewjob?jk=da070db6e9060b88</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Fairlawn, OH, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da070db6e9060b88</t>
+          <t>https://www.indeed.com/viewjob?jk=63d188ef103369c5</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>IS Technical Specialist</t>
+          <t>Database Automation Developer (contract)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, MongoDB, CI/CD, Terraform, AKS, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63d188ef103369c5</t>
+          <t>https://www.indeed.com/viewjob?jk=78a015d8ecbb3c7f</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Database Automation Developer (contract)</t>
+          <t>Software Engineer I - Full Stack</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,17 +3916,17 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, MongoDB, CI/CD, Terraform, AKS, Git</t>
+          <t>AWS, YARN, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78a015d8ecbb3c7f</t>
+          <t>https://www.indeed.com/viewjob?jk=e317b1b40c2e7beb</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-16.xlsx
+++ b/results/job_matches_2026-04-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,12 +503,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AWS Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Vertical Relevance</t>
+          <t>Nexnovels</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -517,11 +517,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=664db57e743f0c66</t>
+          <t>https://www.indeed.com/viewjob?jk=fe02b0827629874b</t>
         </is>
       </c>
     </row>
@@ -608,52 +608,52 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Architect, Senior</t>
+          <t>Senior ML Engineer - Agentic AI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Intermountain Health</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Murray, UT, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8184ec5fc529fc27</t>
+          <t>https://www.indeed.com/viewjob?jk=0ee08a694c71ee91</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Kafka Engineer</t>
+          <t>Application Developer, Portland Oregon</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TECHNOLOGENT</t>
+          <t>Portland General Electric</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, Oracle</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51b24f7efaba6116</t>
+          <t>https://www.indeed.com/viewjob?jk=f9f186e739ef98be</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Application Developer, Portland Oregon</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Portland General Electric</t>
+          <t>HelioCampus</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9f186e739ef98be</t>
+          <t>https://www.indeed.com/viewjob?jk=333fbc294a529a0f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HelioCampus</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=333fbc294a529a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=8a711c2fcb36b6cf</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer/Data Scientist</t>
+          <t>Sr. Data Engineer (ON-SITE)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Equinox</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, Snowflake, DynamoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a711c2fcb36b6cf</t>
+          <t>https://www.indeed.com/viewjob?jk=038b96d69cecd888</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (ON-SITE)</t>
+          <t>Databricks Data Analyst</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Equinox</t>
+          <t>Lincoln Financial Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,139 +801,139 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, Snowflake, DynamoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=038b96d69cecd888</t>
+          <t>https://www.indeed.com/viewjob?jk=ce89a36f70a3941b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Databricks Data Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce89a36f70a3941b</t>
+          <t>https://www.indeed.com/viewjob?jk=cb699a2e3bdbb440</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I</t>
+          <t>Sr Cloud Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LTK</t>
+          <t>Federal Reserve Bank of St. Louis</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Scala, PostgreSQL, MySQL, DynamoDB, Cassandra, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77a9388986ca4483</t>
+          <t>https://www.indeed.com/viewjob?jk=af192f5dcbf84698</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>BLOC Resources, LLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>Azure, Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb699a2e3bdbb440</t>
+          <t>https://www.indeed.com/viewjob?jk=d9e13379e16ee4b4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Senior Ad Ops Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BLOC Resources, LLC</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9e13379e16ee4b4</t>
+          <t>https://www.indeed.com/viewjob?jk=f14f238cb8b8c5f1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Ad Ops Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,17 +976,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f14f238cb8b8c5f1</t>
+          <t>https://www.indeed.com/viewjob?jk=fe1513252d7f11af</t>
         </is>
       </c>
     </row>
@@ -1098,25 +1098,25 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Java Software Developer</t>
+          <t>Senior, Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Cassandra</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,94 +1126,94 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c2cee659fe1d0db</t>
+          <t>https://www.indeed.com/viewjob?jk=3fcd1c4e67959eea</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer - Power BI</t>
+          <t>AI Intern</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Broadview Federal Credit Union</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Databricks Lakehouse, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, dbt, MLflow</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddee7a1fd9164fde</t>
+          <t>https://www.indeed.com/viewjob?jk=7bea47ac5f13bd1f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Architecture Intern</t>
+          <t>Software Engineer III – Cloud Platform Engineering - Python / AWS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Smart Data Solutions</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, EMR, S3, ECS, RDS, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d67805e12d384da2</t>
+          <t>https://www.indeed.com/viewjob?jk=bb199efc831c0dc4</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior, Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Atlanta, KS, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Cassandra</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Azure Cosmos DB, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fcd1c4e67959eea</t>
+          <t>https://www.indeed.com/viewjob?jk=e9a02726d78410b5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI Intern</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Energy Services Group</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, dbt, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bea47ac5f13bd1f</t>
+          <t>https://www.indeed.com/viewjob?jk=6918de34da34b82a</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93144249a4967543</t>
+          <t>https://www.indeed.com/viewjob?jk=b2a1afc987319b9a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Site Reliability Engineer (Cloud Enablement)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>Flexera</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlanta, KS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Azure Cosmos DB, Data Modeling, ELT</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9a02726d78410b5</t>
+          <t>https://www.indeed.com/viewjob?jk=72d1842ef3999b1d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Energy Services Group</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6918de34da34b82a</t>
+          <t>https://www.indeed.com/viewjob?jk=a5acecf0e4305790</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Data Engineer - Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, Databricks, GCP, Spark, Scala, Kafka, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2a1afc987319b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=48617c6692425cb2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (Cloud Enablement)</t>
+          <t>AI/ML Engineering Intern (Summer 2026)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Flexera</t>
+          <t>Poshmark</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>Redshift, Databricks, Spark, Scala, Kafka, MongoDB, MLflow, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,67 +1441,67 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72d1842ef3999b1d</t>
+          <t>https://www.indeed.com/viewjob?jk=7fd3431b51acd4b5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - Cloud Dev</t>
+          <t>Cloudera Public Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Transmedics</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Andover, MA, US USA</t>
+          <t>Plano, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2220b49620882d</t>
+          <t>https://www.indeed.com/viewjob?jk=ce7428fbc9c89fa9</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Enterprise Application Developer (Full Stack)</t>
+          <t>DevOps &amp; AI Automation Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Exponent</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, ECS, RDS, Azure, Scala, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57406ee750d6ac9c</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6b296a0ce2f382</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Warehouse Architect</t>
+          <t>Senior Data Engineer - IICS</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>SYSTECH USA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Databricks, GCP, Spark, Scala, Kafka, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, Cloud Storage, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,102 +1546,102 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48617c6692425cb2</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf36b7e279da791</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Enterprise Application Developer (Full Stack)</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Exponent</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, ECS, RDS, Azure, Scala, SQL Server</t>
+          <t>AWS, Glue, S3, RDS, Scala, Kafka, Snowflake, SQL Server, ETL, Tableau</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acf79124967bf4c3</t>
+          <t>https://www.indeed.com/viewjob?jk=782f670b324716aa</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>AWS, Glue, S3, RDS, Scala, Kafka, Snowflake, SQL Server, ETL, Tableau</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5acecf0e4305790</t>
+          <t>https://www.indeed.com/viewjob?jk=65a4b202ac924d0b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AI/ML Engineering Intern (Summer 2026)</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Poshmark</t>
+          <t>Kharon</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, Scala, Kafka, MongoDB, MLflow, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Databricks, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,102 +1651,102 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fd3431b51acd4b5</t>
+          <t>https://www.indeed.com/viewjob?jk=1834ddbeb8ec8bb3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Cloudera Public Cloud Platform Engineer</t>
+          <t>Architect: Enterprise Data</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Mayer Brown LLP</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Plano, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce7428fbc9c89fa9</t>
+          <t>https://www.indeed.com/viewjob?jk=ced77385e81a71b8</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Full Stack Developer (JS/TS, AWS)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Panasonic Automotive</t>
+          <t>Low Associates</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>South Bend, IN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, Spark, Scala, Spark Streaming, Kafka, MLOps, MLflow</t>
+          <t>AWS, Lambda, API Gateway, IAM, Azure, GCP, Cloud Storage, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11ce688bd126a002</t>
+          <t>https://www.indeed.com/viewjob?jk=45727b1c951a0e5a</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DevOps &amp; AI Automation Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sunbit, Inc</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6b296a0ce2f382</t>
+          <t>https://www.indeed.com/viewjob?jk=1444a89356fbe315</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - IICS</t>
+          <t>Senior Developer - Level III - 26-04057</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SYSTECH USA</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Cloud Storage, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD</t>
+          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf36b7e279da791</t>
+          <t>https://www.indeed.com/viewjob?jk=43063b055188ce3c</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Developer - Level III - 26-04057</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Kafka, Snowflake, SQL Server, ETL, Tableau</t>
+          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=782f670b324716aa</t>
+          <t>https://www.indeed.com/viewjob?jk=6cc0ba82c4bd25dc</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Developer - Level III - 26-04057</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Kafka, Snowflake, SQL Server, ETL, Tableau</t>
+          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65a4b202ac924d0b</t>
+          <t>https://www.indeed.com/viewjob?jk=9eeb6502ebf78cc0</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Developer - Level III - 26-04057</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Kharon</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Santa Clarita, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1834ddbeb8ec8bb3</t>
+          <t>https://www.indeed.com/viewjob?jk=473b7754552ef179</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer, Smart Factory Solutions</t>
+          <t>Senior Developer - Level III - 26-04057</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Magna International</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Lancaster, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Azure DevOps</t>
+          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7d8d9f6032e5b6f</t>
+          <t>https://www.indeed.com/viewjob?jk=5e872365f29ac108</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Sr Business Intelligence Developer - Onsite</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Sunbit, Inc</t>
+          <t>Bass Pro Shops</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1444a89356fbe315</t>
+          <t>https://www.indeed.com/viewjob?jk=ba1611f04cfe11a7</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Web Application Architect 3</t>
+          <t>Machine Learning Engineer (171680)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Bloomberg Industry Group</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,77 +1991,77 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7846d03774f71aa5</t>
+          <t>https://www.indeed.com/viewjob?jk=a860d07867e70be2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Full Stack Developer (JS/TS, AWS)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Low Associates</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>South Bend, IN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, Azure, GCP, Cloud Storage, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45727b1c951a0e5a</t>
+          <t>https://www.indeed.com/viewjob?jk=523330c74b38a27b</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Developer - Level III - 26-04057</t>
+          <t>Senior SRE</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, GCP, Scala, DynamoDB, Cassandra, NoSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43063b055188ce3c</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc41b902449ace0</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Developer - Level III - 26-04057</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cc0ba82c4bd25dc</t>
+          <t>https://www.indeed.com/viewjob?jk=7beef8ad4f571f7a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Developer - Level III - 26-04057</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eeb6502ebf78cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=3088b1f92a7a6242</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Developer - Level III - 26-04057</t>
+          <t>AI Cloud Security and Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Troutman Pepper Locke</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Santa Clarita, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=473b7754552ef179</t>
+          <t>https://www.indeed.com/viewjob?jk=04325b074eb62665</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Developer - Level III - 26-04057</t>
+          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Lancaster, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e872365f29ac108</t>
+          <t>https://www.indeed.com/viewjob?jk=c20056a5b9ffca80</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr Business Intelligence Developer - Onsite</t>
+          <t>Data Engineer (SQL / Spark / Python)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Bass Pro Shops</t>
+          <t>cloudteam</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, Oozie, YARN</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,59 +2246,59 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba1611f04cfe11a7</t>
+          <t>https://www.indeed.com/viewjob?jk=6ae648cd8fe57362</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer (171680)</t>
+          <t>Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Holland &amp; Knight</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Brandon, FL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, Airflow, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a860d07867e70be2</t>
+          <t>https://www.indeed.com/viewjob?jk=3abb3ed211255b11</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=523330c74b38a27b</t>
+          <t>https://www.indeed.com/viewjob?jk=766f2f5e9a7201f1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior SRE</t>
+          <t>Cloud Software Engineer 3 - III</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>InterImage</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, DynamoDB, Cassandra, NoSQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc41b902449ace0</t>
+          <t>https://www.indeed.com/viewjob?jk=16ddbf61e3ea0b92</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Software Engineer 3 - II</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>InterImage</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7beef8ad4f571f7a</t>
+          <t>https://www.indeed.com/viewjob?jk=43bfe7ca1f6eddb7</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Cloud Software Engineer 3 - I</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>InterImage</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3088b1f92a7a6242</t>
+          <t>https://www.indeed.com/viewjob?jk=2124d09922154cc4</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AI Cloud Security and Infrastructure Engineer</t>
+          <t>GIS Support Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Troutman Pepper Locke</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, API Gateway, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04325b074eb62665</t>
+          <t>https://www.indeed.com/viewjob?jk=e24b40c19089ff90</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
+          <t>Data Engineer, Cat Digital Data &amp; AI</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c20056a5b9ffca80</t>
+          <t>https://www.indeed.com/viewjob?jk=699bf154d150027f</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer (SQL / Spark / Python)</t>
+          <t>Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>cloudteam</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, Oozie, YARN</t>
+          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ae648cd8fe57362</t>
+          <t>https://www.indeed.com/viewjob?jk=39b5eeee4ff704ee</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>SRE Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Holland &amp; Knight</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Brandon, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3abb3ed211255b11</t>
+          <t>https://www.indeed.com/viewjob?jk=907826ed55a037a8</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Oracle, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766f2f5e9a7201f1</t>
+          <t>https://www.indeed.com/viewjob?jk=bca63339137d0189</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer 3 - III</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>InterImage</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16ddbf61e3ea0b92</t>
+          <t>https://www.indeed.com/viewjob?jk=deb135bf06a2110e</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer 3 - II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>InterImage</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43bfe7ca1f6eddb7</t>
+          <t>https://www.indeed.com/viewjob?jk=2be9ee403cf20f67</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer 3 - I</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>InterImage</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2124d09922154cc4</t>
+          <t>https://www.indeed.com/viewjob?jk=156e5a4def2a4a5d</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>GIS Support Engineer</t>
+          <t>Senior Analytic Data Engineer (Python/Power BI)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Highmark Health</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, ETL, Power BI</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e24b40c19089ff90</t>
+          <t>https://www.indeed.com/viewjob?jk=100c60fa90e63408</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Performance Test Engineer</t>
+          <t>Sr. Software Engineer II</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TIAG</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Splunk, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82eb3dabcdfd111c</t>
+          <t>https://www.indeed.com/viewjob?jk=04a1d1c06680e371</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Developer Architect (Cloud Services)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Core &amp; Main</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec8ec9187f270065</t>
+          <t>https://www.indeed.com/viewjob?jk=b5e2495e00e0060d</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SRE Architect</t>
+          <t>Senior Devops Engineer - MN</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>RAZR Marketing, Inc.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Splunk, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, PostgreSQL, Docker, Kubernetes, CloudWatch</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=907826ed55a037a8</t>
+          <t>https://www.indeed.com/viewjob?jk=3375eb3b3d50ba05</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr. Software QA Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Carlsmed</t>
+          <t>Core &amp; Main</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f92907b243e51105</t>
+          <t>https://www.indeed.com/viewjob?jk=b2cdf5f4ac6a6c1a</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer, Cat Digital Data &amp; AI</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=699bf154d150027f</t>
+          <t>https://www.indeed.com/viewjob?jk=1a31dfca06d884ad</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer (Full Stack)</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39b5eeee4ff704ee</t>
+          <t>https://www.indeed.com/viewjob?jk=f6b1cb632eed3bcb</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Oracle, ETL, CI/CD, Git</t>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bca63339137d0189</t>
+          <t>https://www.indeed.com/viewjob?jk=ec090a150db0c5f8</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deb135bf06a2110e</t>
+          <t>https://www.indeed.com/viewjob?jk=3fe79bacd5e58f55</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2be9ee403cf20f67</t>
+          <t>https://www.indeed.com/viewjob?jk=f09282ebd98b3570</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=156e5a4def2a4a5d</t>
+          <t>https://www.indeed.com/viewjob?jk=fa1d73f24fc01af9</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Analytic Data Engineer (Python/Power BI)</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Highmark Health</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, ETL, Power BI</t>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=100c60fa90e63408</t>
+          <t>https://www.indeed.com/viewjob?jk=7e4150c94fe908c8</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Metropolitan Companies</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Wyomissing, PA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Splunk, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, SQL Server, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04a1d1c06680e371</t>
+          <t>https://www.indeed.com/viewjob?jk=12c03c3bb6ce8c38</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst/Associate - New York</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Core &amp; Main</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5e2495e00e0060d</t>
+          <t>https://www.indeed.com/viewjob?jk=1dd43ffc6d7fda89</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer - MN</t>
+          <t>Supervisor, Software Engineering</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>RAZR Marketing, Inc.</t>
+          <t>Energy Systems Group</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Newburgh, IN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, PostgreSQL, Docker, Kubernetes, CloudWatch</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3375eb3b3d50ba05</t>
+          <t>https://www.indeed.com/viewjob?jk=9c197f77bdf171e6</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer, Experimentation Platform (Backend Services)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Core &amp; Main</t>
+          <t>Paramount Streaming</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Kinesis, Redshift, RDS, GCP, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2cdf5f4ac6a6c1a</t>
+          <t>https://www.indeed.com/viewjob?jk=1f33593f93ffe80a</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>IS Technical Specialist</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>WILLDAN GROUP</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a31dfca06d884ad</t>
+          <t>https://www.indeed.com/viewjob?jk=757269b719268379</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>IS Technical Specialist</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>WILLDAN GROUP</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6b1cb632eed3bcb</t>
+          <t>https://www.indeed.com/viewjob?jk=609b33430f9df835</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>IS Technical Specialist</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>WILLDAN GROUP</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec090a150db0c5f8</t>
+          <t>https://www.indeed.com/viewjob?jk=ef377da6b1a8bbfd</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>IS Technical Specialist</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>WILLDAN GROUP</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fe79bacd5e58f55</t>
+          <t>https://www.indeed.com/viewjob?jk=6aea6ee79779b03b</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>IS Technical Specialist</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>WILLDAN GROUP</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Fairlawn, OH, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f09282ebd98b3570</t>
+          <t>https://www.indeed.com/viewjob?jk=da070db6e9060b88</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>IS Technical Specialist</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>WILLDAN GROUP</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,462 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1d73f24fc01af9</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Cloud Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>WILLDAN GROUP</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7e4150c94fe908c8</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Metropolitan Companies</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Wyomissing, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, SQL Server, ETL, ELT, Power BI, Tableau, CI/CD</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=12c03c3bb6ce8c38</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Experimentation Platform (Backend Services)</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Paramount Streaming</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, Redshift, RDS, GCP, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1f33593f93ffe80a</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst/Associate - New York</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Goldman Sachs</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1dd43ffc6d7fda89</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Supervisor, Software Engineering</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Energy Systems Group</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Newburgh, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9c197f77bdf171e6</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>IS Technical Specialist</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Huntington Bank</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=757269b719268379</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>IS Technical Specialist</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Huntington Bank</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Cleveland, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=609b33430f9df835</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>IS Technical Specialist</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Huntington Bank</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Cincinnati, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ef377da6b1a8bbfd</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>IS Technical Specialist</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Huntington Bank</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6aea6ee79779b03b</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>IS Technical Specialist</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Huntington Bank</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Fairlawn, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=da070db6e9060b88</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>IS Technical Specialist</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Huntington Bank</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=63d188ef103369c5</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Database Automation Developer (contract)</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>BNY</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, MongoDB, CI/CD, Terraform, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=78a015d8ecbb3c7f</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Software Engineer I - Full Stack</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Chewy</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, YARN, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e317b1b40c2e7beb</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-16.xlsx
+++ b/results/job_matches_2026-04-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Application Developer, Portland Oregon</t>
+          <t>Databricks Data Architect - Consultant</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Portland General Electric</t>
+          <t>BluEnt</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,42 +661,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9f186e739ef98be</t>
+          <t>https://www.indeed.com/viewjob?jk=8c12fb6e67e8bda7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Application Developer, Portland Oregon</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HelioCampus</t>
+          <t>Portland General Electric</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=333fbc294a529a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=f9f186e739ef98be</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer/Data Scientist</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>HelioCampus</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a711c2fcb36b6cf</t>
+          <t>https://www.indeed.com/viewjob?jk=333fbc294a529a0f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (ON-SITE)</t>
+          <t>Data Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Equinox</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, Snowflake, DynamoDB</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=038b96d69cecd888</t>
+          <t>https://www.indeed.com/viewjob?jk=8a711c2fcb36b6cf</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Databricks Data Analyst</t>
+          <t>Sr. Data Engineer (ON-SITE)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>Equinox</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,104 +801,104 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, Snowflake, DynamoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce89a36f70a3941b</t>
+          <t>https://www.indeed.com/viewjob?jk=038b96d69cecd888</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Data Analyst</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Lincoln Financial Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb699a2e3bdbb440</t>
+          <t>https://www.indeed.com/viewjob?jk=ce89a36f70a3941b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of St. Louis</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af192f5dcbf84698</t>
+          <t>https://www.indeed.com/viewjob?jk=cb699a2e3bdbb440</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Sr Cloud Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BLOC Resources, LLC</t>
+          <t>Federal Reserve Bank of St. Louis</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9e13379e16ee4b4</t>
+          <t>https://www.indeed.com/viewjob?jk=af192f5dcbf84698</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Ad Ops Engineer</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>BLOC Resources, LLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>Azure, Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f14f238cb8b8c5f1</t>
+          <t>https://www.indeed.com/viewjob?jk=d9e13379e16ee4b4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Ad Ops Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,69 +976,69 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe1513252d7f11af</t>
+          <t>https://www.indeed.com/viewjob?jk=f14f238cb8b8c5f1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Associate IT Officer, Data and Information Management (Associate Data Engineer)</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>World Bank Group</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a40cff6b5df03cd</t>
+          <t>https://www.indeed.com/viewjob?jk=fe1513252d7f11af</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer- OrderlyMeds</t>
+          <t>Associate IT Officer, Data and Information Management (Associate Data Engineer)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>OrderlyMeds</t>
+          <t>World Bank Group</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb2a73a0846955d</t>
+          <t>https://www.indeed.com/viewjob?jk=7a40cff6b5df03cd</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer- OrderlyMeds</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>OrderlyMeds</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Databricks, Scala, DynamoDB</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa4d88005315e7ba</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb2a73a0846955d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior, Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Cassandra</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Databricks, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fcd1c4e67959eea</t>
+          <t>https://www.indeed.com/viewjob?jk=aa4d88005315e7ba</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI Intern</t>
+          <t>Senior, Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, dbt, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Cassandra</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bea47ac5f13bd1f</t>
+          <t>https://www.indeed.com/viewjob?jk=3fcd1c4e67959eea</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer III – Cloud Platform Engineering - Python / AWS</t>
+          <t>AI Intern</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, ECS, RDS, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, dbt, MLflow</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb199efc831c0dc4</t>
+          <t>https://www.indeed.com/viewjob?jk=7bea47ac5f13bd1f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III – Cloud Platform Engineering - Python / AWS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Atlanta, KS, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Azure Cosmos DB, Data Modeling, ELT</t>
+          <t>AWS, EMR, S3, ECS, RDS, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9a02726d78410b5</t>
+          <t>https://www.indeed.com/viewjob?jk=bb199efc831c0dc4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Energy Services Group</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Atlanta, KS, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Azure Cosmos DB, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6918de34da34b82a</t>
+          <t>https://www.indeed.com/viewjob?jk=e9a02726d78410b5</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Energy Services Group</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2a1afc987319b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=6918de34da34b82a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (Cloud Enablement)</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Flexera</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72d1842ef3999b1d</t>
+          <t>https://www.indeed.com/viewjob?jk=b2a1afc987319b9a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Site Reliability Engineer (Cloud Enablement)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Flexera</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5acecf0e4305790</t>
+          <t>https://www.indeed.com/viewjob?jk=72d1842ef3999b1d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Warehouse Architect</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Databricks, GCP, Spark, Scala, Kafka, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48617c6692425cb2</t>
+          <t>https://www.indeed.com/viewjob?jk=a5acecf0e4305790</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AI/ML Engineering Intern (Summer 2026)</t>
+          <t>Data Engineer - Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Poshmark</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, Scala, Kafka, MongoDB, MLflow, Jenkins, Docker, Kubernetes</t>
+          <t>RDS, Databricks, GCP, Spark, Scala, Kafka, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fd3431b51acd4b5</t>
+          <t>https://www.indeed.com/viewjob?jk=48617c6692425cb2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Cloudera Public Cloud Platform Engineer</t>
+          <t>AI/ML Engineering Intern (Summer 2026)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Poshmark</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Plano, CA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
+          <t>Redshift, Databricks, Spark, Scala, Kafka, MongoDB, MLflow, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce7428fbc9c89fa9</t>
+          <t>https://www.indeed.com/viewjob?jk=7fd3431b51acd4b5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DevOps &amp; AI Automation Engineer</t>
+          <t>Cloudera Public Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,59 +1501,59 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6b296a0ce2f382</t>
+          <t>https://www.indeed.com/viewjob?jk=ce7428fbc9c89fa9</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - IICS</t>
+          <t>Platform Operations Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SYSTECH USA</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Cloud Storage, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, CodeBuild</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf36b7e279da791</t>
+          <t>https://www.indeed.com/viewjob?jk=62bcd4ad2d0bbc62</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>DevOps &amp; AI Automation Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1563,42 +1563,42 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Kafka, Snowflake, SQL Server, ETL, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=782f670b324716aa</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6b296a0ce2f382</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Software Developer Internship</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Kafka, Snowflake, SQL Server, ETL, Tableau</t>
+          <t>AWS, Lambda, SQS, RDS, Azure, Kafka, DynamoDB, Power BI, Splunk, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65a4b202ac924d0b</t>
+          <t>https://www.indeed.com/viewjob?jk=c5ee38c644f00bbc</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Data Engineer - IICS</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Kharon</t>
+          <t>SYSTECH USA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Redshift, Cloud Storage, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1834ddbeb8ec8bb3</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf36b7e279da791</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Architect: Enterprise Data</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mayer Brown LLP</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, S3, RDS, Scala, Kafka, Snowflake, SQL Server, ETL, Tableau</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced77385e81a71b8</t>
+          <t>https://www.indeed.com/viewjob?jk=782f670b324716aa</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Full Stack Developer (JS/TS, AWS)</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Low Associates</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>South Bend, IN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, Azure, GCP, Cloud Storage, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, Glue, S3, RDS, Scala, Kafka, Snowflake, SQL Server, ETL, Tableau</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45727b1c951a0e5a</t>
+          <t>https://www.indeed.com/viewjob?jk=65a4b202ac924d0b</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sunbit, Inc</t>
+          <t>Kharon</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
+          <t>AWS, S3, RDS, Databricks, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1444a89356fbe315</t>
+          <t>https://www.indeed.com/viewjob?jk=1834ddbeb8ec8bb3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Developer - Level III - 26-04057</t>
+          <t>Architect: Enterprise Data</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Mayer Brown LLP</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43063b055188ce3c</t>
+          <t>https://www.indeed.com/viewjob?jk=ced77385e81a71b8</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Developer - Level III - 26-04057</t>
+          <t>Full Stack Developer (JS/TS, AWS)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Low Associates</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>South Bend, IN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, API Gateway, IAM, Azure, GCP, Cloud Storage, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cc0ba82c4bd25dc</t>
+          <t>https://www.indeed.com/viewjob?jk=45727b1c951a0e5a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Developer - Level III - 26-04057</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Sunbit, Inc</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eeb6502ebf78cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=1444a89356fbe315</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Santa Clarita, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=473b7754552ef179</t>
+          <t>https://www.indeed.com/viewjob?jk=43063b055188ce3c</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Lancaster, CA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e872365f29ac108</t>
+          <t>https://www.indeed.com/viewjob?jk=6cc0ba82c4bd25dc</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr Business Intelligence Developer - Onsite</t>
+          <t>Senior Developer - Level III - 26-04057</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Bass Pro Shops</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba1611f04cfe11a7</t>
+          <t>https://www.indeed.com/viewjob?jk=9eeb6502ebf78cc0</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer (171680)</t>
+          <t>Senior Developer - Level III - 26-04057</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Santa Clarita, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,42 +1991,42 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a860d07867e70be2</t>
+          <t>https://www.indeed.com/viewjob?jk=473b7754552ef179</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Developer - Level III - 26-04057</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Lancaster, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
+          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=523330c74b38a27b</t>
+          <t>https://www.indeed.com/viewjob?jk=5e872365f29ac108</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior SRE</t>
+          <t>Sr Business Intelligence Developer - Onsite</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>Bass Pro Shops</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, DynamoDB, Cassandra, NoSQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,59 +2071,59 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc41b902449ace0</t>
+          <t>https://www.indeed.com/viewjob?jk=ba1611f04cfe11a7</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Engineer (171680)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7beef8ad4f571f7a</t>
+          <t>https://www.indeed.com/viewjob?jk=a860d07867e70be2</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3088b1f92a7a6242</t>
+          <t>https://www.indeed.com/viewjob?jk=523330c74b38a27b</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AI Cloud Security and Infrastructure Engineer</t>
+          <t>Senior SRE</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Troutman Pepper Locke</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, GCP, Scala, DynamoDB, Cassandra, NoSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04325b074eb62665</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc41b902449ace0</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c20056a5b9ffca80</t>
+          <t>https://www.indeed.com/viewjob?jk=7beef8ad4f571f7a</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer (SQL / Spark / Python)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>cloudteam</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, Oozie, YARN</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ae648cd8fe57362</t>
+          <t>https://www.indeed.com/viewjob?jk=3088b1f92a7a6242</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>AI Cloud Security and Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Holland &amp; Knight</t>
+          <t>Troutman Pepper Locke</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brandon, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3abb3ed211255b11</t>
+          <t>https://www.indeed.com/viewjob?jk=04325b074eb62665</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766f2f5e9a7201f1</t>
+          <t>https://www.indeed.com/viewjob?jk=c20056a5b9ffca80</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer 3 - III</t>
+          <t>Data Engineer (SQL / Spark / Python)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>InterImage</t>
+          <t>cloudteam</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, Oozie, YARN</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16ddbf61e3ea0b92</t>
+          <t>https://www.indeed.com/viewjob?jk=6ae648cd8fe57362</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer 3 - II</t>
+          <t>Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>InterImage</t>
+          <t>Holland &amp; Knight</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Brandon, FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, Airflow, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43bfe7ca1f6eddb7</t>
+          <t>https://www.indeed.com/viewjob?jk=3abb3ed211255b11</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer 3 - I</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>InterImage</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2124d09922154cc4</t>
+          <t>https://www.indeed.com/viewjob?jk=766f2f5e9a7201f1</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>GIS Support Engineer</t>
+          <t>Cloud Software Engineer 3 - III</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>InterImage</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e24b40c19089ff90</t>
+          <t>https://www.indeed.com/viewjob?jk=16ddbf61e3ea0b92</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer, Cat Digital Data &amp; AI</t>
+          <t>Cloud Software Engineer 3 - II</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>InterImage</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=699bf154d150027f</t>
+          <t>https://www.indeed.com/viewjob?jk=43bfe7ca1f6eddb7</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer (Full Stack)</t>
+          <t>Cloud Software Engineer 3 - I</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>InterImage</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39b5eeee4ff704ee</t>
+          <t>https://www.indeed.com/viewjob?jk=2124d09922154cc4</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SRE Architect</t>
+          <t>GIS Support Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Splunk, CI/CD, Terraform</t>
+          <t>AWS, API Gateway, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=907826ed55a037a8</t>
+          <t>https://www.indeed.com/viewjob?jk=e24b40c19089ff90</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Data Engineer, Cat Digital Data &amp; AI</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Oracle, ETL, CI/CD, Git</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bca63339137d0189</t>
+          <t>https://www.indeed.com/viewjob?jk=699bf154d150027f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deb135bf06a2110e</t>
+          <t>https://www.indeed.com/viewjob?jk=39b5eeee4ff704ee</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>SRE Architect</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2be9ee403cf20f67</t>
+          <t>https://www.indeed.com/viewjob?jk=907826ed55a037a8</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Oracle, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=156e5a4def2a4a5d</t>
+          <t>https://www.indeed.com/viewjob?jk=bca63339137d0189</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Analytic Data Engineer (Python/Power BI)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Highmark Health</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, ETL, Power BI</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=100c60fa90e63408</t>
+          <t>https://www.indeed.com/viewjob?jk=deb135bf06a2110e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Splunk, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04a1d1c06680e371</t>
+          <t>https://www.indeed.com/viewjob?jk=2be9ee403cf20f67</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Core &amp; Main</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5e2495e00e0060d</t>
+          <t>https://www.indeed.com/viewjob?jk=156e5a4def2a4a5d</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer - MN</t>
+          <t>Senior Analytic Data Engineer (Python/Power BI)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>RAZR Marketing, Inc.</t>
+          <t>Highmark Health</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, PostgreSQL, Docker, Kubernetes, CloudWatch</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, ETL, Power BI</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3375eb3b3d50ba05</t>
+          <t>https://www.indeed.com/viewjob?jk=100c60fa90e63408</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr. Software Engineer II</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Core &amp; Main</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Splunk, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2cdf5f4ac6a6c1a</t>
+          <t>https://www.indeed.com/viewjob?jk=04a1d1c06680e371</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>WILLDAN GROUP</t>
+          <t>Core &amp; Main</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a31dfca06d884ad</t>
+          <t>https://www.indeed.com/viewjob?jk=b5e2495e00e0060d</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Senior Devops Engineer - MN</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>WILLDAN GROUP</t>
+          <t>RAZR Marketing, Inc.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, PostgreSQL, Docker, Kubernetes, CloudWatch</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6b1cb632eed3bcb</t>
+          <t>https://www.indeed.com/viewjob?jk=3375eb3b3d50ba05</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>WILLDAN GROUP</t>
+          <t>Core &amp; Main</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec090a150db0c5f8</t>
+          <t>https://www.indeed.com/viewjob?jk=b2cdf5f4ac6a6c1a</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fe79bacd5e58f55</t>
+          <t>https://www.indeed.com/viewjob?jk=1a31dfca06d884ad</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f09282ebd98b3570</t>
+          <t>https://www.indeed.com/viewjob?jk=f6b1cb632eed3bcb</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1d73f24fc01af9</t>
+          <t>https://www.indeed.com/viewjob?jk=ec090a150db0c5f8</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e4150c94fe908c8</t>
+          <t>https://www.indeed.com/viewjob?jk=3fe79bacd5e58f55</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Metropolitan Companies</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Wyomissing, PA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, SQL Server, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12c03c3bb6ce8c38</t>
+          <t>https://www.indeed.com/viewjob?jk=f09282ebd98b3570</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst/Associate - New York</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dd43ffc6d7fda89</t>
+          <t>https://www.indeed.com/viewjob?jk=fa1d73f24fc01af9</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Supervisor, Software Engineering</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Energy Systems Group</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Newburgh, IN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c197f77bdf171e6</t>
+          <t>https://www.indeed.com/viewjob?jk=7e4150c94fe908c8</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Experimentation Platform (Backend Services)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Paramount Streaming</t>
+          <t>Metropolitan Companies</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Wyomissing, PA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, GCP, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, SQL Server, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f33593f93ffe80a</t>
+          <t>https://www.indeed.com/viewjob?jk=12c03c3bb6ce8c38</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>IS Technical Specialist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>CardioOne</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=757269b719268379</t>
+          <t>https://www.indeed.com/viewjob?jk=34653b24bff70a46</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>IS Technical Specialist</t>
+          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst/Associate - New York</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=609b33430f9df835</t>
+          <t>https://www.indeed.com/viewjob?jk=1dd43ffc6d7fda89</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>IS Technical Specialist</t>
+          <t>Supervisor, Software Engineering</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Energy Systems Group</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Newburgh, IN, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef377da6b1a8bbfd</t>
+          <t>https://www.indeed.com/viewjob?jk=9c197f77bdf171e6</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>IS Technical Specialist</t>
+          <t>Senior Software Engineer, Experimentation Platform (Backend Services)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Paramount Streaming</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
+          <t>AWS, Kinesis, Redshift, RDS, GCP, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aea6ee79779b03b</t>
+          <t>https://www.indeed.com/viewjob?jk=1f33593f93ffe80a</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Fairlawn, OH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da070db6e9060b88</t>
+          <t>https://www.indeed.com/viewjob?jk=757269b719268379</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3470,6 +3470,146 @@
         </is>
       </c>
       <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=609b33430f9df835</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>IS Technical Specialist</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Huntington Bank</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef377da6b1a8bbfd</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>IS Technical Specialist</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Huntington Bank</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6aea6ee79779b03b</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>IS Technical Specialist</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Huntington Bank</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Fairlawn, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da070db6e9060b88</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>IS Technical Specialist</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Huntington Bank</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=63d188ef103369c5</t>
         </is>

--- a/results/job_matches_2026-04-16.xlsx
+++ b/results/job_matches_2026-04-16.xlsx
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior ML Engineer - Agentic AI</t>
+          <t>Databricks Data Architect - Consultant</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>BluEnt</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ee08a694c71ee91</t>
+          <t>https://www.indeed.com/viewjob?jk=8c12fb6e67e8bda7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Databricks Data Architect - Consultant</t>
+          <t>Senior ML Engineer - Agentic AI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BluEnt</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Spark</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c12fb6e67e8bda7</t>
+          <t>https://www.indeed.com/viewjob?jk=0ee08a694c71ee91</t>
         </is>
       </c>
     </row>
@@ -853,52 +853,52 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Cloud Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Federal Reserve Bank of St. Louis</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb699a2e3bdbb440</t>
+          <t>https://www.indeed.com/viewjob?jk=af192f5dcbf84698</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr Cloud Engineer</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of St. Louis</t>
+          <t>BLOC Resources, LLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Scala, Oracle, PostgreSQL</t>
+          <t>Azure, Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af192f5dcbf84698</t>
+          <t>https://www.indeed.com/viewjob?jk=d9e13379e16ee4b4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Senior Ad Ops Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BLOC Resources, LLC</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9e13379e16ee4b4</t>
+          <t>https://www.indeed.com/viewjob?jk=f14f238cb8b8c5f1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Ad Ops Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,69 +976,69 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f14f238cb8b8c5f1</t>
+          <t>https://www.indeed.com/viewjob?jk=fe1513252d7f11af</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Associate IT Officer, Data and Information Management (Associate Data Engineer)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>World Bank Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe1513252d7f11af</t>
+          <t>https://www.indeed.com/viewjob?jk=7a40cff6b5df03cd</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Associate IT Officer, Data and Information Management (Associate Data Engineer)</t>
+          <t>Data Engineer- OrderlyMeds</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>World Bank Group</t>
+          <t>OrderlyMeds</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a40cff6b5df03cd</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb2a73a0846955d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer- OrderlyMeds</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>OrderlyMeds</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Databricks, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb2a73a0846955d</t>
+          <t>https://www.indeed.com/viewjob?jk=aa4d88005315e7ba</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior, Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Databricks, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Cassandra</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa4d88005315e7ba</t>
+          <t>https://www.indeed.com/viewjob?jk=3fcd1c4e67959eea</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior, Software Engineer</t>
+          <t>Software Engineer III – Cloud Platform Engineering - Python / AWS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Cassandra</t>
+          <t>AWS, EMR, S3, ECS, RDS, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fcd1c4e67959eea</t>
+          <t>https://www.indeed.com/viewjob?jk=bb199efc831c0dc4</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI Intern</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Atlanta, KS, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, dbt, MLflow</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Azure Cosmos DB, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bea47ac5f13bd1f</t>
+          <t>https://www.indeed.com/viewjob?jk=e9a02726d78410b5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer III – Cloud Platform Engineering - Python / AWS</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Energy Services Group</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, ECS, RDS, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb199efc831c0dc4</t>
+          <t>https://www.indeed.com/viewjob?jk=6918de34da34b82a</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, KS, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Azure Cosmos DB, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9a02726d78410b5</t>
+          <t>https://www.indeed.com/viewjob?jk=b2a1afc987319b9a</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Site Reliability Engineer (Cloud Enablement)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Energy Services Group</t>
+          <t>Flexera</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6918de34da34b82a</t>
+          <t>https://www.indeed.com/viewjob?jk=72d1842ef3999b1d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2a1afc987319b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=a5acecf0e4305790</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (Cloud Enablement)</t>
+          <t>Data Engineer - Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Flexera</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Databricks, GCP, Spark, Scala, Kafka, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,67 +1371,67 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72d1842ef3999b1d</t>
+          <t>https://www.indeed.com/viewjob?jk=48617c6692425cb2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Machine Learning Engineer II (Remote)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Kohl's</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, ETL, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5acecf0e4305790</t>
+          <t>https://www.indeed.com/viewjob?jk=2a7d736f0a5c3255</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Warehouse Architect</t>
+          <t>AI/ML Engineering Intern (Summer 2026)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>Poshmark</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Databricks, GCP, Spark, Scala, Kafka, Oracle, Data Modeling, ETL, ELT</t>
+          <t>Redshift, Databricks, Spark, Scala, Kafka, MongoDB, MLflow, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48617c6692425cb2</t>
+          <t>https://www.indeed.com/viewjob?jk=7fd3431b51acd4b5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI/ML Engineering Intern (Summer 2026)</t>
+          <t>Cloudera Public Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Poshmark</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Plano, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, Scala, Kafka, MongoDB, MLflow, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fd3431b51acd4b5</t>
+          <t>https://www.indeed.com/viewjob?jk=ce7428fbc9c89fa9</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cloudera Public Cloud Platform Engineer</t>
+          <t>Platform Operations Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Plano, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,29 +1501,29 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, CodeBuild</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce7428fbc9c89fa9</t>
+          <t>https://www.indeed.com/viewjob?jk=62bcd4ad2d0bbc62</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Platform Operations Engineer</t>
+          <t>DevOps &amp; AI Automation Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1536,42 +1536,42 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, CodeBuild</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62bcd4ad2d0bbc62</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6b296a0ce2f382</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DevOps &amp; AI Automation Engineer</t>
+          <t>Software Developer Internship</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, RDS, Azure, Kafka, DynamoDB, Power BI, Splunk, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6b296a0ce2f382</t>
+          <t>https://www.indeed.com/viewjob?jk=c5ee38c644f00bbc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Developer Internship</t>
+          <t>Sr. Software Engineer - Data Infrastructure</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, RDS, Azure, Kafka, DynamoDB, Power BI, Splunk, AWS CodePipeline</t>
+          <t>AWS, S3, RDS, GCP, HDFS, Hive, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5ee38c644f00bbc</t>
+          <t>https://www.indeed.com/viewjob?jk=df9f48d9232b00bf</t>
         </is>
       </c>
     </row>
@@ -3303,17 +3303,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst/Associate - New York</t>
+          <t>Supervisor, Software Engineering</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Energy Systems Group</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Newburgh, IN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dd43ffc6d7fda89</t>
+          <t>https://www.indeed.com/viewjob?jk=9c197f77bdf171e6</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Supervisor, Software Engineering</t>
+          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst/Associate - New York</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Energy Systems Group</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Newburgh, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,17 +3356,17 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c197f77bdf171e6</t>
+          <t>https://www.indeed.com/viewjob?jk=1dd43ffc6d7fda89</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-16.xlsx
+++ b/results/job_matches_2026-04-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G91"/>
+  <dimension ref="A1:G108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,12 +503,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Data Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nexnovels</t>
+          <t>Vertical Relevance</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -517,11 +517,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>20.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, Spark Streaming</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe02b0827629874b</t>
+          <t>https://www.indeed.com/viewjob?jk=664db57e743f0c66</t>
         </is>
       </c>
     </row>
@@ -608,52 +608,52 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Databricks Data Architect - Consultant</t>
+          <t>Data Architect, Senior</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BluEnt</t>
+          <t>Intermountain Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Murray, UT, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Spark</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c12fb6e67e8bda7</t>
+          <t>https://www.indeed.com/viewjob?jk=8184ec5fc529fc27</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior ML Engineer - Agentic AI</t>
+          <t>Databricks Data Architect - Consultant</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>BluEnt</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ee08a694c71ee91</t>
+          <t>https://www.indeed.com/viewjob?jk=8c12fb6e67e8bda7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Application Developer, Portland Oregon</t>
+          <t>Senior ML Engineer - Agentic AI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Portland General Electric</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,42 +696,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9f186e739ef98be</t>
+          <t>https://www.indeed.com/viewjob?jk=0ee08a694c71ee91</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Application Developer, Portland Oregon</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HelioCampus</t>
+          <t>Portland General Electric</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=333fbc294a529a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=f9f186e739ef98be</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer/Data Scientist</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>HelioCampus</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a711c2fcb36b6cf</t>
+          <t>https://www.indeed.com/viewjob?jk=333fbc294a529a0f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (ON-SITE)</t>
+          <t>Databricks Data Analyst</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Equinox</t>
+          <t>Lincoln Financial Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,77 +801,77 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, Snowflake, DynamoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=038b96d69cecd888</t>
+          <t>https://www.indeed.com/viewjob?jk=ce89a36f70a3941b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Databricks Data Analyst</t>
+          <t>Senior Data Engineer – Credit Risk (Hybrid) - New York, NY</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce89a36f70a3941b</t>
+          <t>https://www.indeed.com/viewjob?jk=23517bc36e765c0f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr Cloud Engineer</t>
+          <t>Senior Data Engineer – Credit Risk (Hybrid) - New York, NY</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of St. Louis</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,102 +881,102 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af192f5dcbf84698</t>
+          <t>https://www.indeed.com/viewjob?jk=16e736022550c4c5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Senior Data Engineer – Credit Risk (Hybrid) - New York, NY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BLOC Resources, LLC</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9e13379e16ee4b4</t>
+          <t>https://www.indeed.com/viewjob?jk=97b0320ba5b0219b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Ad Ops Engineer</t>
+          <t>Senior Data Engineer – Credit Risk (Hybrid) - New York, NY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bronx, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f14f238cb8b8c5f1</t>
+          <t>https://www.indeed.com/viewjob?jk=22e782dc41b4055e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Graph DBA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,242 +986,242 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe1513252d7f11af</t>
+          <t>https://www.indeed.com/viewjob?jk=c15f03a1274f889c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Associate IT Officer, Data and Information Management (Associate Data Engineer)</t>
+          <t>Graph DBA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>World Bank Group</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a40cff6b5df03cd</t>
+          <t>https://www.indeed.com/viewjob?jk=e8b5a8aa7c2f7cd5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer- OrderlyMeds</t>
+          <t>Graph DBA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>OrderlyMeds</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb2a73a0846955d</t>
+          <t>https://www.indeed.com/viewjob?jk=a0522d81a23e6425</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Graph DBA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Databricks, Scala, DynamoDB</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa4d88005315e7ba</t>
+          <t>https://www.indeed.com/viewjob?jk=10fa9278e203e8c7</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior, Software Engineer</t>
+          <t>Sr Cloud Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>Federal Reserve Bank of St. Louis</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Cassandra</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fcd1c4e67959eea</t>
+          <t>https://www.indeed.com/viewjob?jk=af192f5dcbf84698</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer III – Cloud Platform Engineering - Python / AWS</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>BLOC Resources, LLC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, ECS, RDS, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>Azure, Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb199efc831c0dc4</t>
+          <t>https://www.indeed.com/viewjob?jk=d9e13379e16ee4b4</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Atlanta, KS, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Azure Cosmos DB, Data Modeling, ELT</t>
+          <t>AWS, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9a02726d78410b5</t>
+          <t>https://www.indeed.com/viewjob?jk=fe1513252d7f11af</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Associate IT Officer, Data and Information Management (Associate Data Engineer)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Energy Services Group</t>
+          <t>World Bank Group</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6918de34da34b82a</t>
+          <t>https://www.indeed.com/viewjob?jk=7a40cff6b5df03cd</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Data Engineer- OrderlyMeds</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>OrderlyMeds</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2a1afc987319b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb2a73a0846955d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (Cloud Enablement)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Flexera</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Databricks, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72d1842ef3999b1d</t>
+          <t>https://www.indeed.com/viewjob?jk=aa4d88005315e7ba</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Data Architecture Intern</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Smart Data Solutions</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>AWS, S3, IAM, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5acecf0e4305790</t>
+          <t>https://www.indeed.com/viewjob?jk=d67805e12d384da2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Warehouse Architect</t>
+          <t>Senior, Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Databricks, GCP, Spark, Scala, Kafka, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Cassandra</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48617c6692425cb2</t>
+          <t>https://www.indeed.com/viewjob?jk=3fcd1c4e67959eea</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II (Remote)</t>
+          <t>Software Engineer III – Cloud Platform Engineering - Python / AWS</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Kohl's</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, ETL, MLOps, CI/CD, Docker</t>
+          <t>AWS, EMR, S3, ECS, RDS, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a7d736f0a5c3255</t>
+          <t>https://www.indeed.com/viewjob?jk=bb199efc831c0dc4</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AI/ML Engineering Intern (Summer 2026)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Poshmark</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Atlanta, KS, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, Scala, Kafka, MongoDB, MLflow, Jenkins, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Azure Cosmos DB, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,102 +1441,102 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fd3431b51acd4b5</t>
+          <t>https://www.indeed.com/viewjob?jk=e9a02726d78410b5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Cloudera Public Cloud Platform Engineer</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Energy Services Group</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Plano, CA, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce7428fbc9c89fa9</t>
+          <t>https://www.indeed.com/viewjob?jk=6918de34da34b82a</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Platform Operations Engineer</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, CodeBuild</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62bcd4ad2d0bbc62</t>
+          <t>https://www.indeed.com/viewjob?jk=b2a1afc987319b9a</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DevOps &amp; AI Automation Engineer</t>
+          <t>Senior Software Development Engineer - Cloud Dev</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Transmedics</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Kinesis, Redshift, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6b296a0ce2f382</t>
+          <t>https://www.indeed.com/viewjob?jk=2f2220b49620882d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Developer Internship</t>
+          <t>Senior Enterprise Application Developer (Full Stack)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>Exponent</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, RDS, Azure, Kafka, DynamoDB, Power BI, Splunk, AWS CodePipeline</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, ECS, RDS, Azure, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5ee38c644f00bbc</t>
+          <t>https://www.indeed.com/viewjob?jk=57406ee750d6ac9c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Data Infrastructure</t>
+          <t>Data Engineer - Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, GCP, HDFS, Hive, Spark, Scala, Kafka, CI/CD</t>
+          <t>RDS, Databricks, GCP, Spark, Scala, Kafka, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df9f48d9232b00bf</t>
+          <t>https://www.indeed.com/viewjob?jk=48617c6692425cb2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - IICS</t>
+          <t>Senior Enterprise Application Developer (Full Stack)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SYSTECH USA</t>
+          <t>Exponent</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Cloud Storage, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, ECS, RDS, Azure, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,19 +1651,19 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf36b7e279da791</t>
+          <t>https://www.indeed.com/viewjob?jk=acf79124967bf4c3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1672,46 +1672,46 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Kafka, Snowflake, SQL Server, ETL, Tableau</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=782f670b324716aa</t>
+          <t>https://www.indeed.com/viewjob?jk=a5acecf0e4305790</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Machine Learning Engineer II (Remote)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Kohl's</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Kafka, Snowflake, SQL Server, ETL, Tableau</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, ETL, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65a4b202ac924d0b</t>
+          <t>https://www.indeed.com/viewjob?jk=2a7d736f0a5c3255</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>AI/ML Engineering Intern (Summer 2026)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Kharon</t>
+          <t>Poshmark</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>Redshift, Databricks, Spark, Scala, Kafka, MongoDB, MLflow, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,137 +1756,137 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1834ddbeb8ec8bb3</t>
+          <t>https://www.indeed.com/viewjob?jk=7fd3431b51acd4b5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Architect: Enterprise Data</t>
+          <t>Cloudera Public Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Mayer Brown LLP</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Plano, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced77385e81a71b8</t>
+          <t>https://www.indeed.com/viewjob?jk=ce7428fbc9c89fa9</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Full Stack Developer (JS/TS, AWS)</t>
+          <t>Site Reliability Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Low Associates</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>South Bend, IN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, Azure, GCP, Cloud Storage, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45727b1c951a0e5a</t>
+          <t>https://www.indeed.com/viewjob?jk=50c8f5c8b89d420d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Platform Operations Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Sunbit, Inc</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, CodeBuild</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1444a89356fbe315</t>
+          <t>https://www.indeed.com/viewjob?jk=62bcd4ad2d0bbc62</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Developer - Level III - 26-04057</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Panasonic Automotive</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Vertex AI, Spark, Scala, Spark Streaming, Kafka, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43063b055188ce3c</t>
+          <t>https://www.indeed.com/viewjob?jk=11ce688bd126a002</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Developer - Level III - 26-04057</t>
+          <t>DevOps &amp; AI Automation Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cc0ba82c4bd25dc</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6b296a0ce2f382</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Developer - Level III - 26-04057</t>
+          <t>Software Developer Internship</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, SQS, RDS, Azure, Kafka, DynamoDB, Power BI, Splunk, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eeb6502ebf78cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=c5ee38c644f00bbc</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Developer - Level III - 26-04057</t>
+          <t>Sr. Software Engineer - Data Infrastructure</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Santa Clarita, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, S3, RDS, GCP, HDFS, Hive, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=473b7754552ef179</t>
+          <t>https://www.indeed.com/viewjob?jk=df9f48d9232b00bf</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Developer - Level III - 26-04057</t>
+          <t>Senior Data Engineer - IICS</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>SYSTECH USA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lancaster, CA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Redshift, Cloud Storage, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e872365f29ac108</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf36b7e279da791</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr Business Intelligence Developer - Onsite</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Bass Pro Shops</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Glue, S3, RDS, Scala, Kafka, Snowflake, SQL Server, ETL, Tableau</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba1611f04cfe11a7</t>
+          <t>https://www.indeed.com/viewjob?jk=782f670b324716aa</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer (171680)</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,42 +2096,42 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Glue, S3, RDS, Scala, Kafka, Snowflake, SQL Server, ETL, Tableau</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a860d07867e70be2</t>
+          <t>https://www.indeed.com/viewjob?jk=65a4b202ac924d0b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Kharon</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
+          <t>AWS, S3, RDS, Databricks, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,67 +2141,67 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=523330c74b38a27b</t>
+          <t>https://www.indeed.com/viewjob?jk=1834ddbeb8ec8bb3</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior SRE</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>DEPARTMENT OF BUILDINGS</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, DynamoDB, Cassandra, NoSQL, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc41b902449ace0</t>
+          <t>https://www.indeed.com/viewjob?jk=2e9557f408354fe7</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Architect: Enterprise Data</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Mayer Brown LLP</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7beef8ad4f571f7a</t>
+          <t>https://www.indeed.com/viewjob?jk=ced77385e81a71b8</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Full Stack Developer, Smart Factory Solutions</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Magna International</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, S3, ECS, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3088b1f92a7a6242</t>
+          <t>https://www.indeed.com/viewjob?jk=a7d8d9f6032e5b6f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AI Cloud Security and Infrastructure Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Troutman Pepper Locke</t>
+          <t>Sunbit, Inc</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,67 +2281,67 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04325b074eb62665</t>
+          <t>https://www.indeed.com/viewjob?jk=1444a89356fbe315</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
+          <t>Full Stack Developer (JS/TS, AWS)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Low Associates</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>South Bend, IN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
+          <t>AWS, Lambda, API Gateway, IAM, Azure, GCP, Cloud Storage, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c20056a5b9ffca80</t>
+          <t>https://www.indeed.com/viewjob?jk=45727b1c951a0e5a</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer (SQL / Spark / Python)</t>
+          <t>Senior Developer - Level III - 26-04057</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>cloudteam</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, Oozie, YARN</t>
+          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ae648cd8fe57362</t>
+          <t>https://www.indeed.com/viewjob?jk=43063b055188ce3c</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>Senior Developer - Level III - 26-04057</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Holland &amp; Knight</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Brandon, FL, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, Airflow, Git</t>
+          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3abb3ed211255b11</t>
+          <t>https://www.indeed.com/viewjob?jk=6cc0ba82c4bd25dc</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Senior Developer - Level III - 26-04057</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
+          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766f2f5e9a7201f1</t>
+          <t>https://www.indeed.com/viewjob?jk=9eeb6502ebf78cc0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer 3 - III</t>
+          <t>Senior Developer - Level III - 26-04057</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>InterImage</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Santa Clarita, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
+          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16ddbf61e3ea0b92</t>
+          <t>https://www.indeed.com/viewjob?jk=473b7754552ef179</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer 3 - II</t>
+          <t>Senior Developer - Level III - 26-04057</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>InterImage</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Lancaster, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
+          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43bfe7ca1f6eddb7</t>
+          <t>https://www.indeed.com/viewjob?jk=5e872365f29ac108</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer 3 - I</t>
+          <t>Sr Business Intelligence Developer - Onsite</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>InterImage</t>
+          <t>Bass Pro Shops</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Dataflow, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2124d09922154cc4</t>
+          <t>https://www.indeed.com/viewjob?jk=ba1611f04cfe11a7</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>GIS Support Engineer</t>
+          <t>Database Engineer 3 - Contingent (contract)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, GCP, BigQuery, Hadoop, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e24b40c19089ff90</t>
+          <t>https://www.indeed.com/viewjob?jk=2b28c0b653e1b4d8</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer, Cat Digital Data &amp; AI</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=699bf154d150027f</t>
+          <t>https://www.indeed.com/viewjob?jk=523330c74b38a27b</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer (Full Stack)</t>
+          <t>Senior SRE</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, GCP, Scala, DynamoDB, Cassandra, NoSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39b5eeee4ff704ee</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc41b902449ace0</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SRE Architect</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,24 +2656,24 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Splunk, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=907826ed55a037a8</t>
+          <t>https://www.indeed.com/viewjob?jk=c254d2582994d51f</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Oracle, ETL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bca63339137d0189</t>
+          <t>https://www.indeed.com/viewjob?jk=7beef8ad4f571f7a</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deb135bf06a2110e</t>
+          <t>https://www.indeed.com/viewjob?jk=3088b1f92a7a6242</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Cloud Security and Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Troutman Pepper Locke</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2be9ee403cf20f67</t>
+          <t>https://www.indeed.com/viewjob?jk=04325b074eb62665</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=156e5a4def2a4a5d</t>
+          <t>https://www.indeed.com/viewjob?jk=c20056a5b9ffca80</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Analytic Data Engineer (Python/Power BI)</t>
+          <t>Data Engineer (SQL / Spark / Python)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Highmark Health</t>
+          <t>cloudteam</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, Oozie, YARN</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=100c60fa90e63408</t>
+          <t>https://www.indeed.com/viewjob?jk=6ae648cd8fe57362</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II</t>
+          <t>Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Holland &amp; Knight</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Brandon, FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Splunk, CI/CD, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, Airflow, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04a1d1c06680e371</t>
+          <t>https://www.indeed.com/viewjob?jk=3abb3ed211255b11</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Core &amp; Main</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,67 +2911,67 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5e2495e00e0060d</t>
+          <t>https://www.indeed.com/viewjob?jk=766f2f5e9a7201f1</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer - MN</t>
+          <t>Senior Architect - Data Architecture &amp; Engineering</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>RAZR Marketing, Inc.</t>
+          <t>CCG</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, PostgreSQL, Docker, Kubernetes, CloudWatch</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3375eb3b3d50ba05</t>
+          <t>https://www.indeed.com/viewjob?jk=819e894636bd2075</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Performance Test Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Core &amp; Main</t>
+          <t>TIAG</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, IAM, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2cdf5f4ac6a6c1a</t>
+          <t>https://www.indeed.com/viewjob?jk=82eb3dabcdfd111c</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Software Developer Architect (Cloud Services)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>WILLDAN GROUP</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a31dfca06d884ad</t>
+          <t>https://www.indeed.com/viewjob?jk=ec8ec9187f270065</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>SRE Architect</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>WILLDAN GROUP</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6b1cb632eed3bcb</t>
+          <t>https://www.indeed.com/viewjob?jk=907826ed55a037a8</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Data Engineer, Cat Digital Data &amp; AI</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>WILLDAN GROUP</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec090a150db0c5f8</t>
+          <t>https://www.indeed.com/viewjob?jk=699bf154d150027f</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Sr. Software QA Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>WILLDAN GROUP</t>
+          <t>Carlsmed</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fe79bacd5e58f55</t>
+          <t>https://www.indeed.com/viewjob?jk=f92907b243e51105</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>WILLDAN GROUP</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f09282ebd98b3570</t>
+          <t>https://www.indeed.com/viewjob?jk=39b5eeee4ff704ee</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>WILLDAN GROUP</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Oracle, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1d73f24fc01af9</t>
+          <t>https://www.indeed.com/viewjob?jk=bca63339137d0189</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>WILLDAN GROUP</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e4150c94fe908c8</t>
+          <t>https://www.indeed.com/viewjob?jk=3da1fa1569c709a3</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Metropolitan Companies</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Wyomissing, PA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, SQL Server, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12c03c3bb6ce8c38</t>
+          <t>https://www.indeed.com/viewjob?jk=deb135bf06a2110e</t>
         </is>
       </c>
     </row>
@@ -3273,12 +3273,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CardioOne</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34653b24bff70a46</t>
+          <t>https://www.indeed.com/viewjob?jk=2be9ee403cf20f67</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Supervisor, Software Engineering</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Energy Systems Group</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Newburgh, IN, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c197f77bdf171e6</t>
+          <t>https://www.indeed.com/viewjob?jk=156e5a4def2a4a5d</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst/Associate - New York</t>
+          <t>Senior Analytic Data Engineer (Python/Power BI)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Highmark Health</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, ETL, Power BI</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dd43ffc6d7fda89</t>
+          <t>https://www.indeed.com/viewjob?jk=100c60fa90e63408</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Experimentation Platform (Backend Services)</t>
+          <t>Sr. Software Engineer II</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Paramount Streaming</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, GCP, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Splunk, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f33593f93ffe80a</t>
+          <t>https://www.indeed.com/viewjob?jk=04a1d1c06680e371</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>IS Technical Specialist</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Core &amp; Main</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=757269b719268379</t>
+          <t>https://www.indeed.com/viewjob?jk=b5e2495e00e0060d</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>IS Technical Specialist</t>
+          <t>Senior Devops Engineer - MN</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>RAZR Marketing, Inc.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, PostgreSQL, Docker, Kubernetes, CloudWatch</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=609b33430f9df835</t>
+          <t>https://www.indeed.com/viewjob?jk=3375eb3b3d50ba05</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>IS Technical Specialist</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Core &amp; Main</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef377da6b1a8bbfd</t>
+          <t>https://www.indeed.com/viewjob?jk=b2cdf5f4ac6a6c1a</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>IS Technical Specialist</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aea6ee79779b03b</t>
+          <t>https://www.indeed.com/viewjob?jk=1a31dfca06d884ad</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>IS Technical Specialist</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Fairlawn, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da070db6e9060b88</t>
+          <t>https://www.indeed.com/viewjob?jk=f6b1cb632eed3bcb</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>IS Technical Specialist</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,15 +3601,610 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ec090a150db0c5f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Cloud Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>WILLDAN GROUP</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3fe79bacd5e58f55</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Cloud Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>WILLDAN GROUP</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f09282ebd98b3570</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Cloud Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>WILLDAN GROUP</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fa1d73f24fc01af9</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Cloud Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>WILLDAN GROUP</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e4150c94fe908c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Metropolitan Companies</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Wyomissing, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, SQL Server, ETL, ELT, Power BI, Tableau, CI/CD</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=12c03c3bb6ce8c38</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>CardioOne</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>CO, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=34653b24bff70a46</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Python Automation Developer</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest, Git, Python</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=023ea0e85c7b758a</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>CardioOne</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b44f024bbd36d11</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Experimentation Platform (Backend Services)</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Paramount Streaming</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, Redshift, RDS, GCP, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1f33593f93ffe80a</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst/Associate - New York</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1dd43ffc6d7fda89</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Supervisor, Software Engineering</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Energy Systems Group</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Newburgh, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9c197f77bdf171e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>IS Technical Specialist</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Huntington Bank</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
           <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=757269b719268379</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>IS Technical Specialist</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Huntington Bank</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=609b33430f9df835</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>IS Technical Specialist</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Huntington Bank</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef377da6b1a8bbfd</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>IS Technical Specialist</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Huntington Bank</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6aea6ee79779b03b</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>IS Technical Specialist</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Huntington Bank</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Fairlawn, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da070db6e9060b88</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>IS Technical Specialist</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Huntington Bank</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=63d188ef103369c5</t>
         </is>

--- a/results/job_matches_2026-04-16.xlsx
+++ b/results/job_matches_2026-04-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AWS Data Architect</t>
+          <t>Data Architect/Modeler</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Vertical Relevance</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=664db57e743f0c66</t>
+          <t>https://www.indeed.com/viewjob?jk=e10ec33698957c81</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Architect/Modeler</t>
+          <t>Analytics Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Infoverity</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Dublin, OH, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, S3, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e10ec33698957c81</t>
+          <t>https://www.indeed.com/viewjob?jk=ca5a94e3ea76c9da</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Analytics Architect</t>
+          <t>Databricks Data Architect - Consultant</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Infoverity</t>
+          <t>BluEnt</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dublin, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca5a94e3ea76c9da</t>
+          <t>https://www.indeed.com/viewjob?jk=8c12fb6e67e8bda7</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Architect, Senior</t>
+          <t>Application Developer, Portland Oregon</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Intermountain Health</t>
+          <t>Portland General Electric</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Murray, UT, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Event Hubs, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,182 +636,182 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8184ec5fc529fc27</t>
+          <t>https://www.indeed.com/viewjob?jk=f9f186e739ef98be</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Databricks Data Architect - Consultant</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BluEnt</t>
+          <t>HelioCampus</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Spark</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c12fb6e67e8bda7</t>
+          <t>https://www.indeed.com/viewjob?jk=333fbc294a529a0f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior ML Engineer - Agentic AI</t>
+          <t>Databricks Data Analyst</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Lincoln Financial Group</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ee08a694c71ee91</t>
+          <t>https://www.indeed.com/viewjob?jk=ce89a36f70a3941b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Application Developer, Portland Oregon</t>
+          <t>Senior Data Engineer – Credit Risk (Hybrid) - New York, NY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Portland General Electric</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9f186e739ef98be</t>
+          <t>https://www.indeed.com/viewjob?jk=23517bc36e765c0f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Engineer – Credit Risk (Hybrid) - New York, NY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HelioCampus</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=333fbc294a529a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=16e736022550c4c5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Databricks Data Analyst</t>
+          <t>Senior Data Engineer – Credit Risk (Hybrid) - New York, NY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce89a36f70a3941b</t>
+          <t>https://www.indeed.com/viewjob?jk=97b0320ba5b0219b</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Bronx, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23517bc36e765c0f</t>
+          <t>https://www.indeed.com/viewjob?jk=22e782dc41b4055e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Credit Risk (Hybrid) - New York, NY</t>
+          <t>Graph DBA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16e736022550c4c5</t>
+          <t>https://www.indeed.com/viewjob?jk=c15f03a1274f889c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Credit Risk (Hybrid) - New York, NY</t>
+          <t>Graph DBA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97b0320ba5b0219b</t>
+          <t>https://www.indeed.com/viewjob?jk=e8b5a8aa7c2f7cd5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Credit Risk (Hybrid) - New York, NY</t>
+          <t>Graph DBA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bronx, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22e782dc41b4055e</t>
+          <t>https://www.indeed.com/viewjob?jk=a0522d81a23e6425</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c15f03a1274f889c</t>
+          <t>https://www.indeed.com/viewjob?jk=10fa9278e203e8c7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Graph DBA</t>
+          <t>Sr Cloud Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Federal Reserve Bank of St. Louis</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,19 +1021,19 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8b5a8aa7c2f7cd5</t>
+          <t>https://www.indeed.com/viewjob?jk=af192f5dcbf84698</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Graph DBA</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>BLOC Resources, LLC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1042,46 +1042,46 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>Azure, Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0522d81a23e6425</t>
+          <t>https://www.indeed.com/viewjob?jk=d9e13379e16ee4b4</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Graph DBA</t>
+          <t>Sr. Consultant SW Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,67 +1091,67 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10fa9278e203e8c7</t>
+          <t>https://www.indeed.com/viewjob?jk=f337cce3b659c83d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Cloud Engineer</t>
+          <t>Associate IT Officer, Data and Information Management (Associate Data Engineer)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of St. Louis</t>
+          <t>World Bank Group</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af192f5dcbf84698</t>
+          <t>https://www.indeed.com/viewjob?jk=7a40cff6b5df03cd</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Data Engineer- OrderlyMeds</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BLOC Resources, LLC</t>
+          <t>OrderlyMeds</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,102 +1161,102 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9e13379e16ee4b4</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb2a73a0846955d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior, Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Cassandra</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe1513252d7f11af</t>
+          <t>https://www.indeed.com/viewjob?jk=3fcd1c4e67959eea</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Associate IT Officer, Data and Information Management (Associate Data Engineer)</t>
+          <t>Software Engineer III – Cloud Platform Engineering - Python / AWS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>World Bank Group</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, EMR, S3, ECS, RDS, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a40cff6b5df03cd</t>
+          <t>https://www.indeed.com/viewjob?jk=bb199efc831c0dc4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer- OrderlyMeds</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>OrderlyMeds</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, KS, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Azure Cosmos DB, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb2a73a0846955d</t>
+          <t>https://www.indeed.com/viewjob?jk=e9a02726d78410b5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Energy Services Group</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Databricks, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa4d88005315e7ba</t>
+          <t>https://www.indeed.com/viewjob?jk=6918de34da34b82a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Architecture Intern</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Smart Data Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d67805e12d384da2</t>
+          <t>https://www.indeed.com/viewjob?jk=b2a1afc987319b9a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior, Software Engineer</t>
+          <t>Data Engineer - Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Cassandra</t>
+          <t>RDS, Databricks, GCP, Spark, Scala, Kafka, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fcd1c4e67959eea</t>
+          <t>https://www.indeed.com/viewjob?jk=48617c6692425cb2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer III – Cloud Platform Engineering - Python / AWS</t>
+          <t>Machine Learning Engineer II (Remote)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Kohl's</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, ECS, RDS, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, ETL, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,67 +1406,67 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb199efc831c0dc4</t>
+          <t>https://www.indeed.com/viewjob?jk=2a7d736f0a5c3255</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloudera Public Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, KS, US USA</t>
+          <t>Plano, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Azure Cosmos DB, Data Modeling, ELT</t>
+          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9a02726d78410b5</t>
+          <t>https://www.indeed.com/viewjob?jk=ce7428fbc9c89fa9</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>DevOps &amp; AI Automation Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Energy Services Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6918de34da34b82a</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6b296a0ce2f382</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Sr. Software Engineer - Data Infrastructure</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, S3, RDS, GCP, HDFS, Hive, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2a1afc987319b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=df9f48d9232b00bf</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - Cloud Dev</t>
+          <t>Senior Data Engineer - IICS</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Transmedics</t>
+          <t>SYSTECH USA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Andover, MA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>AWS, Redshift, Cloud Storage, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,102 +1546,102 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2220b49620882d</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf36b7e279da791</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Enterprise Application Developer (Full Stack)</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Exponent</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, ECS, RDS, Azure, Scala, SQL Server</t>
+          <t>AWS, Glue, S3, RDS, Scala, Kafka, Snowflake, SQL Server, ETL, Tableau</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57406ee750d6ac9c</t>
+          <t>https://www.indeed.com/viewjob?jk=782f670b324716aa</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Warehouse Architect</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Databricks, GCP, Spark, Scala, Kafka, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, S3, RDS, Scala, Kafka, Snowflake, SQL Server, ETL, Tableau</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48617c6692425cb2</t>
+          <t>https://www.indeed.com/viewjob?jk=65a4b202ac924d0b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Enterprise Application Developer (Full Stack)</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Exponent</t>
+          <t>Kharon</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, ECS, RDS, Azure, Scala, SQL Server</t>
+          <t>AWS, S3, RDS, Databricks, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,67 +1651,67 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acf79124967bf4c3</t>
+          <t>https://www.indeed.com/viewjob?jk=1834ddbeb8ec8bb3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Data Platform Engineer | Digital Operations</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Beta Technologies</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>South Burlington, VT, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5acecf0e4305790</t>
+          <t>https://www.indeed.com/viewjob?jk=741939e568ff083b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II (Remote)</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Kohl's</t>
+          <t>DEPARTMENT OF BUILDINGS</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, ETL, MLOps, CI/CD, Docker</t>
+          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a7d736f0a5c3255</t>
+          <t>https://www.indeed.com/viewjob?jk=2e9557f408354fe7</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AI/ML Engineering Intern (Summer 2026)</t>
+          <t>Architect: Enterprise Data</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Poshmark</t>
+          <t>Mayer Brown LLP</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, Scala, Kafka, MongoDB, MLflow, Jenkins, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,137 +1756,137 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fd3431b51acd4b5</t>
+          <t>https://www.indeed.com/viewjob?jk=ced77385e81a71b8</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Cloudera Public Cloud Platform Engineer</t>
+          <t>Full Stack Developer (JS/TS, AWS)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Low Associates</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Plano, CA, US USA</t>
+          <t>South Bend, IN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, API Gateway, IAM, Azure, GCP, Cloud Storage, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce7428fbc9c89fa9</t>
+          <t>https://www.indeed.com/viewjob?jk=45727b1c951a0e5a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Site Reliability Architect</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Sunbit, Inc</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, Splunk, CI/CD</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c8f5c8b89d420d</t>
+          <t>https://www.indeed.com/viewjob?jk=1444a89356fbe315</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Platform Operations Engineer</t>
+          <t>Senior Developer - Level III - 26-04057</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, CodeBuild</t>
+          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62bcd4ad2d0bbc62</t>
+          <t>https://www.indeed.com/viewjob?jk=43063b055188ce3c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Senior Developer - Level III - 26-04057</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Panasonic Automotive</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, Spark, Scala, Spark Streaming, Kafka, MLOps, MLflow</t>
+          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11ce688bd126a002</t>
+          <t>https://www.indeed.com/viewjob?jk=6cc0ba82c4bd25dc</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DevOps &amp; AI Automation Engineer</t>
+          <t>Senior Developer - Level III - 26-04057</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6b296a0ce2f382</t>
+          <t>https://www.indeed.com/viewjob?jk=9eeb6502ebf78cc0</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Developer Internship</t>
+          <t>Senior Developer - Level III - 26-04057</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Santa Clarita, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, RDS, Azure, Kafka, DynamoDB, Power BI, Splunk, AWS CodePipeline</t>
+          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5ee38c644f00bbc</t>
+          <t>https://www.indeed.com/viewjob?jk=473b7754552ef179</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Data Infrastructure</t>
+          <t>Senior Developer - Level III - 26-04057</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lancaster, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, GCP, HDFS, Hive, Spark, Scala, Kafka, CI/CD</t>
+          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df9f48d9232b00bf</t>
+          <t>https://www.indeed.com/viewjob?jk=5e872365f29ac108</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - IICS</t>
+          <t>Sr Business Intelligence Developer - Onsite</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SYSTECH USA</t>
+          <t>Bass Pro Shops</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Cloud Storage, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf36b7e279da791</t>
+          <t>https://www.indeed.com/viewjob?jk=ba1611f04cfe11a7</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Database Engineer 3 - Contingent (contract)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Kafka, Snowflake, SQL Server, ETL, Tableau</t>
+          <t>AWS, Azure, GCP, BigQuery, Hadoop, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,67 +2071,67 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=782f670b324716aa</t>
+          <t>https://www.indeed.com/viewjob?jk=2b28c0b653e1b4d8</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Kafka, Snowflake, SQL Server, ETL, Tableau</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65a4b202ac924d0b</t>
+          <t>https://www.indeed.com/viewjob?jk=523330c74b38a27b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior SRE</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Kharon</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, GCP, Scala, DynamoDB, Cassandra, NoSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1834ddbeb8ec8bb3</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc41b902449ace0</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>DEPARTMENT OF BUILDINGS</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e9557f408354fe7</t>
+          <t>https://www.indeed.com/viewjob?jk=c254d2582994d51f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Architect: Enterprise Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Mayer Brown LLP</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced77385e81a71b8</t>
+          <t>https://www.indeed.com/viewjob?jk=7beef8ad4f571f7a</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer, Smart Factory Solutions</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Magna International</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7d8d9f6032e5b6f</t>
+          <t>https://www.indeed.com/viewjob?jk=3088b1f92a7a6242</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>AI Cloud Security and Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Sunbit, Inc</t>
+          <t>Troutman Pepper Locke</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,67 +2281,67 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1444a89356fbe315</t>
+          <t>https://www.indeed.com/viewjob?jk=04325b074eb62665</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Full Stack Developer (JS/TS, AWS)</t>
+          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Low Associates</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>South Bend, IN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, Azure, GCP, Cloud Storage, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45727b1c951a0e5a</t>
+          <t>https://www.indeed.com/viewjob?jk=c20056a5b9ffca80</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Developer - Level III - 26-04057</t>
+          <t>Data Engineer (SQL / Spark / Python)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>cloudteam</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, Oozie, YARN</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,67 +2351,67 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43063b055188ce3c</t>
+          <t>https://www.indeed.com/viewjob?jk=6ae648cd8fe57362</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Developer - Level III - 26-04057</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>API Gateway, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cc0ba82c4bd25dc</t>
+          <t>https://www.indeed.com/viewjob?jk=412ff8500fa79e71</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Developer - Level III - 26-04057</t>
+          <t>Data Engineer, Cat Digital Data &amp; AI</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eeb6502ebf78cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=699bf154d150027f</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Developer - Level III - 26-04057</t>
+          <t>Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Santa Clarita, CA, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=473b7754552ef179</t>
+          <t>https://www.indeed.com/viewjob?jk=39b5eeee4ff704ee</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Developer - Level III - 26-04057</t>
+          <t>SRE Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Lancaster, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e872365f29ac108</t>
+          <t>https://www.indeed.com/viewjob?jk=907826ed55a037a8</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr Business Intelligence Developer - Onsite</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Bass Pro Shops</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Oracle, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba1611f04cfe11a7</t>
+          <t>https://www.indeed.com/viewjob?jk=bca63339137d0189</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Database Engineer 3 - Contingent (contract)</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Hadoop, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,14 +2561,14 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b28c0b653e1b4d8</t>
+          <t>https://www.indeed.com/viewjob?jk=3da1fa1569c709a3</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2582,11 +2582,11 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=523330c74b38a27b</t>
+          <t>https://www.indeed.com/viewjob?jk=deb135bf06a2110e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior SRE</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, DynamoDB, Cassandra, NoSQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,67 +2631,67 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc41b902449ace0</t>
+          <t>https://www.indeed.com/viewjob?jk=2be9ee403cf20f67</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c254d2582994d51f</t>
+          <t>https://www.indeed.com/viewjob?jk=156e5a4def2a4a5d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analytic Data Engineer (Python/Power BI)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Highmark Health</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, ETL, Power BI</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7beef8ad4f571f7a</t>
+          <t>https://www.indeed.com/viewjob?jk=100c60fa90e63408</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Sr. Software Engineer II</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Splunk, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3088b1f92a7a6242</t>
+          <t>https://www.indeed.com/viewjob?jk=04a1d1c06680e371</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AI Cloud Security and Infrastructure Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Troutman Pepper Locke</t>
+          <t>Core &amp; Main</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04325b074eb62665</t>
+          <t>https://www.indeed.com/viewjob?jk=b5e2495e00e0060d</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
+          <t>Senior Devops Engineer - MN</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>RAZR Marketing, Inc.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, PostgreSQL, Docker, Kubernetes, CloudWatch</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c20056a5b9ffca80</t>
+          <t>https://www.indeed.com/viewjob?jk=3375eb3b3d50ba05</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer (SQL / Spark / Python)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>cloudteam</t>
+          <t>Core &amp; Main</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, Oozie, YARN</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ae648cd8fe57362</t>
+          <t>https://www.indeed.com/viewjob?jk=b2cdf5f4ac6a6c1a</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Holland &amp; Knight</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Brandon, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, Airflow, Git</t>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3abb3ed211255b11</t>
+          <t>https://www.indeed.com/viewjob?jk=1a31dfca06d884ad</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,67 +2911,67 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766f2f5e9a7201f1</t>
+          <t>https://www.indeed.com/viewjob?jk=f6b1cb632eed3bcb</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Architect - Data Architecture &amp; Engineering</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CCG</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server, Power BI, Azure DevOps</t>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=819e894636bd2075</t>
+          <t>https://www.indeed.com/viewjob?jk=ec090a150db0c5f8</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Performance Test Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>TIAG</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82eb3dabcdfd111c</t>
+          <t>https://www.indeed.com/viewjob?jk=3fe79bacd5e58f55</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Developer Architect (Cloud Services)</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec8ec9187f270065</t>
+          <t>https://www.indeed.com/viewjob?jk=f09282ebd98b3570</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SRE Architect</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Splunk, CI/CD, Terraform</t>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=907826ed55a037a8</t>
+          <t>https://www.indeed.com/viewjob?jk=fa1d73f24fc01af9</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer, Cat Digital Data &amp; AI</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,102 +3086,102 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=699bf154d150027f</t>
+          <t>https://www.indeed.com/viewjob?jk=7e4150c94fe908c8</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr. Software QA Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Carlsmed</t>
+          <t>CardioOne</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f92907b243e51105</t>
+          <t>https://www.indeed.com/viewjob?jk=34653b24bff70a46</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer (Full Stack)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>CardioOne</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39b5eeee4ff704ee</t>
+          <t>https://www.indeed.com/viewjob?jk=7b44f024bbd36d11</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst/Associate - New York</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Oracle, ETL, CI/CD, Git</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bca63339137d0189</t>
+          <t>https://www.indeed.com/viewjob?jk=1dd43ffc6d7fda89</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Senior Software Engineer, Experimentation Platform (Backend Services)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Paramount Streaming</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
+          <t>AWS, Kinesis, Redshift, RDS, GCP, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3da1fa1569c709a3</t>
+          <t>https://www.indeed.com/viewjob?jk=1f33593f93ffe80a</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>IS Technical Specialist</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deb135bf06a2110e</t>
+          <t>https://www.indeed.com/viewjob?jk=757269b719268379</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>IS Technical Specialist</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2be9ee403cf20f67</t>
+          <t>https://www.indeed.com/viewjob?jk=609b33430f9df835</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>IS Technical Specialist</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=156e5a4def2a4a5d</t>
+          <t>https://www.indeed.com/viewjob?jk=ef377da6b1a8bbfd</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Analytic Data Engineer (Python/Power BI)</t>
+          <t>IS Technical Specialist</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Highmark Health</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, ETL, Power BI</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=100c60fa90e63408</t>
+          <t>https://www.indeed.com/viewjob?jk=6aea6ee79779b03b</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II</t>
+          <t>IS Technical Specialist</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Fairlawn, OH, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Splunk, CI/CD, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04a1d1c06680e371</t>
+          <t>https://www.indeed.com/viewjob?jk=da070db6e9060b88</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>IS Technical Specialist</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Core &amp; Main</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3435,776 +3435,6 @@
         </is>
       </c>
       <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b5e2495e00e0060d</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Senior Devops Engineer - MN</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>RAZR Marketing, Inc.</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Minnetonka, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, PostgreSQL, Docker, Kubernetes, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3375eb3b3d50ba05</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Data Engineer II</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Core &amp; Main</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>OH, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b2cdf5f4ac6a6c1a</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Cloud Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>WILLDAN GROUP</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1a31dfca06d884ad</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Cloud Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>WILLDAN GROUP</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f6b1cb632eed3bcb</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Cloud Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>WILLDAN GROUP</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ec090a150db0c5f8</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Cloud Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>WILLDAN GROUP</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3fe79bacd5e58f55</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Cloud Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>WILLDAN GROUP</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f09282ebd98b3570</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Cloud Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>WILLDAN GROUP</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1d73f24fc01af9</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Cloud Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>WILLDAN GROUP</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7e4150c94fe908c8</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Metropolitan Companies</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Wyomissing, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, SQL Server, ETL, ELT, Power BI, Tableau, CI/CD</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=12c03c3bb6ce8c38</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>CardioOne</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>CO, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=34653b24bff70a46</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Python Automation Developer</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest, Git, Python</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=023ea0e85c7b758a</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>CardioOne</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7b44f024bbd36d11</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Experimentation Platform (Backend Services)</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Paramount Streaming</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, Redshift, RDS, GCP, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1f33593f93ffe80a</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst/Associate - New York</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Goldman Sachs</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1dd43ffc6d7fda89</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Supervisor, Software Engineering</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Energy Systems Group</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Newburgh, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9c197f77bdf171e6</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>IS Technical Specialist</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Huntington Bank</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=757269b719268379</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>IS Technical Specialist</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Huntington Bank</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Cleveland, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=609b33430f9df835</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>IS Technical Specialist</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Huntington Bank</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Cincinnati, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ef377da6b1a8bbfd</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>IS Technical Specialist</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Huntington Bank</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6aea6ee79779b03b</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>IS Technical Specialist</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Huntington Bank</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Fairlawn, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=da070db6e9060b88</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>IS Technical Specialist</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Huntington Bank</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=63d188ef103369c5</t>
         </is>

--- a/results/job_matches_2026-04-16.xlsx
+++ b/results/job_matches_2026-04-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G86"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,12 +573,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Databricks Data Architect - Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BluEnt</t>
+          <t>Veeva Systems</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Spark</t>
+          <t>AWS, EMR, Kinesis, Step Functions, RDS, Databricks, Medallion Architecture, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c12fb6e67e8bda7</t>
+          <t>https://www.indeed.com/viewjob?jk=a83dccf18841adf6</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Application Developer, Portland Oregon</t>
+          <t>Databricks Data Architect - Consultant</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Portland General Electric</t>
+          <t>BluEnt</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,42 +626,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9f186e739ef98be</t>
+          <t>https://www.indeed.com/viewjob?jk=8c12fb6e67e8bda7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Application Developer, Portland Oregon</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HelioCampus</t>
+          <t>Portland General Electric</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=333fbc294a529a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=f9f186e739ef98be</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Databricks Data Analyst</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>HelioCampus</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,52 +696,52 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce89a36f70a3941b</t>
+          <t>https://www.indeed.com/viewjob?jk=333fbc294a529a0f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Credit Risk (Hybrid) - New York, NY</t>
+          <t>Databricks Data Analyst</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Lincoln Financial Group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23517bc36e765c0f</t>
+          <t>https://www.indeed.com/viewjob?jk=ce89a36f70a3941b</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16e736022550c4c5</t>
+          <t>https://www.indeed.com/viewjob?jk=23517bc36e765c0f</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97b0320ba5b0219b</t>
+          <t>https://www.indeed.com/viewjob?jk=16e736022550c4c5</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bronx, NY, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22e782dc41b4055e</t>
+          <t>https://www.indeed.com/viewjob?jk=97b0320ba5b0219b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Graph DBA</t>
+          <t>Senior Data Engineer – Credit Risk (Hybrid) - New York, NY</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Bronx, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c15f03a1274f889c</t>
+          <t>https://www.indeed.com/viewjob?jk=22e782dc41b4055e</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8b5a8aa7c2f7cd5</t>
+          <t>https://www.indeed.com/viewjob?jk=c15f03a1274f889c</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0522d81a23e6425</t>
+          <t>https://www.indeed.com/viewjob?jk=e8b5a8aa7c2f7cd5</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10fa9278e203e8c7</t>
+          <t>https://www.indeed.com/viewjob?jk=a0522d81a23e6425</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr Cloud Engineer</t>
+          <t>Graph DBA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of St. Louis</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af192f5dcbf84698</t>
+          <t>https://www.indeed.com/viewjob?jk=10fa9278e203e8c7</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Sr Cloud Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BLOC Resources, LLC</t>
+          <t>Federal Reserve Bank of St. Louis</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9e13379e16ee4b4</t>
+          <t>https://www.indeed.com/viewjob?jk=af192f5dcbf84698</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Consultant SW Engineer</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>BLOC Resources, LLC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,69 +1081,69 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>Azure, Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f337cce3b659c83d</t>
+          <t>https://www.indeed.com/viewjob?jk=d9e13379e16ee4b4</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Associate IT Officer, Data and Information Management (Associate Data Engineer)</t>
+          <t>Sr. Consultant SW Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>World Bank Group</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a40cff6b5df03cd</t>
+          <t>https://www.indeed.com/viewjob?jk=f337cce3b659c83d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer- OrderlyMeds</t>
+          <t>Associate IT Officer, Data and Information Management (Associate Data Engineer)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>OrderlyMeds</t>
+          <t>World Bank Group</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb2a73a0846955d</t>
+          <t>https://www.indeed.com/viewjob?jk=7a40cff6b5df03cd</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior, Software Engineer</t>
+          <t>Data Engineer- OrderlyMeds</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>OrderlyMeds</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Cassandra</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fcd1c4e67959eea</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb2a73a0846955d</t>
         </is>
       </c>
     </row>
@@ -1308,17 +1308,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Unissant</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,17 +1326,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2a1afc987319b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=a00da07441b7a67f</t>
         </is>
       </c>
     </row>
@@ -1448,52 +1448,52 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DevOps &amp; AI Automation Engineer</t>
+          <t>DEVELOPER L3(CONTRACT)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wayne, PA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6b296a0ce2f382</t>
+          <t>https://www.indeed.com/viewjob?jk=0e2ca368a02b432d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Data Infrastructure</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, GCP, HDFS, Hive, Spark, Scala, Kafka, CI/CD</t>
+          <t>AWS, Glue, S3, RDS, Scala, Kafka, Snowflake, SQL Server, ETL, Tableau</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df9f48d9232b00bf</t>
+          <t>https://www.indeed.com/viewjob?jk=782f670b324716aa</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - IICS</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SYSTECH USA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Cloud Storage, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, S3, RDS, Scala, Kafka, Snowflake, SQL Server, ETL, Tableau</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf36b7e279da791</t>
+          <t>https://www.indeed.com/viewjob?jk=65a4b202ac924d0b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Kharon</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Kafka, Snowflake, SQL Server, ETL, Tableau</t>
+          <t>AWS, S3, RDS, Databricks, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=782f670b324716aa</t>
+          <t>https://www.indeed.com/viewjob?jk=1834ddbeb8ec8bb3</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Data Engineer - IICS</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SYSTECH USA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Kafka, Snowflake, SQL Server, ETL, Tableau</t>
+          <t>AWS, Redshift, Cloud Storage, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65a4b202ac924d0b</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf36b7e279da791</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Data Platform Engineer | Digital Operations</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Kharon</t>
+          <t>Beta Technologies</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>South Burlington, VT, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1834ddbeb8ec8bb3</t>
+          <t>https://www.indeed.com/viewjob?jk=741939e568ff083b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Platform Engineer | Digital Operations</t>
+          <t>Sr. Software Engineer - Data Infrastructure</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Beta Technologies</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>South Burlington, VT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, GCP, HDFS, Hive, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=741939e568ff083b</t>
+          <t>https://www.indeed.com/viewjob?jk=df9f48d9232b00bf</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>DEPARTMENT OF BUILDINGS</t>
+          <t>IWCO</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chanhassen, MN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e9557f408354fe7</t>
+          <t>https://www.indeed.com/viewjob?jk=196d52ca727cd7dc</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Architect: Enterprise Data</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Mayer Brown LLP</t>
+          <t>DEPARTMENT OF BUILDINGS</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced77385e81a71b8</t>
+          <t>https://www.indeed.com/viewjob?jk=2e9557f408354fe7</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Full Stack Developer (JS/TS, AWS)</t>
+          <t>Architect: Enterprise Data</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Low Associates</t>
+          <t>Mayer Brown LLP</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>South Bend, IN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, Azure, GCP, Cloud Storage, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>RDS, Azure, Data Factory, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45727b1c951a0e5a</t>
+          <t>https://www.indeed.com/viewjob?jk=ced77385e81a71b8</t>
         </is>
       </c>
     </row>
@@ -2078,17 +2078,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=523330c74b38a27b</t>
+          <t>https://www.indeed.com/viewjob?jk=c254d2582994d51f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior SRE</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, DynamoDB, Cassandra, NoSQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc41b902449ace0</t>
+          <t>https://www.indeed.com/viewjob?jk=523330c74b38a27b</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c254d2582994d51f</t>
+          <t>https://www.indeed.com/viewjob?jk=7beef8ad4f571f7a</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7beef8ad4f571f7a</t>
+          <t>https://www.indeed.com/viewjob?jk=3088b1f92a7a6242</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior SRE</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, GCP, Scala, DynamoDB, Cassandra, NoSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3088b1f92a7a6242</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc41b902449ace0</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AI Cloud Security and Infrastructure Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Troutman Pepper Locke</t>
+          <t>COVERCRAFT INDUSTRIES</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,24 +2271,24 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04325b074eb62665</t>
+          <t>https://www.indeed.com/viewjob?jk=d5dc2c7f7fff79d2</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
+          <t>API Gateway, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c20056a5b9ffca80</t>
+          <t>https://www.indeed.com/viewjob?jk=412ff8500fa79e71</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer (SQL / Spark / Python)</t>
+          <t>Data Engineer, Cat Digital Data &amp; AI</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>cloudteam</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, Oozie, YARN</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ae648cd8fe57362</t>
+          <t>https://www.indeed.com/viewjob?jk=699bf154d150027f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>API Gateway, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=412ff8500fa79e71</t>
+          <t>https://www.indeed.com/viewjob?jk=39b5eeee4ff704ee</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer, Cat Digital Data &amp; AI</t>
+          <t>SRE Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=699bf154d150027f</t>
+          <t>https://www.indeed.com/viewjob?jk=907826ed55a037a8</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer (Full Stack)</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Oracle, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,94 +2456,94 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39b5eeee4ff704ee</t>
+          <t>https://www.indeed.com/viewjob?jk=bca63339137d0189</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SRE Architect</t>
+          <t>Cloud Infrastructure Engineer Prin</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Splunk, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=907826ed55a037a8</t>
+          <t>https://www.indeed.com/viewjob?jk=e17559f247cbc51a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Oracle, ETL, CI/CD, Git</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bca63339137d0189</t>
+          <t>https://www.indeed.com/viewjob?jk=3da1fa1569c709a3</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Core &amp; Main</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,17 +2551,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3da1fa1569c709a3</t>
+          <t>https://www.indeed.com/viewjob?jk=b5e2495e00e0060d</t>
         </is>
       </c>
     </row>
@@ -2603,17 +2603,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Devops Engineer - MN</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>RAZR Marketing, Inc.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, PostgreSQL, Docker, Kubernetes, CloudWatch</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2be9ee403cf20f67</t>
+          <t>https://www.indeed.com/viewjob?jk=3375eb3b3d50ba05</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Core &amp; Main</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=156e5a4def2a4a5d</t>
+          <t>https://www.indeed.com/viewjob?jk=b2cdf5f4ac6a6c1a</t>
         </is>
       </c>
     </row>
@@ -2708,17 +2708,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Splunk, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04a1d1c06680e371</t>
+          <t>https://www.indeed.com/viewjob?jk=2be9ee403cf20f67</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Core &amp; Main</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5e2495e00e0060d</t>
+          <t>https://www.indeed.com/viewjob?jk=156e5a4def2a4a5d</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer - MN</t>
+          <t>Java backend data engineer - Smithfield RI</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>RAZR Marketing, Inc.</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, PostgreSQL, Docker, Kubernetes, CloudWatch</t>
+          <t>AWS, S3, Snowflake, Oracle, Data Modeling, Star Schema, Jenkins, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3375eb3b3d50ba05</t>
+          <t>https://www.indeed.com/viewjob?jk=3d795ea45cb03ea9</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Core &amp; Main</t>
+          <t>CardioOne</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2cdf5f4ac6a6c1a</t>
+          <t>https://www.indeed.com/viewjob?jk=34653b24bff70a46</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>WILLDAN GROUP</t>
+          <t>CardioOne</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a31dfca06d884ad</t>
+          <t>https://www.indeed.com/viewjob?jk=7b44f024bbd36d11</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst/Associate - New York</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>WILLDAN GROUP</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6b1cb632eed3bcb</t>
+          <t>https://www.indeed.com/viewjob?jk=1dd43ffc6d7fda89</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Senior Software Engineer, Experimentation Platform (Backend Services)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>WILLDAN GROUP</t>
+          <t>Paramount Streaming</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, Redshift, RDS, GCP, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,497 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec090a150db0c5f8</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Cloud Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>WILLDAN GROUP</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3fe79bacd5e58f55</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Cloud Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>WILLDAN GROUP</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f09282ebd98b3570</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Cloud Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>WILLDAN GROUP</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1d73f24fc01af9</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Cloud Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>WILLDAN GROUP</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, S3, ECS, IAM, RDS, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7e4150c94fe908c8</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>CardioOne</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>CO, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=34653b24bff70a46</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>CardioOne</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7b44f024bbd36d11</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst/Associate - New York</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Goldman Sachs</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1dd43ffc6d7fda89</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Experimentation Platform (Backend Services)</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Paramount Streaming</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, Redshift, RDS, GCP, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=1f33593f93ffe80a</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>IS Technical Specialist</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Huntington Bank</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=757269b719268379</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>IS Technical Specialist</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Huntington Bank</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Cleveland, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=609b33430f9df835</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>IS Technical Specialist</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Huntington Bank</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Cincinnati, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ef377da6b1a8bbfd</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>IS Technical Specialist</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Huntington Bank</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6aea6ee79779b03b</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>IS Technical Specialist</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Huntington Bank</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Fairlawn, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=da070db6e9060b88</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>IS Technical Specialist</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Huntington Bank</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=63d188ef103369c5</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-16.xlsx
+++ b/results/job_matches_2026-04-16.xlsx
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Credit Risk (Hybrid) - New York, NY</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>EssilorLuxottica</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23517bc36e765c0f</t>
+          <t>https://www.indeed.com/viewjob?jk=cb1eb66e038f22b4</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16e736022550c4c5</t>
+          <t>https://www.indeed.com/viewjob?jk=23517bc36e765c0f</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97b0320ba5b0219b</t>
+          <t>https://www.indeed.com/viewjob?jk=16e736022550c4c5</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bronx, NY, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22e782dc41b4055e</t>
+          <t>https://www.indeed.com/viewjob?jk=97b0320ba5b0219b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Graph DBA</t>
+          <t>Senior Data Engineer – Credit Risk (Hybrid) - New York, NY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Bronx, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c15f03a1274f889c</t>
+          <t>https://www.indeed.com/viewjob?jk=22e782dc41b4055e</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8b5a8aa7c2f7cd5</t>
+          <t>https://www.indeed.com/viewjob?jk=c15f03a1274f889c</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0522d81a23e6425</t>
+          <t>https://www.indeed.com/viewjob?jk=e8b5a8aa7c2f7cd5</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10fa9278e203e8c7</t>
+          <t>https://www.indeed.com/viewjob?jk=a0522d81a23e6425</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Cloud Engineer</t>
+          <t>Graph DBA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of St. Louis</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af192f5dcbf84698</t>
+          <t>https://www.indeed.com/viewjob?jk=10fa9278e203e8c7</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Sr Cloud Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BLOC Resources, LLC</t>
+          <t>Federal Reserve Bank of St. Louis</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9e13379e16ee4b4</t>
+          <t>https://www.indeed.com/viewjob?jk=af192f5dcbf84698</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Consultant SW Engineer</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>BLOC Resources, LLC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,69 +1116,69 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>Azure, Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f337cce3b659c83d</t>
+          <t>https://www.indeed.com/viewjob?jk=d9e13379e16ee4b4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Associate IT Officer, Data and Information Management (Associate Data Engineer)</t>
+          <t>Sr. Consultant SW Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>World Bank Group</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a40cff6b5df03cd</t>
+          <t>https://www.indeed.com/viewjob?jk=f337cce3b659c83d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer- OrderlyMeds</t>
+          <t>Associate IT Officer, Data and Information Management (Associate Data Engineer)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>OrderlyMeds</t>
+          <t>World Bank Group</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,59 +1196,59 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb2a73a0846955d</t>
+          <t>https://www.indeed.com/viewjob?jk=7a40cff6b5df03cd</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer III – Cloud Platform Engineering - Python / AWS</t>
+          <t>Data Engineer- OrderlyMeds</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>OrderlyMeds</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, ECS, RDS, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb199efc831c0dc4</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb2a73a0846955d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III – Cloud Platform Engineering - Python / AWS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, KS, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Azure Cosmos DB, Data Modeling, ELT</t>
+          <t>AWS, EMR, S3, ECS, RDS, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9a02726d78410b5</t>
+          <t>https://www.indeed.com/viewjob?jk=bb199efc831c0dc4</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Energy Services Group</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Atlanta, KS, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Azure Cosmos DB, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6918de34da34b82a</t>
+          <t>https://www.indeed.com/viewjob?jk=e9a02726d78410b5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Unissant</t>
+          <t>Energy Services Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00da07441b7a67f</t>
+          <t>https://www.indeed.com/viewjob?jk=6918de34da34b82a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Warehouse Architect</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>Trepp</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,42 +1361,42 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Databricks, GCP, Spark, Scala, Kafka, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48617c6692425cb2</t>
+          <t>https://www.indeed.com/viewjob?jk=793bcf53c033205f</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II (Remote)</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Kohl's</t>
+          <t>Unissant</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, ETL, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,67 +1406,67 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a7d736f0a5c3255</t>
+          <t>https://www.indeed.com/viewjob?jk=a00da07441b7a67f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cloudera Public Cloud Platform Engineer</t>
+          <t>Data Engineer - Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Plano, CA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, GCP, Hive, Impala, Spark, Scala, Kafka</t>
+          <t>RDS, Databricks, GCP, Spark, Scala, Kafka, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce7428fbc9c89fa9</t>
+          <t>https://www.indeed.com/viewjob?jk=48617c6692425cb2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DEVELOPER L3(CONTRACT)</t>
+          <t>Machine Learning Engineer II (Remote)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Kohl's</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Wayne, PA, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, ETL, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e2ca368a02b432d</t>
+          <t>https://www.indeed.com/viewjob?jk=2a7d736f0a5c3255</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior SRE I</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Kafka, Snowflake, SQL Server, ETL, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=782f670b324716aa</t>
+          <t>https://www.indeed.com/viewjob?jk=389e6808cb55dd7e</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>DEVELOPER L3(CONTRACT)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Wayne, PA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Kafka, Snowflake, SQL Server, ETL, Tableau</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65a4b202ac924d0b</t>
+          <t>https://www.indeed.com/viewjob?jk=0e2ca368a02b432d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Kharon</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Glue, S3, RDS, Scala, Kafka, Snowflake, SQL Server, ETL, Tableau</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1834ddbeb8ec8bb3</t>
+          <t>https://www.indeed.com/viewjob?jk=782f670b324716aa</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - IICS</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SYSTECH USA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Cloud Storage, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, S3, RDS, Scala, Kafka, Snowflake, SQL Server, ETL, Tableau</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf36b7e279da791</t>
+          <t>https://www.indeed.com/viewjob?jk=65a4b202ac924d0b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Platform Engineer | Digital Operations</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Beta Technologies</t>
+          <t>Kharon</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>South Burlington, VT, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Databricks, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=741939e568ff083b</t>
+          <t>https://www.indeed.com/viewjob?jk=1834ddbeb8ec8bb3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Data Infrastructure</t>
+          <t>Senior Data Engineer - IICS</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>SYSTECH USA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, GCP, HDFS, Hive, Spark, Scala, Kafka, CI/CD</t>
+          <t>AWS, Redshift, Cloud Storage, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df9f48d9232b00bf</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf36b7e279da791</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Data Platform Engineer | Digital Operations</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>IWCO</t>
+          <t>Beta Technologies</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chanhassen, MN, US USA</t>
+          <t>South Burlington, VT, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,29 +1711,29 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=196d52ca727cd7dc</t>
+          <t>https://www.indeed.com/viewjob?jk=741939e568ff083b</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Sr. Software Engineer - Data Infrastructure</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>DEPARTMENT OF BUILDINGS</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, GCP, HDFS, Hive, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e9557f408354fe7</t>
+          <t>https://www.indeed.com/viewjob?jk=df9f48d9232b00bf</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Architect: Enterprise Data</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Mayer Brown LLP</t>
+          <t>IWCO</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Chanhassen, MN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,29 +1781,29 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced77385e81a71b8</t>
+          <t>https://www.indeed.com/viewjob?jk=196d52ca727cd7dc</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Sunbit, Inc</t>
+          <t>DEPARTMENT OF BUILDINGS</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
+          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1444a89356fbe315</t>
+          <t>https://www.indeed.com/viewjob?jk=2e9557f408354fe7</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Developer - Level III - 26-04057</t>
+          <t>Architect: Enterprise Data</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Mayer Brown LLP</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43063b055188ce3c</t>
+          <t>https://www.indeed.com/viewjob?jk=ced77385e81a71b8</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Developer - Level III - 26-04057</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Sunbit, Inc</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cc0ba82c4bd25dc</t>
+          <t>https://www.indeed.com/viewjob?jk=1444a89356fbe315</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eeb6502ebf78cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=43063b055188ce3c</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Santa Clarita, CA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=473b7754552ef179</t>
+          <t>https://www.indeed.com/viewjob?jk=6cc0ba82c4bd25dc</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Lancaster, CA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e872365f29ac108</t>
+          <t>https://www.indeed.com/viewjob?jk=9eeb6502ebf78cc0</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr Business Intelligence Developer - Onsite</t>
+          <t>Senior Developer - Level III - 26-04057</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Bass Pro Shops</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Santa Clarita, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,94 +2036,94 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba1611f04cfe11a7</t>
+          <t>https://www.indeed.com/viewjob?jk=473b7754552ef179</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Database Engineer 3 - Contingent (contract)</t>
+          <t>Senior Developer - Level III - 26-04057</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Lancaster, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Hadoop, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b28c0b653e1b4d8</t>
+          <t>https://www.indeed.com/viewjob?jk=5e872365f29ac108</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Sr Business Intelligence Developer - Onsite</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Bass Pro Shops</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c254d2582994d51f</t>
+          <t>https://www.indeed.com/viewjob?jk=ba1611f04cfe11a7</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Database Engineer 3 - Contingent (contract)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Azure, GCP, BigQuery, Hadoop, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=523330c74b38a27b</t>
+          <t>https://www.indeed.com/viewjob?jk=2b28c0b653e1b4d8</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7beef8ad4f571f7a</t>
+          <t>https://www.indeed.com/viewjob?jk=c254d2582994d51f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3088b1f92a7a6242</t>
+          <t>https://www.indeed.com/viewjob?jk=523330c74b38a27b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior SRE</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, DynamoDB, Cassandra, NoSQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc41b902449ace0</t>
+          <t>https://www.indeed.com/viewjob?jk=7beef8ad4f571f7a</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>COVERCRAFT INDUSTRIES</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5dc2c7f7fff79d2</t>
+          <t>https://www.indeed.com/viewjob?jk=3088b1f92a7a6242</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Senior SRE</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>API Gateway, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, Scala, DynamoDB, Cassandra, NoSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=412ff8500fa79e71</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc41b902449ace0</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer, Cat Digital Data &amp; AI</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>COVERCRAFT INDUSTRIES</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=699bf154d150027f</t>
+          <t>https://www.indeed.com/viewjob?jk=d5dc2c7f7fff79d2</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer (Full Stack)</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
+          <t>API Gateway, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39b5eeee4ff704ee</t>
+          <t>https://www.indeed.com/viewjob?jk=412ff8500fa79e71</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SRE Architect</t>
+          <t>Data Engineer, Cat Digital Data &amp; AI</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Splunk, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=907826ed55a037a8</t>
+          <t>https://www.indeed.com/viewjob?jk=699bf154d150027f</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Oracle, ETL, CI/CD, Git</t>
+          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,94 +2456,94 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bca63339137d0189</t>
+          <t>https://www.indeed.com/viewjob?jk=39b5eeee4ff704ee</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer Prin</t>
+          <t>SRE Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e17559f247cbc51a</t>
+          <t>https://www.indeed.com/viewjob?jk=907826ed55a037a8</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Oracle, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3da1fa1569c709a3</t>
+          <t>https://www.indeed.com/viewjob?jk=bca63339137d0189</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Cloud Infrastructure Engineer Prin</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Core &amp; Main</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5e2495e00e0060d</t>
+          <t>https://www.indeed.com/viewjob?jk=e17559f247cbc51a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deb135bf06a2110e</t>
+          <t>https://www.indeed.com/viewjob?jk=3da1fa1569c709a3</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer - MN</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>RAZR Marketing, Inc.</t>
+          <t>Core &amp; Main</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, PostgreSQL, Docker, Kubernetes, CloudWatch</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3375eb3b3d50ba05</t>
+          <t>https://www.indeed.com/viewjob?jk=b5e2495e00e0060d</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Core &amp; Main</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2cdf5f4ac6a6c1a</t>
+          <t>https://www.indeed.com/viewjob?jk=deb135bf06a2110e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Analytic Data Engineer (Python/Power BI)</t>
+          <t>Senior Devops Engineer - MN</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Highmark Health</t>
+          <t>RAZR Marketing, Inc.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, ETL, Power BI</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, PostgreSQL, Docker, Kubernetes, CloudWatch</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=100c60fa90e63408</t>
+          <t>https://www.indeed.com/viewjob?jk=3375eb3b3d50ba05</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Core &amp; Main</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2be9ee403cf20f67</t>
+          <t>https://www.indeed.com/viewjob?jk=b2cdf5f4ac6a6c1a</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Analytic Data Engineer (Python/Power BI)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Highmark Health</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, ETL, Power BI</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=156e5a4def2a4a5d</t>
+          <t>https://www.indeed.com/viewjob?jk=100c60fa90e63408</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Java backend data engineer - Smithfield RI</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, Snowflake, Oracle, Data Modeling, Star Schema, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Splunk, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d795ea45cb03ea9</t>
+          <t>https://www.indeed.com/viewjob?jk=f589c151e81c3302</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Java backend data engineer - Smithfield RI</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CardioOne</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, S3, Snowflake, Oracle, Data Modeling, Star Schema, Jenkins, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34653b24bff70a46</t>
+          <t>https://www.indeed.com/viewjob?jk=3d795ea45cb03ea9</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2871,29 +2871,29 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b44f024bbd36d11</t>
+          <t>https://www.indeed.com/viewjob?jk=34653b24bff70a46</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst/Associate - New York</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>CardioOne</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,17 +2901,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dd43ffc6d7fda89</t>
+          <t>https://www.indeed.com/viewjob?jk=7b44f024bbd36d11</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-16.xlsx
+++ b/results/job_matches_2026-04-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,47 +538,47 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Analytics Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Infoverity</t>
+          <t>Veeva Systems</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dublin, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, EMR, Kinesis, Step Functions, RDS, Databricks, Medallion Architecture, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca5a94e3ea76c9da</t>
+          <t>https://www.indeed.com/viewjob?jk=a83dccf18841adf6</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Data Architect - Consultant</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Veeva Systems</t>
+          <t>BluEnt</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Step Functions, RDS, Databricks, Medallion Architecture, GCP, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83dccf18841adf6</t>
+          <t>https://www.indeed.com/viewjob?jk=8c12fb6e67e8bda7</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Databricks Data Architect - Consultant</t>
+          <t>Application Developer, Portland Oregon</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BluEnt</t>
+          <t>Portland General Electric</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,42 +626,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Spark</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c12fb6e67e8bda7</t>
+          <t>https://www.indeed.com/viewjob?jk=f9f186e739ef98be</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Application Developer, Portland Oregon</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Portland General Electric</t>
+          <t>HelioCampus</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9f186e739ef98be</t>
+          <t>https://www.indeed.com/viewjob?jk=333fbc294a529a0f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Kafka Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HelioCampus</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,69 +696,69 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=333fbc294a529a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=288d8ed989f5e263</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Databricks Data Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>EssilorLuxottica</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce89a36f70a3941b</t>
+          <t>https://www.indeed.com/viewjob?jk=cb1eb66e038f22b4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer – Credit Risk (Hybrid) - New York, NY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EssilorLuxottica</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb1eb66e038f22b4</t>
+          <t>https://www.indeed.com/viewjob?jk=23517bc36e765c0f</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23517bc36e765c0f</t>
+          <t>https://www.indeed.com/viewjob?jk=16e736022550c4c5</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16e736022550c4c5</t>
+          <t>https://www.indeed.com/viewjob?jk=97b0320ba5b0219b</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Bronx, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97b0320ba5b0219b</t>
+          <t>https://www.indeed.com/viewjob?jk=22e782dc41b4055e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Credit Risk (Hybrid) - New York, NY</t>
+          <t>Graph DBA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bronx, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22e782dc41b4055e</t>
+          <t>https://www.indeed.com/viewjob?jk=c15f03a1274f889c</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c15f03a1274f889c</t>
+          <t>https://www.indeed.com/viewjob?jk=e8b5a8aa7c2f7cd5</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8b5a8aa7c2f7cd5</t>
+          <t>https://www.indeed.com/viewjob?jk=a0522d81a23e6425</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,59 +1021,59 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0522d81a23e6425</t>
+          <t>https://www.indeed.com/viewjob?jk=10fa9278e203e8c7</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Graph DBA</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>BLOC Resources, LLC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>Azure, Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10fa9278e203e8c7</t>
+          <t>https://www.indeed.com/viewjob?jk=d9e13379e16ee4b4</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr Cloud Engineer</t>
+          <t>Sr. Consultant SW Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of St. Louis</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af192f5dcbf84698</t>
+          <t>https://www.indeed.com/viewjob?jk=f337cce3b659c83d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Associate IT Officer, Data and Information Management (Associate Data Engineer)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BLOC Resources, LLC</t>
+          <t>World Bank Group</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9e13379e16ee4b4</t>
+          <t>https://www.indeed.com/viewjob?jk=7a40cff6b5df03cd</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Consultant SW Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f337cce3b659c83d</t>
+          <t>https://www.indeed.com/viewjob?jk=59d1f24bbcec7861</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Associate IT Officer, Data and Information Management (Associate Data Engineer)</t>
+          <t>Senior Analytics Engineer - Power BI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>World Bank Group</t>
+          <t>Broadview Federal Credit Union</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Databricks Lakehouse, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,59 +1196,59 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a40cff6b5df03cd</t>
+          <t>https://www.indeed.com/viewjob?jk=ddee7a1fd9164fde</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer- OrderlyMeds</t>
+          <t>Senior Cloud Operations Engineer - Boston</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>OrderlyMeds</t>
+          <t>REsurety</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, ECS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb2a73a0846955d</t>
+          <t>https://www.indeed.com/viewjob?jk=29974d87917cb0fe</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer III – Cloud Platform Engineering - Python / AWS</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, ECS, RDS, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb199efc831c0dc4</t>
+          <t>https://www.indeed.com/viewjob?jk=be868335e3ef6e98</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III – Cloud Platform Engineering - Python / AWS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, KS, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Azure Cosmos DB, Data Modeling, ELT</t>
+          <t>AWS, EMR, S3, ECS, RDS, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9a02726d78410b5</t>
+          <t>https://www.indeed.com/viewjob?jk=bb199efc831c0dc4</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Energy Services Group</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Atlanta, KS, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Azure Cosmos DB, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6918de34da34b82a</t>
+          <t>https://www.indeed.com/viewjob?jk=e9a02726d78410b5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Trepp</t>
+          <t>Energy Services Group</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=793bcf53c033205f</t>
+          <t>https://www.indeed.com/viewjob?jk=6918de34da34b82a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Unissant</t>
+          <t>Trepp</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00da07441b7a67f</t>
+          <t>https://www.indeed.com/viewjob?jk=793bcf53c033205f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Warehouse Architect</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>Unissant</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,69 +1431,69 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Databricks, GCP, Spark, Scala, Kafka, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48617c6692425cb2</t>
+          <t>https://www.indeed.com/viewjob?jk=a00da07441b7a67f</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II (Remote)</t>
+          <t>Data Engineer - Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Kohl's</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, ETL, MLOps, CI/CD, Docker</t>
+          <t>RDS, Databricks, GCP, Spark, Scala, Kafka, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a7d736f0a5c3255</t>
+          <t>https://www.indeed.com/viewjob?jk=48617c6692425cb2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior SRE I</t>
+          <t>Machine Learning Engineer II (Remote)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Kohl's</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, ETL, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=389e6808cb55dd7e</t>
+          <t>https://www.indeed.com/viewjob?jk=2a7d736f0a5c3255</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DEVELOPER L3(CONTRACT)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Intrado</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Wayne, PA, US USA</t>
+          <t>Longmont, CO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
+          <t>IAM, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e2ca368a02b432d</t>
+          <t>https://www.indeed.com/viewjob?jk=e9f81856c387866b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>DEVELOPER L3(CONTRACT)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Wayne, PA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Kafka, Snowflake, SQL Server, ETL, Tableau</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=782f670b324716aa</t>
+          <t>https://www.indeed.com/viewjob?jk=0e2ca368a02b432d</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65a4b202ac924d0b</t>
+          <t>https://www.indeed.com/viewjob?jk=782f670b324716aa</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Kharon</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Glue, S3, RDS, Scala, Kafka, Snowflake, SQL Server, ETL, Tableau</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1834ddbeb8ec8bb3</t>
+          <t>https://www.indeed.com/viewjob?jk=65a4b202ac924d0b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - IICS</t>
+          <t>Data Platform Engineer | Digital Operations</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SYSTECH USA</t>
+          <t>Beta Technologies</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>South Burlington, VT, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Cloud Storage, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf36b7e279da791</t>
+          <t>https://www.indeed.com/viewjob?jk=741939e568ff083b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Platform Engineer | Digital Operations</t>
+          <t>Sr. Software Engineer - Data Infrastructure</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Beta Technologies</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>South Burlington, VT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, GCP, HDFS, Hive, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=741939e568ff083b</t>
+          <t>https://www.indeed.com/viewjob?jk=df9f48d9232b00bf</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Data Infrastructure</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>IWCO</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chanhassen, MN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, GCP, HDFS, Hive, Spark, Scala, Kafka, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df9f48d9232b00bf</t>
+          <t>https://www.indeed.com/viewjob?jk=196d52ca727cd7dc</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>IWCO</t>
+          <t>DEPARTMENT OF BUILDINGS</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chanhassen, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=196d52ca727cd7dc</t>
+          <t>https://www.indeed.com/viewjob?jk=2e9557f408354fe7</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Architect: Enterprise Data</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>DEPARTMENT OF BUILDINGS</t>
+          <t>Mayer Brown LLP</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e9557f408354fe7</t>
+          <t>https://www.indeed.com/viewjob?jk=ced77385e81a71b8</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Architect: Enterprise Data</t>
+          <t>Senior Developer - Level III - 26-04057</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Mayer Brown LLP</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced77385e81a71b8</t>
+          <t>https://www.indeed.com/viewjob?jk=43063b055188ce3c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Developer - Level III - 26-04057</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Sunbit, Inc</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MySQL, MongoDB, CI/CD, Terraform</t>
+          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1444a89356fbe315</t>
+          <t>https://www.indeed.com/viewjob?jk=6cc0ba82c4bd25dc</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43063b055188ce3c</t>
+          <t>https://www.indeed.com/viewjob?jk=9eeb6502ebf78cc0</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Santa Clarita, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cc0ba82c4bd25dc</t>
+          <t>https://www.indeed.com/viewjob?jk=473b7754552ef179</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Lancaster, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,129 +2001,129 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eeb6502ebf78cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=5e872365f29ac108</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Developer - Level III - 26-04057</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Santa Clarita, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=473b7754552ef179</t>
+          <t>https://www.indeed.com/viewjob?jk=08c0a369d519a555</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Developer - Level III - 26-04057</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Verinext</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Lancaster, CA, US USA</t>
+          <t>Suwanee, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e872365f29ac108</t>
+          <t>https://www.indeed.com/viewjob?jk=63d02d8862b8e251</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr Business Intelligence Developer - Onsite</t>
+          <t>IT Intern - Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Bass Pro Shops</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Snowflake, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba1611f04cfe11a7</t>
+          <t>https://www.indeed.com/viewjob?jk=6189d252c6c4d09f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Database Engineer 3 - Contingent (contract)</t>
+          <t>DevSecOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Hadoop, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>AWS, Glue, Athena, S3, ECS, IAM, RDS, Azure, PostgreSQL, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b28c0b653e1b4d8</t>
+          <t>https://www.indeed.com/viewjob?jk=96f58672f1d141ce</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Database Engineer 3 - Contingent (contract)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Azure, GCP, BigQuery, Hadoop, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c254d2582994d51f</t>
+          <t>https://www.indeed.com/viewjob?jk=2b28c0b653e1b4d8</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=523330c74b38a27b</t>
+          <t>https://www.indeed.com/viewjob?jk=c254d2582994d51f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7beef8ad4f571f7a</t>
+          <t>https://www.indeed.com/viewjob?jk=523330c74b38a27b</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3088b1f92a7a6242</t>
+          <t>https://www.indeed.com/viewjob?jk=7beef8ad4f571f7a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior SRE</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, DynamoDB, Cassandra, NoSQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc41b902449ace0</t>
+          <t>https://www.indeed.com/viewjob?jk=3088b1f92a7a6242</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior SRE</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>COVERCRAFT INDUSTRIES</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,17 +2341,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, GCP, Scala, DynamoDB, Cassandra, NoSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5dc2c7f7fff79d2</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc41b902449ace0</t>
         </is>
       </c>
     </row>
@@ -2393,17 +2393,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer, Cat Digital Data &amp; AI</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>COVERCRAFT INDUSTRIES</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,24 +2411,24 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=699bf154d150027f</t>
+          <t>https://www.indeed.com/viewjob?jk=d5dc2c7f7fff79d2</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer (Full Stack)</t>
+          <t>Data Engineer, Cat Digital Data &amp; AI</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39b5eeee4ff704ee</t>
+          <t>https://www.indeed.com/viewjob?jk=699bf154d150027f</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SRE Architect</t>
+          <t>Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Splunk, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=907826ed55a037a8</t>
+          <t>https://www.indeed.com/viewjob?jk=39b5eeee4ff704ee</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>SRE Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Oracle, ETL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,59 +2526,59 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bca63339137d0189</t>
+          <t>https://www.indeed.com/viewjob?jk=907826ed55a037a8</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer Prin</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Oracle, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e17559f247cbc51a</t>
+          <t>https://www.indeed.com/viewjob?jk=bca63339137d0189</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Business Intelligence Engineer III</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3da1fa1569c709a3</t>
+          <t>https://www.indeed.com/viewjob?jk=a6591940ddbd8809</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Cloud Infrastructure Engineer Prin</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Core &amp; Main</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5e2495e00e0060d</t>
+          <t>https://www.indeed.com/viewjob?jk=e17559f247cbc51a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deb135bf06a2110e</t>
+          <t>https://www.indeed.com/viewjob?jk=3da1fa1569c709a3</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer - MN</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>RAZR Marketing, Inc.</t>
+          <t>Core &amp; Main</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, PostgreSQL, Docker, Kubernetes, CloudWatch</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3375eb3b3d50ba05</t>
+          <t>https://www.indeed.com/viewjob?jk=b5e2495e00e0060d</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Core &amp; Main</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2cdf5f4ac6a6c1a</t>
+          <t>https://www.indeed.com/viewjob?jk=deb135bf06a2110e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Analytic Data Engineer (Python/Power BI)</t>
+          <t>Senior Devops Engineer - MN</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Highmark Health</t>
+          <t>RAZR Marketing, Inc.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, ETL, Power BI</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, PostgreSQL, Docker, Kubernetes, CloudWatch</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=100c60fa90e63408</t>
+          <t>https://www.indeed.com/viewjob?jk=3375eb3b3d50ba05</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Core &amp; Main</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Splunk, CI/CD, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f589c151e81c3302</t>
+          <t>https://www.indeed.com/viewjob?jk=b2cdf5f4ac6a6c1a</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Java backend data engineer - Smithfield RI</t>
+          <t>Senior Analytic Data Engineer (Python/Power BI)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Highmark Health</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, Snowflake, Oracle, Data Modeling, Star Schema, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, ETL, Power BI</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d795ea45cb03ea9</t>
+          <t>https://www.indeed.com/viewjob?jk=100c60fa90e63408</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CardioOne</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Kafka, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34653b24bff70a46</t>
+          <t>https://www.indeed.com/viewjob?jk=009bef0a6c8cccee</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CardioOne</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Splunk, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b44f024bbd36d11</t>
+          <t>https://www.indeed.com/viewjob?jk=f589c151e81c3302</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Experimentation Platform (Backend Services)</t>
+          <t>Java backend data engineer - Smithfield RI</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Paramount Streaming</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,17 +2936,192 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
+          <t>AWS, S3, Snowflake, Oracle, Data Modeling, Star Schema, Jenkins, Terraform, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d795ea45cb03ea9</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>HR -Data Scientist</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Renton, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7513f3b5f73b8498</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>CardioOne</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>CO, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=34653b24bff70a46</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>CardioOne</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b44f024bbd36d11</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Experimentation Platform (Backend Services)</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Paramount Streaming</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
           <t>AWS, Kinesis, Redshift, RDS, GCP, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=1f33593f93ffe80a</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Solution Engineer: Enterprise GenAI &amp; Analytics Enablement</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>American Electric Power</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ed80186b477d6765</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-16.xlsx
+++ b/results/job_matches_2026-04-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Big Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Intellectyx</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pasadena, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.8</v>
+        <v>25</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, BigQuery, Spark</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Hadoop, Hive, Spark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19cc1df5d3223695</t>
+          <t>https://www.indeed.com/viewjob?jk=12cc73e885e46940</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Architect/Modeler</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Intellectyx</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Pasadena, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>20.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Databricks, Spark, Scala</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, BigQuery, Spark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,54 +531,54 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e10ec33698957c81</t>
+          <t>https://www.indeed.com/viewjob?jk=19cc1df5d3223695</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Architect/Modeler</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Veeva Systems</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Step Functions, RDS, Databricks, Medallion Architecture, GCP, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83dccf18841adf6</t>
+          <t>https://www.indeed.com/viewjob?jk=e10ec33698957c81</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Databricks Data Architect - Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BluEnt</t>
+          <t>Veeva Systems</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Spark</t>
+          <t>AWS, EMR, Kinesis, Step Functions, RDS, Databricks, Medallion Architecture, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c12fb6e67e8bda7</t>
+          <t>https://www.indeed.com/viewjob?jk=a83dccf18841adf6</t>
         </is>
       </c>
     </row>
@@ -1063,17 +1063,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Consultant SW Engineer</t>
+          <t>Sr. Eng., Eng Services</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, Athena, S3, IAM, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,67 +1091,67 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f337cce3b659c83d</t>
+          <t>https://www.indeed.com/viewjob?jk=f602056d9e789b25</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Associate IT Officer, Data and Information Management (Associate Data Engineer)</t>
+          <t>Senior Back-End Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>World Bank Group</t>
+          <t>Spectrio LLC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a40cff6b5df03cd</t>
+          <t>https://www.indeed.com/viewjob?jk=1bdc93d3e13ebdd0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Sr. Consultant SW Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59d1f24bbcec7861</t>
+          <t>https://www.indeed.com/viewjob?jk=f337cce3b659c83d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer - Power BI</t>
+          <t>Associate IT Officer, Data and Information Management (Associate Data Engineer)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Broadview Federal Credit Union</t>
+          <t>World Bank Group</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Databricks Lakehouse, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddee7a1fd9164fde</t>
+          <t>https://www.indeed.com/viewjob?jk=7a40cff6b5df03cd</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Cloud Operations Engineer - Boston</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>REsurety</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,59 +1231,59 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29974d87917cb0fe</t>
+          <t>https://www.indeed.com/viewjob?jk=59d1f24bbcec7861</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Senior Analytics Engineer - Power BI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Broadview Federal Credit Union</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Databricks Lakehouse, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be868335e3ef6e98</t>
+          <t>https://www.indeed.com/viewjob?jk=ddee7a1fd9164fde</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer III – Cloud Platform Engineering - Python / AWS</t>
+          <t>Senior Cloud Operations Engineer - Boston</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>REsurety</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, ECS, RDS, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, ECS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb199efc831c0dc4</t>
+          <t>https://www.indeed.com/viewjob?jk=29974d87917cb0fe</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlanta, KS, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Azure Cosmos DB, Data Modeling, ELT</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9a02726d78410b5</t>
+          <t>https://www.indeed.com/viewjob?jk=be868335e3ef6e98</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Software Engineer III – Cloud Platform Engineering - Python / AWS</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Energy Services Group</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, EMR, S3, ECS, RDS, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6918de34da34b82a</t>
+          <t>https://www.indeed.com/viewjob?jk=bb199efc831c0dc4</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Trepp</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, KS, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB, Cassandra</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Azure Cosmos DB, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=793bcf53c033205f</t>
+          <t>https://www.indeed.com/viewjob?jk=e9a02726d78410b5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Unissant</t>
+          <t>Trepp</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00da07441b7a67f</t>
+          <t>https://www.indeed.com/viewjob?jk=793bcf53c033205f</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Warehouse Architect</t>
+          <t>Senior Network Engineer (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,42 +1466,42 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Databricks, GCP, Spark, Scala, Kafka, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48617c6692425cb2</t>
+          <t>https://www.indeed.com/viewjob?jk=cf7e6921496659c0</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II (Remote)</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Kohl's</t>
+          <t>Unissant</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, ETL, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,102 +1511,102 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a7d736f0a5c3255</t>
+          <t>https://www.indeed.com/viewjob?jk=a00da07441b7a67f</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Development Engineer - Cloud Dev</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Intrado</t>
+          <t>Transmedics</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Longmont, CO, US USA</t>
+          <t>Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, Kinesis, Redshift, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9f81856c387866b</t>
+          <t>https://www.indeed.com/viewjob?jk=2f2220b49620882d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DEVELOPER L3(CONTRACT)</t>
+          <t>Data Engineer - Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Wayne, PA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
+          <t>RDS, Databricks, GCP, Spark, Scala, Kafka, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e2ca368a02b432d</t>
+          <t>https://www.indeed.com/viewjob?jk=48617c6692425cb2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Machine Learning Engineer II (Remote)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Kohl's</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Kafka, Snowflake, SQL Server, ETL, Tableau</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, ETL, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,137 +1616,137 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=782f670b324716aa</t>
+          <t>https://www.indeed.com/viewjob?jk=2a7d736f0a5c3255</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Data Engineer, Investments Technology</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Kafka, Snowflake, SQL Server, ETL, Tableau</t>
+          <t>AWS, Lambda, S3, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65a4b202ac924d0b</t>
+          <t>https://www.indeed.com/viewjob?jk=4d24313a2ecfaf34</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Platform Engineer | Digital Operations</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Beta Technologies</t>
+          <t>Intrado</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>South Burlington, VT, US USA</t>
+          <t>Longmont, CO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
+          <t>IAM, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=741939e568ff083b</t>
+          <t>https://www.indeed.com/viewjob?jk=e9f81856c387866b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Data Infrastructure</t>
+          <t>Site Reliability Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, GCP, HDFS, Hive, Spark, Scala, Kafka, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df9f48d9232b00bf</t>
+          <t>https://www.indeed.com/viewjob?jk=50c8f5c8b89d420d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Platform Operations Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>IWCO</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chanhassen, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, CodeBuild</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=196d52ca727cd7dc</t>
+          <t>https://www.indeed.com/viewjob?jk=62bcd4ad2d0bbc62</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>DEVELOPER L3(CONTRACT)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>DEPARTMENT OF BUILDINGS</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Wayne, PA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e9557f408354fe7</t>
+          <t>https://www.indeed.com/viewjob?jk=0e2ca368a02b432d</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Architect: Enterprise Data</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Mayer Brown LLP</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, S3, RDS, Scala, Kafka, Snowflake, SQL Server, ETL, Tableau</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced77385e81a71b8</t>
+          <t>https://www.indeed.com/viewjob?jk=782f670b324716aa</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Developer - Level III - 26-04057</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Glue, S3, RDS, Scala, Kafka, Snowflake, SQL Server, ETL, Tableau</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43063b055188ce3c</t>
+          <t>https://www.indeed.com/viewjob?jk=65a4b202ac924d0b</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Developer - Level III - 26-04057</t>
+          <t>Data Platform Engineer | Digital Operations</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Beta Technologies</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>South Burlington, VT, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cc0ba82c4bd25dc</t>
+          <t>https://www.indeed.com/viewjob?jk=741939e568ff083b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Developer - Level III - 26-04057</t>
+          <t>Sr. Software Engineer - Data Infrastructure</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, S3, RDS, GCP, HDFS, Hive, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eeb6502ebf78cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=df9f48d9232b00bf</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Developer - Level III - 26-04057</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>IWCO</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Santa Clarita, CA, US USA</t>
+          <t>Chanhassen, MN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=473b7754552ef179</t>
+          <t>https://www.indeed.com/viewjob?jk=196d52ca727cd7dc</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Developer - Level III - 26-04057</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>DEPARTMENT OF BUILDINGS</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Lancaster, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,104 +1991,104 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Glue, Lambda, Step Functions, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e872365f29ac108</t>
+          <t>https://www.indeed.com/viewjob?jk=2e9557f408354fe7</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Architect: Enterprise Data</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Mayer Brown LLP</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>RDS, Azure, Data Factory, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08c0a369d519a555</t>
+          <t>https://www.indeed.com/viewjob?jk=ced77385e81a71b8</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Senior Full Stack Developer, Smart Factory Solutions</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Verinext</t>
+          <t>Magna International</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Suwanee, GA, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, S3, ECS, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63d02d8862b8e251</t>
+          <t>https://www.indeed.com/viewjob?jk=a7d8d9f6032e5b6f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>IT Intern - Data Engineer</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Snowflake, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6189d252c6c4d09f</t>
+          <t>https://www.indeed.com/viewjob?jk=08c0a369d519a555</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DevSecOps Cloud Engineer</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>Verinext</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Suwanee, GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, ECS, IAM, RDS, Azure, PostgreSQL, Terraform</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96f58672f1d141ce</t>
+          <t>https://www.indeed.com/viewjob?jk=63d02d8862b8e251</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Database Engineer 3 - Contingent (contract)</t>
+          <t>IT Intern - Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Hadoop, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Snowflake, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b28c0b653e1b4d8</t>
+          <t>https://www.indeed.com/viewjob?jk=6189d252c6c4d09f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>DevSecOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Glue, Athena, S3, ECS, IAM, RDS, Azure, PostgreSQL, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c254d2582994d51f</t>
+          <t>https://www.indeed.com/viewjob?jk=96f58672f1d141ce</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Database Engineer 3 - Contingent (contract)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Azure, GCP, BigQuery, Hadoop, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=523330c74b38a27b</t>
+          <t>https://www.indeed.com/viewjob?jk=2b28c0b653e1b4d8</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7beef8ad4f571f7a</t>
+          <t>https://www.indeed.com/viewjob?jk=c254d2582994d51f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3088b1f92a7a6242</t>
+          <t>https://www.indeed.com/viewjob?jk=523330c74b38a27b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior SRE</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, DynamoDB, Cassandra, NoSQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc41b902449ace0</t>
+          <t>https://www.indeed.com/viewjob?jk=7beef8ad4f571f7a</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Senior SRE</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>API Gateway, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, Scala, DynamoDB, Cassandra, NoSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=412ff8500fa79e71</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc41b902449ace0</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Application Security Analyst</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>COVERCRAFT INDUSTRIES</t>
+          <t>Advait</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Oracle, Splunk, CI/CD, Jenkins, Jenkins, SonarQube, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5dc2c7f7fff79d2</t>
+          <t>https://www.indeed.com/viewjob?jk=d58f2c1ddb77b874</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer, Cat Digital Data &amp; AI</t>
+          <t>Enterprise Analytics BID</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Deaconess Health System</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Evansville, IN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=699bf154d150027f</t>
+          <t>https://www.indeed.com/viewjob?jk=e6e89ffe2f4311bd</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer (Full Stack)</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>COVERCRAFT INDUSTRIES</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39b5eeee4ff704ee</t>
+          <t>https://www.indeed.com/viewjob?jk=d5dc2c7f7fff79d2</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SRE Architect</t>
+          <t>Senior Architect - Data Architecture &amp; Engineering</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>CCG</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Splunk, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=907826ed55a037a8</t>
+          <t>https://www.indeed.com/viewjob?jk=819e894636bd2075</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Senior Performance Test Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>TIAG</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Oracle, ETL, CI/CD, Git</t>
+          <t>AWS, IAM, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,129 +2561,129 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bca63339137d0189</t>
+          <t>https://www.indeed.com/viewjob?jk=82eb3dabcdfd111c</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer III</t>
+          <t>Data Engineer, Cat Digital Data &amp; AI</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6591940ddbd8809</t>
+          <t>https://www.indeed.com/viewjob?jk=699bf154d150027f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer Prin</t>
+          <t>Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e17559f247cbc51a</t>
+          <t>https://www.indeed.com/viewjob?jk=39b5eeee4ff704ee</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Oracle, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3da1fa1569c709a3</t>
+          <t>https://www.indeed.com/viewjob?jk=bca63339137d0189</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Business Intelligence Engineer III</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Core &amp; Main</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5e2495e00e0060d</t>
+          <t>https://www.indeed.com/viewjob?jk=a6591940ddbd8809</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Cloud Infrastructure Engineer Prin</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deb135bf06a2110e</t>
+          <t>https://www.indeed.com/viewjob?jk=e17559f247cbc51a</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer - MN</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>RAZR Marketing, Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,17 +2761,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, PostgreSQL, Docker, Kubernetes, CloudWatch</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3375eb3b3d50ba05</t>
+          <t>https://www.indeed.com/viewjob?jk=3da1fa1569c709a3</t>
         </is>
       </c>
     </row>
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2cdf5f4ac6a6c1a</t>
+          <t>https://www.indeed.com/viewjob?jk=b5e2495e00e0060d</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Analytic Data Engineer (Python/Power BI)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Highmark Health</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, ETL, Power BI</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=100c60fa90e63408</t>
+          <t>https://www.indeed.com/viewjob?jk=deb135bf06a2110e</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Devops Engineer - MN</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>RAZR Marketing, Inc.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, PostgreSQL, Docker, Kubernetes, CloudWatch</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009bef0a6c8cccee</t>
+          <t>https://www.indeed.com/viewjob?jk=3375eb3b3d50ba05</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Splunk, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Kafka, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f589c151e81c3302</t>
+          <t>https://www.indeed.com/viewjob?jk=009bef0a6c8cccee</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Java backend data engineer - Smithfield RI</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, Snowflake, Oracle, Data Modeling, Star Schema, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Splunk, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d795ea45cb03ea9</t>
+          <t>https://www.indeed.com/viewjob?jk=f589c151e81c3302</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>HR -Data Scientist</t>
+          <t>Java backend data engineer - Smithfield RI</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
+          <t>AWS, S3, Snowflake, Oracle, Data Modeling, Star Schema, Jenkins, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7513f3b5f73b8498</t>
+          <t>https://www.indeed.com/viewjob?jk=3d795ea45cb03ea9</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>HR -Data Scientist</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CardioOne</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
+          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34653b24bff70a46</t>
+          <t>https://www.indeed.com/viewjob?jk=7513f3b5f73b8498</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3046,29 +3046,29 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b44f024bbd36d11</t>
+          <t>https://www.indeed.com/viewjob?jk=34653b24bff70a46</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Experimentation Platform (Backend Services)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Paramount Streaming</t>
+          <t>CardioOne</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, GCP, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f33593f93ffe80a</t>
+          <t>https://www.indeed.com/viewjob?jk=7b44f024bbd36d11</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Solution Engineer: Enterprise GenAI &amp; Analytics Enablement</t>
+          <t>Senior Software Engineer, Experimentation Platform (Backend Services)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>American Electric Power</t>
+          <t>Paramount Streaming</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,15 +3111,50 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
+          <t>AWS, Kinesis, Redshift, RDS, GCP, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1f33593f93ffe80a</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Solution Engineer: Enterprise GenAI &amp; Analytics Enablement</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>American Electric Power</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
           <t>AWS, IAM, Azure, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ed80186b477d6765</t>
         </is>

--- a/results/job_matches_2026-04-16.xlsx
+++ b/results/job_matches_2026-04-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect/Modeler</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Intellectyx</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pasadena, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.8</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, BigQuery, Spark</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,59 +531,59 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19cc1df5d3223695</t>
+          <t>https://www.indeed.com/viewjob?jk=e10ec33698957c81</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Architect/Modeler</t>
+          <t>Senior Data Engineer - SDE 26-04140</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e10ec33698957c81</t>
+          <t>https://www.indeed.com/viewjob?jk=d98bfdf8c981815d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - SDE 26-04140</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Veeva Systems</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Step Functions, RDS, Databricks, Medallion Architecture, GCP, Spark, Scala</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83dccf18841adf6</t>
+          <t>https://www.indeed.com/viewjob?jk=08b278bfb38191e0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Application Developer, Portland Oregon</t>
+          <t>Senior Data Engineer - SDE 26-04140</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Portland General Electric</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Bronx, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,77 +626,77 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9f186e739ef98be</t>
+          <t>https://www.indeed.com/viewjob?jk=f397f88e84805b3d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Engineer - SDE 26-04140</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HelioCampus</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=333fbc294a529a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=6b89ceef5f047ae5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Kafka Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Veeva Systems</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Oracle, SQL Server</t>
+          <t>AWS, EMR, Kinesis, Step Functions, RDS, Databricks, Medallion Architecture, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,59 +706,59 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=288d8ed989f5e263</t>
+          <t>https://www.indeed.com/viewjob?jk=a83dccf18841adf6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Application Developer, Portland Oregon</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EssilorLuxottica</t>
+          <t>Portland General Electric</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb1eb66e038f22b4</t>
+          <t>https://www.indeed.com/viewjob?jk=f9f186e739ef98be</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Credit Risk (Hybrid) - New York, NY</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>EssilorLuxottica</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23517bc36e765c0f</t>
+          <t>https://www.indeed.com/viewjob?jk=cb1eb66e038f22b4</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16e736022550c4c5</t>
+          <t>https://www.indeed.com/viewjob?jk=23517bc36e765c0f</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97b0320ba5b0219b</t>
+          <t>https://www.indeed.com/viewjob?jk=16e736022550c4c5</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bronx, NY, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22e782dc41b4055e</t>
+          <t>https://www.indeed.com/viewjob?jk=97b0320ba5b0219b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Graph DBA</t>
+          <t>Senior Data Engineer – Credit Risk (Hybrid) - New York, NY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Bronx, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c15f03a1274f889c</t>
+          <t>https://www.indeed.com/viewjob?jk=22e782dc41b4055e</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8b5a8aa7c2f7cd5</t>
+          <t>https://www.indeed.com/viewjob?jk=c15f03a1274f889c</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0522d81a23e6425</t>
+          <t>https://www.indeed.com/viewjob?jk=e8b5a8aa7c2f7cd5</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,59 +1021,59 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10fa9278e203e8c7</t>
+          <t>https://www.indeed.com/viewjob?jk=a0522d81a23e6425</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Graph DBA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BLOC Resources, LLC</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9e13379e16ee4b4</t>
+          <t>https://www.indeed.com/viewjob?jk=10fa9278e203e8c7</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Eng., Eng Services</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>BLOC Resources, LLC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, IAM, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
+          <t>Azure, Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f602056d9e789b25</t>
+          <t>https://www.indeed.com/viewjob?jk=d9e13379e16ee4b4</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Back-End Engineer</t>
+          <t>Sr. Consultant SW Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Spectrio LLC</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, PostgreSQL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bdc93d3e13ebdd0</t>
+          <t>https://www.indeed.com/viewjob?jk=f337cce3b659c83d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Consultant SW Engineer</t>
+          <t>Sr. Eng., Eng Services</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, Athena, S3, IAM, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f337cce3b659c83d</t>
+          <t>https://www.indeed.com/viewjob?jk=f602056d9e789b25</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Network Engineer (Hybrid - Seattle, WA)</t>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf7e6921496659c0</t>
+          <t>https://www.indeed.com/viewjob?jk=c4db1e66cf2c5955</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Unissant</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00da07441b7a67f</t>
+          <t>https://www.indeed.com/viewjob?jk=941a8e269aca7287</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - Cloud Dev</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Transmedics</t>
+          <t>Unissant</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Andover, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,69 +1536,69 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2220b49620882d</t>
+          <t>https://www.indeed.com/viewjob?jk=a00da07441b7a67f</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Warehouse Architect</t>
+          <t>Machine Learning Engineer II (Remote)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>Kohl's</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Databricks, GCP, Spark, Scala, Kafka, Oracle, Data Modeling, ETL, ELT</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, ETL, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48617c6692425cb2</t>
+          <t>https://www.indeed.com/viewjob?jk=2a7d736f0a5c3255</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II (Remote)</t>
+          <t>Senior Data Engineer, Investments Technology</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Kohl's</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, ETL, MLOps, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a7d736f0a5c3255</t>
+          <t>https://www.indeed.com/viewjob?jk=4d24313a2ecfaf34</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Investments Technology</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Intrado</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Longmont, CO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,42 +1641,42 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
+          <t>IAM, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d24313a2ecfaf34</t>
+          <t>https://www.indeed.com/viewjob?jk=e9f81856c387866b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Engineer, Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Intrado</t>
+          <t>Carnival Cruise Line</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Longmont, CO, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, IAM, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9f81856c387866b</t>
+          <t>https://www.indeed.com/viewjob?jk=ec3bf6ef8f52ebe5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Site Reliability Architect</t>
+          <t>DEVELOPER L3(CONTRACT)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Wayne, PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, Splunk, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c8f5c8b89d420d</t>
+          <t>https://www.indeed.com/viewjob?jk=0e2ca368a02b432d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Platform Operations Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, CodeBuild</t>
+          <t>AWS, Glue, S3, RDS, Scala, Kafka, Snowflake, SQL Server, ETL, Tableau</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62bcd4ad2d0bbc62</t>
+          <t>https://www.indeed.com/viewjob?jk=782f670b324716aa</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DEVELOPER L3(CONTRACT)</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Wayne, PA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
+          <t>AWS, Glue, S3, RDS, Scala, Kafka, Snowflake, SQL Server, ETL, Tableau</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e2ca368a02b432d</t>
+          <t>https://www.indeed.com/viewjob?jk=65a4b202ac924d0b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Platform Engineer | Digital Operations</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Beta Technologies</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>South Burlington, VT, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Kafka, Snowflake, SQL Server, ETL, Tableau</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=782f670b324716aa</t>
+          <t>https://www.indeed.com/viewjob?jk=741939e568ff083b</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Sr. Software Engineer - Data Infrastructure</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Kafka, Snowflake, SQL Server, ETL, Tableau</t>
+          <t>AWS, S3, RDS, GCP, HDFS, Hive, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65a4b202ac924d0b</t>
+          <t>https://www.indeed.com/viewjob?jk=df9f48d9232b00bf</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Platform Engineer | Digital Operations</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Beta Technologies</t>
+          <t>DEPARTMENT OF BUILDINGS</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>South Burlington, VT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=741939e568ff083b</t>
+          <t>https://www.indeed.com/viewjob?jk=2e9557f408354fe7</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Data Infrastructure</t>
+          <t>Architect: Enterprise Data</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Mayer Brown LLP</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, GCP, HDFS, Hive, Spark, Scala, Kafka, CI/CD</t>
+          <t>RDS, Azure, Data Factory, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df9f48d9232b00bf</t>
+          <t>https://www.indeed.com/viewjob?jk=ced77385e81a71b8</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>IWCO</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chanhassen, MN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=196d52ca727cd7dc</t>
+          <t>https://www.indeed.com/viewjob?jk=08c0a369d519a555</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>DEPARTMENT OF BUILDINGS</t>
+          <t>Verinext</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Suwanee, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,94 +2001,94 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e9557f408354fe7</t>
+          <t>https://www.indeed.com/viewjob?jk=63d02d8862b8e251</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Architect: Enterprise Data</t>
+          <t>IT Intern - Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Mayer Brown LLP</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Snowflake, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced77385e81a71b8</t>
+          <t>https://www.indeed.com/viewjob?jk=6189d252c6c4d09f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer, Smart Factory Solutions</t>
+          <t>DevSecOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Magna International</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, Athena, S3, ECS, IAM, RDS, Azure, PostgreSQL, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7d8d9f6032e5b6f</t>
+          <t>https://www.indeed.com/viewjob?jk=96f58672f1d141ce</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Database Engineer 3 - Contingent (contract)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, Azure, GCP, BigQuery, Hadoop, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08c0a369d519a555</t>
+          <t>https://www.indeed.com/viewjob?jk=2b28c0b653e1b4d8</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Verinext</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Suwanee, GA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63d02d8862b8e251</t>
+          <t>https://www.indeed.com/viewjob?jk=c254d2582994d51f</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>IT Intern - Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Snowflake, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6189d252c6c4d09f</t>
+          <t>https://www.indeed.com/viewjob?jk=523330c74b38a27b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DevSecOps Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, ECS, IAM, RDS, Azure, PostgreSQL, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96f58672f1d141ce</t>
+          <t>https://www.indeed.com/viewjob?jk=7beef8ad4f571f7a</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Database Engineer 3 - Contingent (contract)</t>
+          <t>Senior SRE</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Hadoop, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, GCP, Scala, DynamoDB, Cassandra, NoSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b28c0b653e1b4d8</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc41b902449ace0</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer, Cat Digital Data &amp; AI</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c254d2582994d51f</t>
+          <t>https://www.indeed.com/viewjob?jk=699bf154d150027f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Remote Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Astronaut Party Inc.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=523330c74b38a27b</t>
+          <t>https://www.indeed.com/viewjob?jk=c53661df7aef299c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Enterprise Analytics BID</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deaconess Health System</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Evansville, IN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7beef8ad4f571f7a</t>
+          <t>https://www.indeed.com/viewjob?jk=e6e89ffe2f4311bd</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior SRE</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>COVERCRAFT INDUSTRIES</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, DynamoDB, Cassandra, NoSQL, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc41b902449ace0</t>
+          <t>https://www.indeed.com/viewjob?jk=d5dc2c7f7fff79d2</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Application Security Analyst</t>
+          <t>Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Advait</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,42 +2411,42 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, Splunk, CI/CD, Jenkins, Jenkins, SonarQube, Git</t>
+          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d58f2c1ddb77b874</t>
+          <t>https://www.indeed.com/viewjob?jk=39b5eeee4ff704ee</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Enterprise Analytics BID</t>
+          <t>Senior Systems Engineer (Commercial)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Deaconess Health System</t>
+          <t>AutoZone</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Evansville, IN, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI</t>
+          <t>API Gateway, RDS, Google Cloud Platform, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6e89ffe2f4311bd</t>
+          <t>https://www.indeed.com/viewjob?jk=00a3623a3bc10b68</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Business Intelligence Engineer III</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>COVERCRAFT INDUSTRIES</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5dc2c7f7fff79d2</t>
+          <t>https://www.indeed.com/viewjob?jk=a6591940ddbd8809</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Architect - Data Architecture &amp; Engineering</t>
+          <t>Cloud Infrastructure Engineer Prin</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CCG</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server, Power BI, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,67 +2526,67 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=819e894636bd2075</t>
+          <t>https://www.indeed.com/viewjob?jk=e17559f247cbc51a</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Performance Test Engineer</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>TIAG</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82eb3dabcdfd111c</t>
+          <t>https://www.indeed.com/viewjob?jk=3da1fa1569c709a3</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer, Cat Digital Data &amp; AI</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Core &amp; Main</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=699bf154d150027f</t>
+          <t>https://www.indeed.com/viewjob?jk=b5e2495e00e0060d</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer (Full Stack)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,59 +2631,59 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39b5eeee4ff704ee</t>
+          <t>https://www.indeed.com/viewjob?jk=deb135bf06a2110e</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Java backend data engineer - Smithfield RI</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Oracle, ETL, CI/CD, Git</t>
+          <t>AWS, S3, Snowflake, Oracle, Data Modeling, Star Schema, Jenkins, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bca63339137d0189</t>
+          <t>https://www.indeed.com/viewjob?jk=3d795ea45cb03ea9</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer III</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6591940ddbd8809</t>
+          <t>https://www.indeed.com/viewjob?jk=009bef0a6c8cccee</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer Prin</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Splunk, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e17559f247cbc51a</t>
+          <t>https://www.indeed.com/viewjob?jk=f589c151e81c3302</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CardioOne</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3da1fa1569c709a3</t>
+          <t>https://www.indeed.com/viewjob?jk=34653b24bff70a46</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Core &amp; Main</t>
+          <t>CardioOne</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5e2495e00e0060d</t>
+          <t>https://www.indeed.com/viewjob?jk=7b44f024bbd36d11</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>HR -Data Scientist</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,332 +2831,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deb135bf06a2110e</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Senior Devops Engineer - MN</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>RAZR Marketing, Inc.</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Minnetonka, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, PostgreSQL, Docker, Kubernetes, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3375eb3b3d50ba05</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>American Airlines</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Kafka, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=009bef0a6c8cccee</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Waystar</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Splunk, CI/CD, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f589c151e81c3302</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Java backend data engineer - Smithfield RI</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Photon</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Smithfield, RI, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>AWS, S3, Snowflake, Oracle, Data Modeling, Star Schema, Jenkins, Terraform, Docker, Jenkins</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3d795ea45cb03ea9</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>HR -Data Scientist</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Renton, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=7513f3b5f73b8498</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>CardioOne</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>CO, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=34653b24bff70a46</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>CardioOne</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7b44f024bbd36d11</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Experimentation Platform (Backend Services)</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Paramount Streaming</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, Redshift, RDS, GCP, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1f33593f93ffe80a</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Solution Engineer: Enterprise GenAI &amp; Analytics Enablement</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>American Electric Power</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ed80186b477d6765</t>
         </is>
       </c>
     </row>
